--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2693,6 +2693,254 @@
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>社区-聚合(外网)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GitHub·mnfst/awesome-free-llm-apis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://github.com/mnfst/awesome-free-llm-apis</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>精选仓库</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>👁 每周 diff(助理)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>待核</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>仅收永久免费层·无信用卡——外网薅羊毛母矿</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>r/LLM 172 赞</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>社区-聚合(外网)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>r/LocalLLaMA·550+ 免费LLM工具清单</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/LocalLLaMA/comments/1sigg35/</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>reddit帖</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>待核</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>550+ 免费/低价工具</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>社区-聚合(外网)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Reddit 免费API 三大追踪帖</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/AI_Agents/comments/1uqlox8/</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>reddit帖</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>待核</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>可续杯免费API深挖/better_claw限时排名/r.openclaw月更</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>社区-聚合(外网)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>OpenRouter 官方博客·13家免费API横评</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://openrouter.ai/blog/tutorials/free-llm-apis-compared</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>官方博客</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>🤖 harvest 候选</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>待核</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>官方口径横评</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>下轮评估入采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>社区-聚合(外网)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>StationX·120模型$0指南</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://app.stationx.net/articles/free-llm-api</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>待核</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>DeepSeek/Kimi/OpenCode 配置指南</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3661,7 +3909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3846,6 +4094,50 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>外网第一轮：5 个海外聚合源/清单（母矿=awesome-free-llm-apis）</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WebSearch(us)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>总表+发现日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>自愈三件套上线：heartbeat+龙虾watchdog(30min弹窗)+Obsidian自动同步</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>老板令</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tools/export_obsidian_md.py + watchdog_check.sh</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2943,6 +2943,110 @@
       <c r="I57" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>官方-页面(外网)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Cursor 定价（X订阅新体系）</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://cursor.com/pricing</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>10-12 改版:Free/Plus$8/Premium$30/Super$100/Ultra$200 与 Grok 共享池</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>⌨️Coding面板变更线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>官方-页面(外网)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Windsurf 定价</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://windsurf.com/pricing</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>免费档约25 Flow Actions/月·SWE-1 mini·16K</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>外网体验档</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4313,6 +4417,28 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>队列✅（不入总表，负情报）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cursor 10-12 新价目体系(变更线索)+Windsurf 免费档细则；两官方页入采集器</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
         </is>
       </c>
     </row>
@@ -12488,6 +12614,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12516,6 +12647,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12544,6 +12680,11 @@
           <t>github:yacuo/ai-coding-plan</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12572,6 +12713,11 @@
           <t>github:yacuo/ai-coding-plan</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12600,6 +12746,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12628,6 +12779,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12656,6 +12812,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12684,6 +12845,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12712,6 +12878,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12740,6 +12911,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12768,6 +12944,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12796,6 +12977,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12824,6 +13010,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12852,6 +13043,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12880,6 +13076,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12908,6 +13109,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12936,6 +13142,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12964,6 +13175,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12992,6 +13208,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13020,6 +13241,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13048,6 +13274,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13076,6 +13307,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13104,6 +13340,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13132,6 +13373,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13160,6 +13406,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13188,6 +13439,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13216,6 +13472,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13244,6 +13505,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13272,6 +13538,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -13300,6 +13571,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -13328,6 +13604,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -13356,6 +13637,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13384,6 +13670,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13412,6 +13703,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13440,6 +13736,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13468,6 +13769,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13496,6 +13802,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13524,6 +13835,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13552,6 +13868,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13580,6 +13901,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13608,6 +13934,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13636,6 +13967,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13664,6 +14000,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13690,6 +14031,11 @@
       <c r="F293" t="inlineStr">
         <is>
           <t>github:open-free-llm-api/awesome-freellm</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3047,6 +3047,162 @@
       <c r="J59" t="inlineStr">
         <is>
           <t>外网体验档</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>线索-平台(外网)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MonkeyCode ⭐每日3000万免费tokens</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>(官方入口待定位)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>单源(IDE横评)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>每日3000万·无需信用卡——已知最大方每日档</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>超过火山500万/日6倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>线索-平台(外网)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TRAE 五档价目</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://ai.dosa.dev/tools/trae</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>待核</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Free/Lite$8/Pro$20/Pro+$60/Ultra$200</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>字节海外 IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>官方-页面</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MonkeyCode 官方文档(长亭科技)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://monkeycode.docs.baizhi.cloud</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>文档页</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>每日免费token政策</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>官网 monkeycode.cn · GitHub chaitin/MonkeyCode</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4437,6 +4593,50 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>外网重磅线索：MonkeyCode 每日3000万免费tokens(单源待核)+TRAE 五档价目</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>总表线索区</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MonkeyCode 定位：长亭科技/monkeycode.cn；数额多源出入(标准1000万/日·活动3000万·历史促销500亿)→主管按控制台核</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>总表+采集器</t>
         </is>
@@ -14066,6 +14266,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14094,6 +14299,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14122,6 +14332,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14150,6 +14365,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14178,6 +14398,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14206,6 +14431,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14234,6 +14464,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14262,6 +14497,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14290,6 +14530,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14318,6 +14563,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14346,6 +14596,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14374,6 +14629,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14402,6 +14662,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14430,6 +14695,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14458,6 +14728,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14486,6 +14761,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14514,6 +14794,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14542,6 +14827,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14570,6 +14860,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14598,6 +14893,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14626,6 +14926,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14654,6 +14959,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14682,6 +14992,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14710,6 +15025,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14738,6 +15058,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14766,6 +15091,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -14794,6 +15124,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -14822,6 +15157,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14850,6 +15190,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -14878,6 +15223,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -14906,6 +15256,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14934,6 +15289,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -14962,6 +15322,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14990,6 +15355,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15018,6 +15388,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15046,6 +15421,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15074,6 +15454,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15102,6 +15487,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15130,6 +15520,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15158,6 +15553,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15186,6 +15586,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15214,6 +15619,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15242,6 +15652,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15270,6 +15685,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15298,6 +15718,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15326,6 +15751,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15354,6 +15784,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -15382,6 +15817,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -15410,6 +15850,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -15438,6 +15883,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -15466,6 +15916,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -15494,6 +15949,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -15522,6 +15982,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -15550,6 +16015,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -15578,6 +16048,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -15606,6 +16081,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -15634,6 +16114,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -15662,6 +16147,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -15690,6 +16180,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -15718,6 +16213,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -15746,6 +16246,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -15774,6 +16279,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -15802,6 +16312,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -15830,6 +16345,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -15858,6 +16378,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -15886,6 +16411,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -15914,6 +16444,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -15942,6 +16477,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -15970,6 +16510,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -15998,6 +16543,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -16026,6 +16576,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16054,6 +16609,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -16082,6 +16642,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16110,6 +16675,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -16138,6 +16708,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -16166,6 +16741,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -16194,6 +16774,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -16222,6 +16807,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -16250,6 +16840,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -16278,6 +16873,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -16306,6 +16906,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -16334,6 +16939,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -16362,6 +16972,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -16390,6 +17005,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -16418,6 +17038,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -16446,6 +17071,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -16474,6 +17104,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -16502,6 +17137,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -16530,6 +17170,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -16556,6 +17201,11 @@
       <c r="F383" t="inlineStr">
         <is>
           <t>github:ShaikhWarsi/free-ai-tools</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3203,6 +3203,110 @@
       <c r="J62" t="inlineStr">
         <is>
           <t>官网 monkeycode.cn · GitHub chaitin/MonkeyCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>线索-平台(外网)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HuggingFace 推理积分</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/docs/inference-providers</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(低优)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>已查实</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>免费档仅$0.10/月≈10条消息；PRO$9/月含$2——负情报</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Startup 项目另有赠码渠道</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>线索-平台</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>小米 MiMo（已查实：免费计划已领完→转永久降价99%）</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://100t.xiaomimimo.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(低价条目)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>已查实</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>100T计划5月领完；MiMo-2.5 API 约Claude 1/5价·百万上下文</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>多源交叉：鉅亨/网易/知乎/腾讯</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4639,6 +4743,50 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HuggingFace 免费档查实$0.10/月——负情报结案；FreeToken 清单连续两轮内容变化(高活源观察中)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>总表线索区</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小米MiMo查实：100T免费计划已领完→永久降价99%常态化；低价条目候选</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>总表线索区</t>
         </is>
       </c>
     </row>
@@ -17236,6 +17384,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -17264,6 +17417,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -17292,6 +17450,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -17320,6 +17483,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -17348,6 +17516,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -17376,6 +17549,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -17404,6 +17582,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -17432,6 +17615,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -17460,6 +17648,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -17488,6 +17681,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -17516,6 +17714,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -17544,6 +17747,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -17572,6 +17780,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17600,6 +17813,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -17629,6 +17847,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -17657,6 +17880,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -17685,6 +17913,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -17713,6 +17946,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -17741,6 +17979,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -17769,6 +18012,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -17797,6 +18045,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -17825,6 +18078,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -17853,6 +18111,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -17881,6 +18144,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -17909,6 +18177,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -17937,6 +18210,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -17965,6 +18243,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -17993,6 +18276,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -18021,6 +18309,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -18049,6 +18342,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -18077,6 +18375,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -18105,6 +18408,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -18133,6 +18441,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -18161,6 +18474,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -18189,6 +18507,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -18217,6 +18540,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -18245,6 +18573,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -18273,6 +18606,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -18301,6 +18639,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -18329,6 +18672,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -18357,6 +18705,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -18385,6 +18738,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -18413,6 +18771,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -18441,6 +18804,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -18469,6 +18837,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -18497,6 +18870,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -18525,6 +18903,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -18553,6 +18936,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -18581,6 +18969,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -18609,6 +19002,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -18637,6 +19035,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -18665,6 +19068,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -18693,6 +19101,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -18721,6 +19134,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -18749,6 +19167,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -18777,6 +19200,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -18805,6 +19233,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -18833,6 +19266,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -18861,6 +19299,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -18889,6 +19332,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -18917,6 +19365,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -18945,6 +19398,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -18973,6 +19431,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -19001,6 +19464,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -19029,6 +19497,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -19057,6 +19530,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -19085,6 +19563,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -19113,6 +19596,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -19141,6 +19629,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -19169,6 +19662,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -19197,6 +19695,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -19225,6 +19728,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -19253,6 +19761,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -19281,6 +19794,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -19309,6 +19827,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -19337,6 +19860,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -19365,6 +19893,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -19393,6 +19926,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -19421,6 +19959,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -19449,6 +19992,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -19477,6 +20025,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -19505,6 +20058,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -19533,6 +20091,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -19561,6 +20124,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -19589,6 +20157,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -19617,6 +20190,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -19645,6 +20223,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -19673,6 +20256,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -19701,6 +20289,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -19729,6 +20322,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -19757,6 +20355,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -19785,6 +20388,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -19813,6 +20421,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -19841,6 +20454,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -19867,6 +20485,11 @@
       <c r="F478" t="inlineStr">
         <is>
           <t>github:mvalentsev/awesome-free-ai-coding</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3307,6 +3307,110 @@
       <c r="J64" t="inlineStr">
         <is>
           <t>多源交叉：鉅亨/网易/知乎/腾讯</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>smzdm·AI产品免费权益清单(2026.09)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://post.smzdm.com/p/arz6v8rg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>9月版免费权益清单</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>主会话 smzdm 系列新增一贴</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>线索-降级</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>讯飞星辰 Qwen 不限量=6月限时月度活动</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>(CSDN 博客口径，非官方)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>活动</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>✅ 已查实(降级)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>已过期(10月)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>「不限量至2026年」说法不实——限时活动</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>与讯飞避雷前科相互印证</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4787,6 +4891,28 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>总表线索区</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>讯飞星辰不限量查实=6月限时活动(降级)；smzdm 2026.09 清单新帖入表</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>总表</t>
         </is>
       </c>
     </row>
@@ -20520,6 +20646,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -20548,6 +20679,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -20576,6 +20712,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -20604,6 +20745,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -20632,6 +20778,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -20660,6 +20811,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -20688,6 +20844,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -20716,6 +20877,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -20744,6 +20910,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -20772,6 +20943,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -20800,6 +20976,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -20828,6 +21009,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -20856,6 +21042,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -20884,6 +21075,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -20912,6 +21108,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -20940,6 +21141,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -20968,6 +21174,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -20996,6 +21207,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -21024,6 +21240,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -21052,6 +21273,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -21080,6 +21306,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -21108,6 +21339,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -21136,6 +21372,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -21164,6 +21405,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -21192,6 +21438,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -21220,6 +21471,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -21248,6 +21504,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -21276,6 +21537,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -21304,6 +21570,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -21332,6 +21603,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -21360,6 +21636,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -21388,6 +21669,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -21416,6 +21702,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -21444,6 +21735,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -21472,6 +21768,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -21500,6 +21801,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -21528,6 +21834,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -21556,6 +21867,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -21584,6 +21900,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -21612,6 +21933,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -21640,6 +21966,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -21668,6 +21999,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -21696,6 +22032,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -21724,6 +22065,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -21752,6 +22098,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -21780,6 +22131,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -21808,6 +22164,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -21836,6 +22197,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -21862,6 +22228,11 @@
       <c r="F527" t="inlineStr">
         <is>
           <t>github:mvalentsev/awesome-free-ai-coding</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3411,6 +3411,204 @@
       <c r="J66" t="inlineStr">
         <is>
           <t>与讯飞避雷前科相互印证</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>线索-平台(外网)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NVIDIA NIM 免费API大升级⭐</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://news.cnblogs.com/n/841857</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>双源(smzdm+cnblogs)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>80-100+模型一年免费·不限总量·40RPM·国内手机号可注册——远超主数据1000 credits口径</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>变更线索：nvidia-nim 条目或需改写</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CSDN·每月16亿token开源API实践(姊妹两篇)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://blog.csdn.net/weixin_32597009/article/details/163422709</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>15个免费大模型API获取指南</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>含姊妹篇 163422710</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CSDN·2026大模型API免费额度汇总</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://blog.csdn.net/weixin_55062269/article/details/158925835</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>百炼/千帆等额度清单</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CSDN·2026免费LLM API完全指南</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://blog.csdn.net/weixin_48321392/article/details/159241594</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>主流平台限额实测对比</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4911,6 +5109,28 @@
         </is>
       </c>
       <c r="D19" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NVIDIA NIM 免费API大升级变更线索(高优)+3个CSDN聚合源；「每天10亿」仍未定位维持线索</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>总表</t>
         </is>
@@ -22263,6 +22483,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -22291,6 +22516,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -22319,6 +22549,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -22347,6 +22582,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -22375,6 +22615,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -22403,6 +22648,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -22431,6 +22681,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -22459,6 +22714,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -22487,6 +22747,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -22515,6 +22780,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -22543,6 +22813,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -22571,6 +22846,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -22599,6 +22879,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -22627,6 +22912,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -22655,6 +22945,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -22683,6 +22978,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -22711,6 +23011,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -22739,6 +23044,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -22767,6 +23077,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -22795,6 +23110,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -22823,6 +23143,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -22851,6 +23176,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -22879,6 +23209,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -22907,6 +23242,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -22935,6 +23275,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -22963,6 +23308,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -22991,6 +23341,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -23019,6 +23374,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -23047,6 +23407,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -23075,6 +23440,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -23103,6 +23473,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -23131,6 +23506,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -23159,6 +23539,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -23187,6 +23572,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -23215,6 +23605,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -23243,6 +23638,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -23271,6 +23671,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -23299,6 +23704,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -23327,6 +23737,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -23355,6 +23770,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -23383,6 +23803,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -23411,6 +23836,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -23439,6 +23869,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -23467,6 +23902,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -23495,6 +23935,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -23523,6 +23968,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -23551,6 +24001,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -23579,6 +24034,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -23607,6 +24067,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -23635,6 +24100,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -23663,6 +24133,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -23691,6 +24166,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -23719,6 +24199,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -23747,6 +24232,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -23775,6 +24265,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -23803,6 +24298,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -23831,6 +24331,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -23859,6 +24364,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -23887,6 +24397,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -23915,6 +24430,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -23943,6 +24463,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -23971,6 +24496,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -23999,6 +24529,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -24027,6 +24562,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -24055,6 +24595,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -24083,6 +24628,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -24111,6 +24661,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -24139,6 +24694,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -24167,6 +24727,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -24195,6 +24760,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -24223,6 +24793,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -24251,6 +24826,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -24279,6 +24859,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -24307,6 +24892,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -24335,6 +24925,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -24363,6 +24958,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -24391,6 +24991,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -24419,6 +25024,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -24447,6 +25057,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -24475,6 +25090,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -24503,6 +25123,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -24531,6 +25156,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -24559,6 +25189,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -24587,6 +25222,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -24615,6 +25255,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -24643,6 +25288,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -24671,6 +25321,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -24699,6 +25354,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -24727,6 +25387,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -24755,6 +25420,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -24783,6 +25453,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -24811,6 +25486,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -24839,6 +25519,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -24867,6 +25552,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -24893,6 +25583,11 @@
       <c r="F622" t="inlineStr">
         <is>
           <t>github:mvalentsev/awesome-free-ai-coding</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3609,6 +3609,110 @@
       <c r="I70" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>线索-降级</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>智谱「实名送2亿」未证实</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>(SegmentFault 线索)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>活动</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>✅ 已查实(降级)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>官方页无此活动</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>实为:邀请2000万/注册200万/周末3亿等，2亿系夸大</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>防止假羊毛</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>线索-活动</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>智谱「每日一亿 token 免费领取」</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>(CSDN 佐证，入口 open.bigmodel.cn)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>活动</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>单源</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>配合 ZCode 编程场景使用</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>每日登录类摸底唯一产出</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5131,6 +5235,50 @@
         </is>
       </c>
       <c r="D20" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>⭐修正发现：官方promotion页现已列出 Weekend Build 3亿/ZCode 1亿/1024节5亿——zcode-linuxdo 升级路径打开；「实名2亿」降级</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HANDOFF→主会话</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>每日登录类摸底结案：各平台无统一签到中心；智谱每日一亿领取线索转主管；配额5小时重置技巧已属主数据</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>总表</t>
         </is>
@@ -25618,6 +25766,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -25646,6 +25799,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -25674,6 +25832,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -25702,6 +25865,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -25730,6 +25898,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -25758,6 +25931,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -25786,6 +25964,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -25814,6 +25997,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -25842,6 +26030,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -25870,6 +26063,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -25898,6 +26096,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -25926,6 +26129,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -25954,6 +26162,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -25982,6 +26195,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -26010,6 +26228,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -26038,6 +26261,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -26066,6 +26294,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -26094,6 +26327,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -26122,6 +26360,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -26150,6 +26393,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -26178,6 +26426,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -26206,6 +26459,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -26234,6 +26492,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -26262,6 +26525,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -26290,6 +26558,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -26318,6 +26591,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -26346,6 +26624,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -26374,6 +26657,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -26402,6 +26690,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -26430,6 +26723,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -26458,6 +26756,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -26486,6 +26789,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -26514,6 +26822,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -26542,6 +26855,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -26570,6 +26888,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -26598,6 +26921,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -26626,6 +26954,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -26654,6 +26987,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -26682,6 +27020,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -26710,6 +27053,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -26738,6 +27086,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -26766,6 +27119,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -26794,6 +27152,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -26822,6 +27185,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -26850,6 +27218,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -26878,6 +27251,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -26904,6 +27282,11 @@
       <c r="F669" t="inlineStr">
         <is>
           <t>github:mvalentsev/awesome-free-ai-coding</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>offtopic</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3713,6 +3713,58 @@
       <c r="J72" t="inlineStr">
         <is>
           <t>每日登录类摸底唯一产出</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>变更线索(外网)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Windsurf 并入 Cognition/Devin⭐</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://devin.ai/pricing</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>windsurf.com 308 实测</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>官网定价整页跳转 devin.ai——体验档横评中 Windsurf 条目需更新归属</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>采集器已改指新地址</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5281,6 +5333,28 @@
       <c r="D22" t="inlineStr">
         <is>
           <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>源故障诊断结案：gemini/mistral=网络层不可达(VPN相关)、groq=403硬反爬(摘出转人工)、windsurf=308→devin.ai(Windsurf并入Cognition变更线索)；采集器加 disabled 支持(64活跃/1停用)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
         </is>
       </c>
     </row>
@@ -27317,6 +27391,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -27345,6 +27424,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -27373,6 +27457,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -27401,6 +27490,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -27429,6 +27523,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -27457,6 +27556,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -27485,6 +27589,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -27513,6 +27622,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -27541,6 +27655,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -27569,6 +27688,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -27597,6 +27721,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -27625,6 +27754,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -27653,6 +27787,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -27681,6 +27820,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -27709,6 +27853,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -27737,6 +27886,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -27765,6 +27919,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -27793,6 +27952,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -27821,6 +27985,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -27849,6 +28018,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -27877,6 +28051,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -27905,6 +28084,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -27933,6 +28117,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -27961,6 +28150,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -27989,6 +28183,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -28017,6 +28216,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -28045,6 +28249,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -28073,6 +28282,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -28101,6 +28315,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -28129,6 +28348,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -28157,6 +28381,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -28185,6 +28414,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -28213,6 +28447,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -28241,6 +28480,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -28269,6 +28513,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -28297,6 +28546,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -28325,6 +28579,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -28353,6 +28612,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -28381,6 +28645,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -28409,6 +28678,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -28437,6 +28711,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -28465,6 +28744,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -28493,6 +28777,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -28521,6 +28810,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -28549,6 +28843,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -28577,6 +28876,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -28605,6 +28909,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -28631,6 +28940,11 @@
       <c r="F717" t="inlineStr">
         <is>
           <t>github:ClawLabsAI/free-ai-models</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -28975,6 +28975,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -29003,6 +29008,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -29031,6 +29041,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -29059,6 +29074,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -29087,6 +29107,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -29115,6 +29140,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -29143,6 +29173,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -29171,6 +29206,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -29199,6 +29239,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -29227,6 +29272,11 @@
           <t>github:AIPMAndy/FreeToken</t>
         </is>
       </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -29255,6 +29305,11 @@
           <t>github:AIPMAndy/FreeToken</t>
         </is>
       </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -29283,6 +29338,11 @@
           <t>github:AIPMAndy/FreeToken</t>
         </is>
       </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -29311,6 +29371,11 @@
           <t>github:AIPMAndy/FreeToken</t>
         </is>
       </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -29339,6 +29404,11 @@
           <t>github:ruodou233/free-token-eggs</t>
         </is>
       </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -29367,6 +29437,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -29395,6 +29470,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -29423,6 +29503,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -29451,6 +29536,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -29479,6 +29569,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -29507,6 +29602,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -29535,6 +29635,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -29563,6 +29668,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -29591,6 +29701,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -29619,6 +29734,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -29647,6 +29767,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -29675,6 +29800,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -29703,6 +29833,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -29731,6 +29866,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -29759,6 +29899,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -29787,6 +29932,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -29815,6 +29965,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -29843,6 +29998,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -29871,6 +30031,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -29899,6 +30064,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -29927,6 +30097,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -29955,6 +30130,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -29983,6 +30163,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -30011,6 +30196,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -30039,6 +30229,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -30067,6 +30262,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -30095,6 +30295,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -30123,6 +30328,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -30151,6 +30361,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -30179,6 +30394,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -30205,6 +30425,11 @@
       <c r="F762" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3767,6 +3767,158 @@
           <t>采集器已改指新地址</t>
         </is>
       </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>竞品/同类站</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>token.pencilai.top（token羊毛党）</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://token.pencilai.top</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>汇总站</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>👁 每周人工(竞品监测)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>v2ex 2026-10 帖</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>汇集免费模型/编程套餐/领取步骤——同类站，监测其收录差异</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fast.v2ex.com/t/1247809</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>线索-修正</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>小米 MiMo 额度重置+50倍配额+0.01元续费</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>(v2ex TG 频道 2026-05 多帖)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>多帖佐证</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>修正昨日「已领完」结论——现为重置+50倍态</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>另有免费送380亿额度帖</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>线索-平台</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>快手/美团 免费 API(14天)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>(v2ex 帖 cn.v2ex.com/t/1180034)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>单帖</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>国产大厂免费 API 14 天</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4843,7 +4995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5355,6 +5507,28 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>v2ex 摸底：竞品站 token.pencilai.top 发现⭐+MiMo 状态修正(重置50倍)+快手/美团线索+套壳类帖拒收</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>总表</t>
         </is>
       </c>
     </row>
@@ -30460,6 +30634,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -30488,6 +30667,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -30516,6 +30700,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -30544,6 +30733,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -30572,6 +30766,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -30600,6 +30799,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -30628,6 +30832,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -30656,6 +30865,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -30684,6 +30898,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -30712,6 +30931,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -30740,6 +30964,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -30768,6 +30997,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -30796,6 +31030,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -30824,6 +31063,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -30852,6 +31096,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -30880,6 +31129,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -30908,6 +31162,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -30936,6 +31195,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -30964,6 +31228,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -30992,6 +31261,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -31020,6 +31294,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -31048,6 +31327,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -31076,6 +31360,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -31104,6 +31393,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -31132,6 +31426,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -31160,6 +31459,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -31188,6 +31492,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -31216,6 +31525,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -31244,6 +31558,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -31272,6 +31591,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -31300,6 +31624,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -31328,6 +31657,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -31351,6 +31685,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -31374,6 +31713,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -31397,6 +31741,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -31420,6 +31769,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -31443,6 +31797,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -31466,6 +31825,11 @@
           <t>github:CelaDaniel/free-ai-resources-x</t>
         </is>
       </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -31489,6 +31853,11 @@
           <t>github:teodorgross/awesome-ai</t>
         </is>
       </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -31512,6 +31881,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -31535,6 +31909,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -31558,6 +31937,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -31579,6 +31963,11 @@
       <c r="F805" t="inlineStr">
         <is>
           <t>github:mvalentsev/awesome-free-ai-coding</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -3791,7 +3791,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>👁 每周人工(竞品监测)</t>
+          <t>🤖 harvest 竞品雷达</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>v2ex 2026-10 帖</t>
+          <t>✅ 已收编监测</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>fast.v2ex.com/t/1247809</t>
+          <t>侦察完成：编辑线=本地agent免费模型/编程套餐，网页聊天不收录（与我们差异互补）；静态78KB可抓，已入采集器</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4995,7 +4994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5529,6 +5528,28 @@
       <c r="D24" t="inlineStr">
         <is>
           <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>竞品站收编：token.pencilai.top 入采集器（其上新即告警）；OpenRouter API 快照项确认主会话已覆盖→闭环</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
         </is>
       </c>
     </row>
@@ -31993,6 +32014,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -32016,6 +32042,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -32039,6 +32070,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -32062,6 +32098,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -32085,6 +32126,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -32108,6 +32154,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -32131,6 +32182,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -32154,6 +32210,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -32177,6 +32238,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -32200,6 +32266,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -32223,6 +32294,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -32246,6 +32322,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -32269,6 +32350,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -32292,6 +32378,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -32315,6 +32406,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -32338,6 +32434,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -32361,6 +32462,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -32384,6 +32490,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -32407,6 +32518,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -32430,6 +32546,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -32453,6 +32574,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -32476,6 +32602,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -32499,6 +32630,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -32522,6 +32658,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -32545,6 +32686,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -32568,6 +32714,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -32591,6 +32742,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -32614,6 +32770,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -32637,6 +32798,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -32660,6 +32826,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -32683,6 +32854,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -32706,6 +32882,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -32729,6 +32910,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -32752,6 +32938,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -32775,6 +32966,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -32798,6 +32994,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -32821,6 +33022,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -32844,6 +33050,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -32867,6 +33078,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -32890,6 +33106,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -32913,6 +33134,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -32936,6 +33162,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -32959,6 +33190,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -32982,6 +33218,11 @@
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -33005,6 +33246,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -33028,6 +33274,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -33051,6 +33302,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -33074,6 +33330,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -33097,6 +33358,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -33118,6 +33384,11 @@
       <c r="F855" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>offtopic</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3916,6 +3916,58 @@
       <c r="I76" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>线索-变更(外网)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GitHub Copilot 学生免费权益变动⭐</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://education.github.com/pack</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Copilot Pro 学生版 3-12 终止→Copilot Student 4月暂停→现状不明；主数据 github-student-pack 条目表述需复核</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Copilot Free 2000补全/50聊天 仍有效</t>
         </is>
       </c>
     </row>
@@ -4994,7 +5046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5550,6 +5602,28 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GitHub 学生包变更线索：Copilot 学生免费 3-12 终止+Student 计划 4 月暂停→主数据条目需复核；竞品雷达/学生认证项闭环</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>总表</t>
         </is>
       </c>
     </row>
@@ -33414,6 +33488,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -33437,6 +33516,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -33460,6 +33544,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -33483,6 +33572,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -33506,6 +33600,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -33529,6 +33628,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -33552,6 +33656,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -33575,6 +33684,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -33598,6 +33712,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -33621,6 +33740,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -33644,6 +33768,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -33667,6 +33796,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -33690,6 +33824,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -33713,6 +33852,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -33736,6 +33880,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -33759,6 +33908,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -33782,6 +33936,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -33805,6 +33964,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -33828,6 +33992,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -33851,6 +34020,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -33874,6 +34048,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -33897,6 +34076,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -33920,6 +34104,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -33943,6 +34132,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -33966,6 +34160,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -33989,6 +34188,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -34012,6 +34216,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -34035,6 +34244,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -34058,6 +34272,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -34081,6 +34300,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -34104,6 +34328,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -34127,6 +34356,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -34150,6 +34384,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -34173,6 +34412,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -34196,6 +34440,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -34219,6 +34468,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -34242,6 +34496,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -34265,6 +34524,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -34288,6 +34552,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -34311,6 +34580,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -34334,6 +34608,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -34357,6 +34636,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -34380,6 +34664,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -34401,6 +34690,11 @@
       <c r="F899" t="inlineStr">
         <is>
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>offtopic</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -3677,7 +3677,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>(CSDN 佐证，入口 open.bigmodel.cn)</t>
+          <t>https://bigmodel.cn/activity/trial-card/*（页族）</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>⏳ 主管核实(入口已定位)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>配合 ZCode 编程场景使用</t>
+          <t>体验卡页族已定位（8+ 个 trial-card 页），数额需登录核</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4017,7 +4017,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4065,7 +4064,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4113,7 +4111,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4161,7 +4158,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4209,7 +4205,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4257,7 +4252,6 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5334,7 +5328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5956,6 +5950,28 @@
       <c r="D28" t="inlineStr">
         <is>
           <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>智谱「每日一亿」入口定位：bigmodel.cn/activity/trial-card 页族(8+体验卡页)——数额待登录核</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>总表线索升级</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4250,6 +4250,58 @@
       <c r="I83" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>神级工具(外网)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>OmniRoute 本地AI网关⭐</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://github.com/diegosouzapw/OmniRoute</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>开源工具</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>200-300+提供商聚一个端点·免费额度仪表盘15-16亿/月·Combo永不停机路由</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>「34家白嫖神」定位成功；CSDN 双文佐证</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5972,6 +6024,28 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>总表线索升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>「34家白嫖神」定位=OmniRoute(3.7万Star)⭐——工具源入采集器，主会话可评估收录进站点工具区</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>✅ 评估通过已入列</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5380,7 +5380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6044,6 +6044,28 @@
         </is>
       </c>
       <c r="D30" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>lololowe 博客评估通过入采集器（Key合集页·11平台直链）；队列剩3条</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>总表+采集器</t>
         </is>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4302,6 +4302,58 @@
       <c r="J84" t="inlineStr">
         <is>
           <t>「34家白嫖神」定位成功；CSDN 双文佐证</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>线索-平台</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TaoToken 统一Key聚合网关</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://taotoken.net</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>CSDN 5篇推广</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>OpenAI+Anthropic双协议·国内直连·注册送免费额度——数额口径待核</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>聚合平台类（中间商层在收录范围内）</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6068,6 +6120,28 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TaoToken 定位：taotoken.net 统一Key网关（聚合平台类线索→主管核数额口径）</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>总表</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4354,6 +4354,58 @@
       <c r="J85" t="inlineStr">
         <is>
           <t>聚合平台类（中间商层在收录范围内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>线索-套餐(海外)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>z.ai GLM Coding Plan 海外版</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://z.ai</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>套餐订阅</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Reddit+第三方</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Lite$18/Pro$80/Max$168；配额≈Claude同级3倍；海外ZCode $16.2/月</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>⌨️Coding面板海外版候选；无常驻免费额度</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6140,6 +6192,28 @@
         </is>
       </c>
       <c r="D32" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>z.ai 海外 Coding Plan 查实（三档价格+3倍配额定位）→⌨️Coding面板海外版候选</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>总表</t>
         </is>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4406,6 +4406,58 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>⌨️Coding面板海外版候选；无常驻免费额度</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>线索-工具(外网)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AgentReady 省 token 代理</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://agentready.cloud</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(低优)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>HN 2026-02 front</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Drop-in 代理砍 LLM 成本 40-60%——生产力侧工具，非免费token源</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>HN 摸底产出</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6214,6 +6266,28 @@
         </is>
       </c>
       <c r="D33" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HN 摸底：无免费额度类直命中；AgentReady 省token代理工具线索(低优)入账</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>总表</t>
         </is>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4458,6 +4458,110 @@
       <c r="J87" t="inlineStr">
         <is>
           <t>HN 摸底产出</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>线索-平台</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>美团 LongCat 开放平台⭐</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://longcat.ai</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>LongCat-Flash-Chat 已开源(560B MoE)；官方平台+文档已入采集器；免费数额待控制台核</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>快手/美团线索的美团侧落点</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>神级工具(外网)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kilo Code 免费路由扩展</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://blog.kilo.ai</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kilo Auto Free：免信用卡自动路由 8+ 免费模型（开源 VS Code 扩展）</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>其官方文档源已在采集器</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6288,6 +6392,50 @@
         </is>
       </c>
       <c r="D34" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LongCat(美团)查实：开源模型+官方平台，免费数额待控制台核；验证推进至1011条(701相关)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kilo Code 查实：Kilo Auto Free 免费路由层（8+模型无信用卡）→工具区评估；验证推进1061条(750相关)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>总表</t>
         </is>
@@ -31595,7 +31743,7 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>relevant</t>
+          <t>weak</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -5322,7 +5322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5629,6 +5629,33 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>茉界 🆕(雷达发现)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>《GitHub Copilot不让学生免费用最新的大模型了》等 AI 资讯</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>微信内搜索</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>👁 人工关注</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>账号提取管道首个产出；其 Copilot 文章与学生权益变更线索互证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5640,7 +5667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6438,6 +6465,28 @@
       <c r="D36" t="inlineStr">
         <is>
           <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>公众号雷达第4周：新账号「茉界」+Copilot学生变更互证；68源全绿；验证累计1111条(750相关)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>公众号sheet</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -5667,7 +5667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6487,6 +6487,28 @@
       <c r="D37" t="inlineStr">
         <is>
           <t>公众号sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>搜狗/link：单条解析3/3攻克，多查询连发触发反爬——改进项入队（每轮1条/分离会话）</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>队列</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>⏳ 主管核实(已补全细节)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>官网定价整页跳转 devin.ai——体验档横评中 Windsurf 条目需更新归属</t>
+          <t>改名 Devin Desktop；积分制3月废→每日/每周用量刷新；免费档=轻量+有限Cascade；Pro$20/500+credits；薅法=devin.ai 注册14天Pro试用再登录 Windsurf</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5667,7 +5667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6509,6 +6509,28 @@
       <c r="D38" t="inlineStr">
         <is>
           <t>队列</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Devin/Windsurf 迁移细节补全（积分制废弃+14天Pro试用薅法）</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>总表线索升级</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4562,6 +4562,58 @@
       <c r="J89" t="inlineStr">
         <is>
           <t>其官方文档源已在采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>竞品/同类站(老板指派)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AI羊毛情报站 aiyangmao.xyz⭐</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://aiyangmao.xyz</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>汇总站</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>🤖 harvest 竞品雷达</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>免费×139/额度×86/token×99——内容密度高，纯前端皮肤系统(light/dark/neon)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>排版学习对象：三主题一键切换+卡片圆角+CSS变量</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6531,6 +6583,28 @@
       <c r="D39" t="inlineStr">
         <is>
           <t>总表线索升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>aiyangmao.xyz 收编（竞品雷达+排版学习：三主题皮肤系统）——老板指派；16条积压合并巡检完成，心跳确认存活</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4617,6 +4617,318 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>官方-页面(海外)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>DeepInfra 定价</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com/prices</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>免费起·按量</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>官方-页面(海外)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fireworks 定价</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://fireworks.ai/pricing</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>$1 起步积分</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>官方-页面(海外)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Modal 定价</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://modal.com/pricing</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>$30/月免费积分(历史口径)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>官方-页面(海外)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Novita 定价</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://novita.ai/pricing</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>free-to-start·130模型</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>官方-页面(海外)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>xAI 定价</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://console.x.ai</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>负情报盯防(免费档已退场)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>线索-降级(海外)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>xAI 免费档退场</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>(console.x.ai)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>✅ 已查实(负情报)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>$150/月数据共享计划2026春退场；仅剩注册$25(或有不)——Grok4.7 $2/$6每M</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>不立项，盯防再变</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4689,7 +5001,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4717,7 +5028,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4745,7 +5055,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4773,7 +5082,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4801,7 +5109,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4829,7 +5136,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4857,7 +5163,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5045,7 +5350,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5073,7 +5377,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5101,7 +5404,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5129,7 +5431,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5157,7 +5458,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5185,7 +5485,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5245,7 +5544,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5273,7 +5571,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5365,7 +5662,6 @@
           <t>活跃</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7643,7 +7939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8527,6 +8823,28 @@
         </is>
       </c>
       <c r="D40" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>海外扩容战役：DeepInfra/Fireworks/Modal/Novita/xAI 五家核查入表+采集器；Fireworks$1起步/Modal$30月/xAI负情报</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>海外扩容</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>总表+采集器</t>
         </is>
@@ -50584,7 +50902,6 @@
       <c r="D1398" t="n">
         <v>5</v>
       </c>
-      <c r="E1398" t="inlineStr"/>
       <c r="F1398" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
@@ -50788,7 +51105,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1404" t="inlineStr"/>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
@@ -50817,7 +51133,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1405" t="inlineStr"/>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
@@ -50846,7 +51161,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1406" t="inlineStr"/>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
@@ -50875,7 +51189,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1407" t="inlineStr"/>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
@@ -50904,7 +51217,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1408" t="inlineStr"/>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
@@ -50923,7 +51235,6 @@
       <c r="D1409" t="n">
         <v>5</v>
       </c>
-      <c r="E1409" t="inlineStr"/>
       <c r="F1409" t="inlineStr">
         <is>
           <t>https://developer.cloud.tencent.com/arti</t>
@@ -50962,7 +51273,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1410" t="inlineStr"/>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
@@ -50991,7 +51301,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1411" t="inlineStr"/>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
@@ -51020,7 +51329,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1412" t="inlineStr"/>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
@@ -51049,7 +51357,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1413" t="inlineStr"/>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
@@ -51078,7 +51385,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1414" t="inlineStr"/>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
@@ -51107,7 +51413,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1415" t="inlineStr"/>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
@@ -51136,7 +51441,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1416" t="inlineStr"/>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
@@ -51165,7 +51469,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1417" t="inlineStr"/>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
@@ -51194,7 +51497,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1418" t="inlineStr"/>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
@@ -51223,7 +51525,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1419" t="inlineStr"/>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
@@ -51252,7 +51553,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1420" t="inlineStr"/>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
@@ -51281,7 +51581,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1421" t="inlineStr"/>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
@@ -51310,7 +51609,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1422" t="inlineStr"/>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
@@ -51339,7 +51637,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1423" t="inlineStr"/>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
@@ -51368,7 +51665,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1424" t="inlineStr"/>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
@@ -51397,7 +51693,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1425" t="inlineStr"/>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
@@ -51426,7 +51721,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1426" t="inlineStr"/>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
@@ -51455,7 +51749,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1427" t="inlineStr"/>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
@@ -51484,7 +51777,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1428" t="inlineStr"/>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
@@ -51513,7 +51805,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1429" t="inlineStr"/>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
@@ -51542,7 +51833,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1430" t="inlineStr"/>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
@@ -51571,7 +51861,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1431" t="inlineStr"/>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
@@ -51600,7 +51889,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1432" t="inlineStr"/>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
@@ -51629,7 +51917,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1433" t="inlineStr"/>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
@@ -51658,7 +51945,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1434" t="inlineStr"/>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
@@ -51687,7 +51973,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1435" t="inlineStr"/>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
@@ -51716,7 +52001,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1436" t="inlineStr"/>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
@@ -51745,7 +52029,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1437" t="inlineStr"/>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
@@ -51774,7 +52057,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1438" t="inlineStr"/>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
@@ -51803,7 +52085,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1439" t="inlineStr"/>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
@@ -51832,7 +52113,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1440" t="inlineStr"/>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
@@ -51861,7 +52141,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1441" t="inlineStr"/>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
@@ -51890,7 +52169,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1442" t="inlineStr"/>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
@@ -51919,7 +52197,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1443" t="inlineStr"/>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
@@ -51948,7 +52225,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1444" t="inlineStr"/>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
@@ -51977,7 +52253,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1445" t="inlineStr"/>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
@@ -52006,7 +52281,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1446" t="inlineStr"/>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
@@ -52035,7 +52309,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1447" t="inlineStr"/>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
@@ -52064,7 +52337,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1448" t="inlineStr"/>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
@@ -52093,7 +52365,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1449" t="inlineStr"/>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
@@ -52122,7 +52393,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1450" t="inlineStr"/>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
@@ -52151,7 +52421,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1451" t="inlineStr"/>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
@@ -52180,7 +52449,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1452" t="inlineStr"/>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
@@ -52209,7 +52477,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1453" t="inlineStr"/>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
@@ -52238,7 +52505,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1454" t="inlineStr"/>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
@@ -52267,7 +52533,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1455" t="inlineStr"/>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
@@ -52296,7 +52561,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1456" t="inlineStr"/>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
@@ -52325,7 +52589,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1457" t="inlineStr"/>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
@@ -52354,7 +52617,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1458" t="inlineStr"/>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
@@ -52383,7 +52645,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1459" t="inlineStr"/>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
@@ -52412,7 +52673,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1460" t="inlineStr"/>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
@@ -52441,7 +52701,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1461" t="inlineStr"/>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
@@ -52470,7 +52729,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1462" t="inlineStr"/>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
@@ -52499,7 +52757,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1463" t="inlineStr"/>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
@@ -52528,7 +52785,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1464" t="inlineStr"/>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
@@ -52557,7 +52813,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1465" t="inlineStr"/>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
@@ -52586,7 +52841,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1466" t="inlineStr"/>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
@@ -52615,7 +52869,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1467" t="inlineStr"/>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
@@ -52644,7 +52897,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1468" t="inlineStr"/>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
@@ -52673,7 +52925,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1469" t="inlineStr"/>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
@@ -52702,7 +52953,6 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1470" t="inlineStr"/>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
@@ -52731,7 +52981,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1471" t="inlineStr"/>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
@@ -52760,7 +53009,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1472" t="inlineStr"/>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
@@ -52789,7 +53037,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1473" t="inlineStr"/>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
@@ -52818,7 +53065,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1474" t="inlineStr"/>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
@@ -52847,7 +53093,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1475" t="inlineStr"/>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
@@ -52876,7 +53121,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1476" t="inlineStr"/>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
@@ -52905,7 +53149,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1477" t="inlineStr"/>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
@@ -52934,7 +53177,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1478" t="inlineStr"/>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
@@ -52963,7 +53205,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1479" t="inlineStr"/>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
@@ -52992,7 +53233,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1480" t="inlineStr"/>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
@@ -53021,7 +53261,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1481" t="inlineStr"/>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
@@ -53050,7 +53289,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1482" t="inlineStr"/>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
@@ -53079,7 +53317,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1483" t="inlineStr"/>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
@@ -53108,7 +53345,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1484" t="inlineStr"/>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
@@ -53137,7 +53373,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1485" t="inlineStr"/>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
@@ -53166,7 +53401,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1486" t="inlineStr"/>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
@@ -53195,7 +53429,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1487" t="inlineStr"/>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
@@ -53224,7 +53457,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1488" t="inlineStr"/>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
@@ -53253,7 +53485,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1489" t="inlineStr"/>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
@@ -53282,7 +53513,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1490" t="inlineStr"/>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
@@ -53311,7 +53541,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1491" t="inlineStr"/>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
@@ -53340,7 +53569,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1492" t="inlineStr"/>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
@@ -53369,7 +53597,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1493" t="inlineStr"/>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
@@ -53398,7 +53625,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1494" t="inlineStr"/>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
@@ -53427,7 +53653,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1495" t="inlineStr"/>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
@@ -53456,7 +53681,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1496" t="inlineStr"/>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
@@ -53485,7 +53709,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1497" t="inlineStr"/>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
@@ -53514,7 +53737,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1498" t="inlineStr"/>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
@@ -53543,7 +53765,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1499" t="inlineStr"/>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
@@ -53572,7 +53793,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1500" t="inlineStr"/>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
@@ -53601,7 +53821,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1501" t="inlineStr"/>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
@@ -53630,7 +53849,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1502" t="inlineStr"/>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
@@ -53659,7 +53877,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1503" t="inlineStr"/>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
@@ -53688,7 +53905,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1504" t="inlineStr"/>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
@@ -53717,7 +53933,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1505" t="inlineStr"/>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
@@ -53746,7 +53961,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1506" t="inlineStr"/>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
@@ -53775,7 +53989,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1507" t="inlineStr"/>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
@@ -53804,7 +54017,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1508" t="inlineStr"/>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
@@ -53833,7 +54045,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1509" t="inlineStr"/>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
@@ -53862,7 +54073,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1510" t="inlineStr"/>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
@@ -53891,7 +54101,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1511" t="inlineStr"/>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
@@ -53920,7 +54129,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1512" t="inlineStr"/>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
@@ -53949,7 +54157,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1513" t="inlineStr"/>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
@@ -53978,7 +54185,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1514" t="inlineStr"/>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
@@ -54007,7 +54213,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1515" t="inlineStr"/>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
@@ -54036,7 +54241,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1516" t="inlineStr"/>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
@@ -54065,7 +54269,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1517" t="inlineStr"/>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
@@ -54094,7 +54297,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1518" t="inlineStr"/>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
@@ -54123,7 +54325,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1519" t="inlineStr"/>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
@@ -54152,7 +54353,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1520" t="inlineStr"/>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
@@ -54181,7 +54381,6 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1521" t="inlineStr"/>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
@@ -54210,7 +54409,6 @@
           <t>github:KhaiTrang1995/agentic-awesome-kit</t>
         </is>
       </c>
-      <c r="G1522" t="inlineStr"/>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
@@ -54239,7 +54437,6 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
-      <c r="G1523" t="inlineStr"/>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
@@ -54268,7 +54465,6 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
-      <c r="G1524" t="inlineStr"/>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
@@ -54297,7 +54493,6 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
-      <c r="G1525" t="inlineStr"/>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
@@ -54326,7 +54521,6 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
-      <c r="G1526" t="inlineStr"/>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
@@ -54355,7 +54549,6 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
-      <c r="G1527" t="inlineStr"/>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
@@ -54384,7 +54577,6 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
-      <c r="G1528" t="inlineStr"/>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
@@ -54413,7 +54605,6 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
-      <c r="G1529" t="inlineStr"/>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
@@ -54442,7 +54633,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1530" t="inlineStr"/>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
@@ -54471,7 +54661,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1531" t="inlineStr"/>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
@@ -54500,7 +54689,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1532" t="inlineStr"/>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
@@ -54529,7 +54717,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1533" t="inlineStr"/>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
@@ -54558,7 +54745,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1534" t="inlineStr"/>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
@@ -54587,7 +54773,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1535" t="inlineStr"/>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
@@ -54616,7 +54801,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1536" t="inlineStr"/>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
@@ -54645,7 +54829,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1537" t="inlineStr"/>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
@@ -54674,7 +54857,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1538" t="inlineStr"/>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
@@ -54703,7 +54885,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1539" t="inlineStr"/>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
@@ -54732,7 +54913,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1540" t="inlineStr"/>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
@@ -54761,7 +54941,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1541" t="inlineStr"/>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
@@ -54790,7 +54969,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1542" t="inlineStr"/>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
@@ -54819,7 +54997,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1543" t="inlineStr"/>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
@@ -54848,7 +55025,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1544" t="inlineStr"/>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
@@ -54877,7 +55053,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1545" t="inlineStr"/>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
@@ -54906,7 +55081,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1546" t="inlineStr"/>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
@@ -54935,7 +55109,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1547" t="inlineStr"/>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
@@ -54964,7 +55137,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1548" t="inlineStr"/>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
@@ -54993,7 +55165,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1549" t="inlineStr"/>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
@@ -55022,7 +55193,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1550" t="inlineStr"/>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
@@ -55051,7 +55221,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1551" t="inlineStr"/>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
@@ -55080,7 +55249,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1552" t="inlineStr"/>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
@@ -55109,7 +55277,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1553" t="inlineStr"/>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
@@ -55138,7 +55305,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1554" t="inlineStr"/>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
@@ -55167,7 +55333,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1555" t="inlineStr"/>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
@@ -55196,7 +55361,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1556" t="inlineStr"/>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
@@ -55225,7 +55389,6 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1557" t="inlineStr"/>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
@@ -55254,7 +55417,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1558" t="inlineStr"/>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
@@ -55283,7 +55445,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1559" t="inlineStr"/>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
@@ -55312,7 +55473,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1560" t="inlineStr"/>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
@@ -55341,7 +55501,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1561" t="inlineStr"/>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
@@ -55370,7 +55529,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1562" t="inlineStr"/>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
@@ -55399,7 +55557,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1563" t="inlineStr"/>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
@@ -55428,7 +55585,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1564" t="inlineStr"/>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
@@ -55457,7 +55613,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1565" t="inlineStr"/>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
@@ -55486,7 +55641,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1566" t="inlineStr"/>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
@@ -55515,7 +55669,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1567" t="inlineStr"/>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
@@ -55544,7 +55697,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1568" t="inlineStr"/>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
@@ -55573,7 +55725,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1569" t="inlineStr"/>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
@@ -55602,7 +55753,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1570" t="inlineStr"/>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
@@ -55631,7 +55781,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1571" t="inlineStr"/>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
@@ -55660,7 +55809,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1572" t="inlineStr"/>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
@@ -55689,7 +55837,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1573" t="inlineStr"/>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
@@ -55718,7 +55865,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1574" t="inlineStr"/>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
@@ -55747,7 +55893,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1575" t="inlineStr"/>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
@@ -55776,7 +55921,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1576" t="inlineStr"/>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
@@ -55805,7 +55949,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1577" t="inlineStr"/>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
@@ -55834,7 +55977,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1578" t="inlineStr"/>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
@@ -55863,7 +56005,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1579" t="inlineStr"/>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
@@ -55892,7 +56033,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1580" t="inlineStr"/>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
@@ -55921,7 +56061,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1581" t="inlineStr"/>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
@@ -55950,7 +56089,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1582" t="inlineStr"/>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
@@ -55979,7 +56117,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1583" t="inlineStr"/>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
@@ -56008,7 +56145,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1584" t="inlineStr"/>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
@@ -56037,7 +56173,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1585" t="inlineStr"/>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
@@ -56066,7 +56201,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1586" t="inlineStr"/>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
@@ -56095,7 +56229,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1587" t="inlineStr"/>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
@@ -56124,7 +56257,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1588" t="inlineStr"/>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
@@ -56153,7 +56285,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1589" t="inlineStr"/>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
@@ -56182,7 +56313,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1590" t="inlineStr"/>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
@@ -56211,7 +56341,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1591" t="inlineStr"/>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
@@ -56240,7 +56369,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1592" t="inlineStr"/>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
@@ -56269,7 +56397,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1593" t="inlineStr"/>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
@@ -56298,7 +56425,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1594" t="inlineStr"/>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
@@ -56327,7 +56453,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1595" t="inlineStr"/>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
@@ -56356,7 +56481,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1596" t="inlineStr"/>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
@@ -56385,7 +56509,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1597" t="inlineStr"/>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
@@ -56414,7 +56537,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1598" t="inlineStr"/>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
@@ -56443,7 +56565,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1599" t="inlineStr"/>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
@@ -56472,7 +56593,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1600" t="inlineStr"/>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
@@ -56501,7 +56621,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1601" t="inlineStr"/>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
@@ -56530,7 +56649,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1602" t="inlineStr"/>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
@@ -56559,7 +56677,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1603" t="inlineStr"/>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
@@ -56588,7 +56705,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1604" t="inlineStr"/>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
@@ -56617,7 +56733,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1605" t="inlineStr"/>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
@@ -56646,7 +56761,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1606" t="inlineStr"/>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
@@ -56675,7 +56789,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1607" t="inlineStr"/>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
@@ -56704,7 +56817,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1608" t="inlineStr"/>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
@@ -56733,7 +56845,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1609" t="inlineStr"/>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
@@ -56762,7 +56873,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1610" t="inlineStr"/>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
@@ -56791,7 +56901,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1611" t="inlineStr"/>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
@@ -56820,7 +56929,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1612" t="inlineStr"/>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
@@ -56849,7 +56957,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1613" t="inlineStr"/>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
@@ -56878,7 +56985,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1614" t="inlineStr"/>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
@@ -56907,7 +57013,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1615" t="inlineStr"/>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
@@ -56936,7 +57041,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1616" t="inlineStr"/>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
@@ -56965,7 +57069,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1617" t="inlineStr"/>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
@@ -56994,7 +57097,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1618" t="inlineStr"/>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
@@ -57023,7 +57125,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1619" t="inlineStr"/>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
@@ -57052,7 +57153,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1620" t="inlineStr"/>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
@@ -57081,7 +57181,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1621" t="inlineStr"/>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
@@ -57110,7 +57209,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1622" t="inlineStr"/>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
@@ -57139,7 +57237,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1623" t="inlineStr"/>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
@@ -57168,7 +57265,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1624" t="inlineStr"/>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
@@ -57197,7 +57293,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1625" t="inlineStr"/>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
@@ -57226,7 +57321,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1626" t="inlineStr"/>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
@@ -57255,7 +57349,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1627" t="inlineStr"/>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
@@ -57284,7 +57377,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1628" t="inlineStr"/>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
@@ -57313,7 +57405,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1629" t="inlineStr"/>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
@@ -57342,7 +57433,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1630" t="inlineStr"/>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
@@ -57371,7 +57461,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1631" t="inlineStr"/>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
@@ -57400,7 +57489,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1632" t="inlineStr"/>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
@@ -57429,7 +57517,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1633" t="inlineStr"/>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
@@ -57458,7 +57545,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1634" t="inlineStr"/>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
@@ -57487,7 +57573,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1635" t="inlineStr"/>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
@@ -57516,7 +57601,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1636" t="inlineStr"/>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
@@ -57545,7 +57629,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1637" t="inlineStr"/>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
@@ -57574,7 +57657,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1638" t="inlineStr"/>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
@@ -57603,7 +57685,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1639" t="inlineStr"/>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
@@ -57632,7 +57713,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1640" t="inlineStr"/>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
@@ -57661,7 +57741,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1641" t="inlineStr"/>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
@@ -57690,7 +57769,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1642" t="inlineStr"/>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
@@ -57719,7 +57797,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1643" t="inlineStr"/>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
@@ -57748,7 +57825,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1644" t="inlineStr"/>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
@@ -57777,7 +57853,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1645" t="inlineStr"/>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
@@ -57806,7 +57881,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1646" t="inlineStr"/>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
@@ -57835,7 +57909,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1647" t="inlineStr"/>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
@@ -57864,7 +57937,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1648" t="inlineStr"/>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
@@ -57893,7 +57965,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1649" t="inlineStr"/>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
@@ -57922,7 +57993,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1650" t="inlineStr"/>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
@@ -57951,7 +58021,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1651" t="inlineStr"/>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
@@ -57980,7 +58049,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1652" t="inlineStr"/>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
@@ -58009,7 +58077,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1653" t="inlineStr"/>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
@@ -58038,7 +58105,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1654" t="inlineStr"/>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
@@ -58067,7 +58133,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1655" t="inlineStr"/>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
@@ -58096,7 +58161,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1656" t="inlineStr"/>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
@@ -58125,7 +58189,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1657" t="inlineStr"/>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
@@ -58154,7 +58217,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1658" t="inlineStr"/>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
@@ -58183,7 +58245,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1659" t="inlineStr"/>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
@@ -58212,7 +58273,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1660" t="inlineStr"/>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
@@ -58241,7 +58301,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1661" t="inlineStr"/>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
@@ -58270,7 +58329,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1662" t="inlineStr"/>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
@@ -58299,7 +58357,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1663" t="inlineStr"/>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
@@ -58328,7 +58385,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1664" t="inlineStr"/>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
@@ -58357,7 +58413,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1665" t="inlineStr"/>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
@@ -58386,7 +58441,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1666" t="inlineStr"/>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
@@ -58415,7 +58469,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1667" t="inlineStr"/>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
@@ -58444,7 +58497,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1668" t="inlineStr"/>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
@@ -58473,7 +58525,6 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1669" t="inlineStr"/>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
@@ -58502,7 +58553,6 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1670" t="inlineStr"/>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
@@ -58531,7 +58581,6 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1671" t="inlineStr"/>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
@@ -58560,7 +58609,6 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1672" t="inlineStr"/>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
@@ -58589,7 +58637,6 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1673" t="inlineStr"/>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
@@ -58618,7 +58665,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1674" t="inlineStr"/>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
@@ -58647,7 +58693,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1675" t="inlineStr"/>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
@@ -58676,7 +58721,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1676" t="inlineStr"/>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
@@ -58705,7 +58749,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1677" t="inlineStr"/>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
@@ -58734,7 +58777,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1678" t="inlineStr"/>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
@@ -58763,7 +58805,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1679" t="inlineStr"/>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
@@ -58792,7 +58833,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1680" t="inlineStr"/>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
@@ -58821,7 +58861,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1681" t="inlineStr"/>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
@@ -58850,7 +58889,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1682" t="inlineStr"/>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
@@ -58879,7 +58917,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1683" t="inlineStr"/>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
@@ -58908,7 +58945,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1684" t="inlineStr"/>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
@@ -58937,7 +58973,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1685" t="inlineStr"/>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
@@ -58966,7 +59001,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1686" t="inlineStr"/>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
@@ -58995,7 +59029,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1687" t="inlineStr"/>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
@@ -59024,7 +59057,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1688" t="inlineStr"/>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
@@ -59053,7 +59085,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1689" t="inlineStr"/>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
@@ -59082,7 +59113,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1690" t="inlineStr"/>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
@@ -59111,7 +59141,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1691" t="inlineStr"/>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
@@ -59140,7 +59169,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1692" t="inlineStr"/>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
@@ -59169,7 +59197,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1693" t="inlineStr"/>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
@@ -59198,7 +59225,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1694" t="inlineStr"/>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
@@ -59227,7 +59253,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1695" t="inlineStr"/>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
@@ -59256,7 +59281,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1696" t="inlineStr"/>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
@@ -59285,7 +59309,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1697" t="inlineStr"/>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
@@ -59314,7 +59337,6 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1698" t="inlineStr"/>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
@@ -59343,7 +59365,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1699" t="inlineStr"/>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
@@ -59372,7 +59393,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1700" t="inlineStr"/>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
@@ -59401,7 +59421,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1701" t="inlineStr"/>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
@@ -59430,7 +59449,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1702" t="inlineStr"/>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
@@ -59459,7 +59477,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1703" t="inlineStr"/>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
@@ -59488,7 +59505,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1704" t="inlineStr"/>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
@@ -59517,7 +59533,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1705" t="inlineStr"/>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
@@ -59546,7 +59561,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1706" t="inlineStr"/>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
@@ -59575,7 +59589,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1707" t="inlineStr"/>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
@@ -59604,7 +59617,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1708" t="inlineStr"/>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
@@ -59633,7 +59645,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1709" t="inlineStr"/>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
@@ -59662,7 +59673,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1710" t="inlineStr"/>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
@@ -59691,7 +59701,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1711" t="inlineStr"/>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
@@ -59720,7 +59729,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1712" t="inlineStr"/>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
@@ -59749,7 +59757,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1713" t="inlineStr"/>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
@@ -59778,7 +59785,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1714" t="inlineStr"/>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
@@ -59807,7 +59813,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1715" t="inlineStr"/>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
@@ -59836,7 +59841,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1716" t="inlineStr"/>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
@@ -59865,7 +59869,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1717" t="inlineStr"/>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
@@ -59894,7 +59897,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1718" t="inlineStr"/>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
@@ -59923,7 +59925,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1719" t="inlineStr"/>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
@@ -59952,7 +59953,6 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1720" t="inlineStr"/>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
@@ -60169,13 +60169,11 @@
       <c r="D1727" t="n">
         <v>3</v>
       </c>
-      <c r="E1727" t="inlineStr"/>
       <c r="F1727" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1727" t="inlineStr"/>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
@@ -60194,13 +60192,11 @@
       <c r="D1728" t="n">
         <v>3</v>
       </c>
-      <c r="E1728" t="inlineStr"/>
       <c r="F1728" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1728" t="inlineStr"/>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
@@ -60219,13 +60215,11 @@
       <c r="D1729" t="n">
         <v>3</v>
       </c>
-      <c r="E1729" t="inlineStr"/>
       <c r="F1729" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1729" t="inlineStr"/>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
@@ -60244,13 +60238,11 @@
       <c r="D1730" t="n">
         <v>3</v>
       </c>
-      <c r="E1730" t="inlineStr"/>
       <c r="F1730" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1730" t="inlineStr"/>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
@@ -60269,13 +60261,11 @@
       <c r="D1731" t="n">
         <v>3</v>
       </c>
-      <c r="E1731" t="inlineStr"/>
       <c r="F1731" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1731" t="inlineStr"/>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
@@ -60294,13 +60284,11 @@
       <c r="D1732" t="n">
         <v>3</v>
       </c>
-      <c r="E1732" t="inlineStr"/>
       <c r="F1732" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1732" t="inlineStr"/>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
@@ -60319,13 +60307,11 @@
       <c r="D1733" t="n">
         <v>3</v>
       </c>
-      <c r="E1733" t="inlineStr"/>
       <c r="F1733" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1733" t="inlineStr"/>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
@@ -60344,13 +60330,11 @@
       <c r="D1734" t="n">
         <v>3</v>
       </c>
-      <c r="E1734" t="inlineStr"/>
       <c r="F1734" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1734" t="inlineStr"/>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
@@ -60369,13 +60353,11 @@
       <c r="D1735" t="n">
         <v>3</v>
       </c>
-      <c r="E1735" t="inlineStr"/>
       <c r="F1735" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1735" t="inlineStr"/>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
@@ -60394,7 +60376,6 @@
       <c r="D1736" t="n">
         <v>3</v>
       </c>
-      <c r="E1736" t="inlineStr"/>
       <c r="F1736" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
@@ -60423,7 +60404,6 @@
       <c r="D1737" t="n">
         <v>3</v>
       </c>
-      <c r="E1737" t="inlineStr"/>
       <c r="F1737" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
@@ -60452,7 +60432,6 @@
       <c r="D1738" t="n">
         <v>3</v>
       </c>
-      <c r="E1738" t="inlineStr"/>
       <c r="F1738" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
@@ -60481,13 +60460,11 @@
       <c r="D1739" t="n">
         <v>0</v>
       </c>
-      <c r="E1739" t="inlineStr"/>
       <c r="F1739" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1739" t="inlineStr"/>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
@@ -60506,13 +60483,11 @@
       <c r="D1740" t="n">
         <v>0</v>
       </c>
-      <c r="E1740" t="inlineStr"/>
       <c r="F1740" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1740" t="inlineStr"/>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">
@@ -60531,13 +60506,11 @@
       <c r="D1741" t="n">
         <v>0</v>
       </c>
-      <c r="E1741" t="inlineStr"/>
       <c r="F1741" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1741" t="inlineStr"/>
     </row>
     <row r="1742">
       <c r="A1742" t="inlineStr">
@@ -60556,13 +60529,11 @@
       <c r="D1742" t="n">
         <v>0</v>
       </c>
-      <c r="E1742" t="inlineStr"/>
       <c r="F1742" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1742" t="inlineStr"/>
     </row>
     <row r="1743">
       <c r="A1743" t="inlineStr">
@@ -60581,13 +60552,11 @@
       <c r="D1743" t="n">
         <v>0</v>
       </c>
-      <c r="E1743" t="inlineStr"/>
       <c r="F1743" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1743" t="inlineStr"/>
     </row>
     <row r="1744">
       <c r="A1744" t="inlineStr">
@@ -60606,13 +60575,11 @@
       <c r="D1744" t="n">
         <v>0</v>
       </c>
-      <c r="E1744" t="inlineStr"/>
       <c r="F1744" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1744" t="inlineStr"/>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
@@ -60631,13 +60598,11 @@
       <c r="D1745" t="n">
         <v>0</v>
       </c>
-      <c r="E1745" t="inlineStr"/>
       <c r="F1745" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1745" t="inlineStr"/>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
@@ -60656,13 +60621,11 @@
       <c r="D1746" t="n">
         <v>0</v>
       </c>
-      <c r="E1746" t="inlineStr"/>
       <c r="F1746" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1746" t="inlineStr"/>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
@@ -60681,13 +60644,11 @@
       <c r="D1747" t="n">
         <v>0</v>
       </c>
-      <c r="E1747" t="inlineStr"/>
       <c r="F1747" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1747" t="inlineStr"/>
     </row>
     <row r="1748">
       <c r="A1748" t="inlineStr">
@@ -60706,13 +60667,11 @@
       <c r="D1748" t="n">
         <v>0</v>
       </c>
-      <c r="E1748" t="inlineStr"/>
       <c r="F1748" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1748" t="inlineStr"/>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
@@ -60731,13 +60690,11 @@
       <c r="D1749" t="n">
         <v>0</v>
       </c>
-      <c r="E1749" t="inlineStr"/>
       <c r="F1749" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1749" t="inlineStr"/>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
@@ -60756,13 +60713,11 @@
       <c r="D1750" t="n">
         <v>0</v>
       </c>
-      <c r="E1750" t="inlineStr"/>
       <c r="F1750" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1750" t="inlineStr"/>
     </row>
     <row r="1751">
       <c r="A1751" t="inlineStr">
@@ -60781,13 +60736,11 @@
       <c r="D1751" t="n">
         <v>0</v>
       </c>
-      <c r="E1751" t="inlineStr"/>
       <c r="F1751" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1751" t="inlineStr"/>
     </row>
     <row r="1752">
       <c r="A1752" t="inlineStr">
@@ -60806,13 +60759,11 @@
       <c r="D1752" t="n">
         <v>0</v>
       </c>
-      <c r="E1752" t="inlineStr"/>
       <c r="F1752" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1752" t="inlineStr"/>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
@@ -60831,13 +60782,11 @@
       <c r="D1753" t="n">
         <v>0</v>
       </c>
-      <c r="E1753" t="inlineStr"/>
       <c r="F1753" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1753" t="inlineStr"/>
     </row>
     <row r="1754">
       <c r="A1754" t="inlineStr">
@@ -60856,13 +60805,11 @@
       <c r="D1754" t="n">
         <v>0</v>
       </c>
-      <c r="E1754" t="inlineStr"/>
       <c r="F1754" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1754" t="inlineStr"/>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
@@ -60881,13 +60828,11 @@
       <c r="D1755" t="n">
         <v>0</v>
       </c>
-      <c r="E1755" t="inlineStr"/>
       <c r="F1755" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1755" t="inlineStr"/>
     </row>
     <row r="1756">
       <c r="A1756" t="inlineStr">
@@ -60906,13 +60851,11 @@
       <c r="D1756" t="n">
         <v>0</v>
       </c>
-      <c r="E1756" t="inlineStr"/>
       <c r="F1756" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1756" t="inlineStr"/>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
@@ -60931,13 +60874,11 @@
       <c r="D1757" t="n">
         <v>0</v>
       </c>
-      <c r="E1757" t="inlineStr"/>
       <c r="F1757" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1757" t="inlineStr"/>
     </row>
     <row r="1758">
       <c r="A1758" t="inlineStr">
@@ -60956,13 +60897,11 @@
       <c r="D1758" t="n">
         <v>0</v>
       </c>
-      <c r="E1758" t="inlineStr"/>
       <c r="F1758" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1758" t="inlineStr"/>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
@@ -60981,13 +60920,11 @@
       <c r="D1759" t="n">
         <v>0</v>
       </c>
-      <c r="E1759" t="inlineStr"/>
       <c r="F1759" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1759" t="inlineStr"/>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
@@ -61006,13 +60943,11 @@
       <c r="D1760" t="n">
         <v>0</v>
       </c>
-      <c r="E1760" t="inlineStr"/>
       <c r="F1760" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1760" t="inlineStr"/>
     </row>
     <row r="1761">
       <c r="A1761" t="inlineStr">
@@ -61031,13 +60966,11 @@
       <c r="D1761" t="n">
         <v>0</v>
       </c>
-      <c r="E1761" t="inlineStr"/>
       <c r="F1761" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1761" t="inlineStr"/>
     </row>
     <row r="1762">
       <c r="A1762" t="inlineStr">
@@ -61056,13 +60989,11 @@
       <c r="D1762" t="n">
         <v>0</v>
       </c>
-      <c r="E1762" t="inlineStr"/>
       <c r="F1762" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1762" t="inlineStr"/>
     </row>
     <row r="1763">
       <c r="A1763" t="inlineStr">
@@ -61081,13 +61012,11 @@
       <c r="D1763" t="n">
         <v>0</v>
       </c>
-      <c r="E1763" t="inlineStr"/>
       <c r="F1763" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1763" t="inlineStr"/>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
@@ -61106,13 +61035,11 @@
       <c r="D1764" t="n">
         <v>0</v>
       </c>
-      <c r="E1764" t="inlineStr"/>
       <c r="F1764" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1764" t="inlineStr"/>
     </row>
     <row r="1765">
       <c r="A1765" t="inlineStr">
@@ -61131,13 +61058,11 @@
       <c r="D1765" t="n">
         <v>0</v>
       </c>
-      <c r="E1765" t="inlineStr"/>
       <c r="F1765" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1765" t="inlineStr"/>
     </row>
     <row r="1766">
       <c r="A1766" t="inlineStr">
@@ -61156,13 +61081,11 @@
       <c r="D1766" t="n">
         <v>0</v>
       </c>
-      <c r="E1766" t="inlineStr"/>
       <c r="F1766" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1766" t="inlineStr"/>
     </row>
     <row r="1767">
       <c r="A1767" t="inlineStr">
@@ -61181,13 +61104,11 @@
       <c r="D1767" t="n">
         <v>0</v>
       </c>
-      <c r="E1767" t="inlineStr"/>
       <c r="F1767" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1767" t="inlineStr"/>
     </row>
     <row r="1768">
       <c r="A1768" t="inlineStr">
@@ -61206,13 +61127,11 @@
       <c r="D1768" t="n">
         <v>0</v>
       </c>
-      <c r="E1768" t="inlineStr"/>
       <c r="F1768" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1768" t="inlineStr"/>
     </row>
     <row r="1769">
       <c r="A1769" t="inlineStr">
@@ -61231,13 +61150,11 @@
       <c r="D1769" t="n">
         <v>0</v>
       </c>
-      <c r="E1769" t="inlineStr"/>
       <c r="F1769" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1769" t="inlineStr"/>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
@@ -61256,13 +61173,11 @@
       <c r="D1770" t="n">
         <v>0</v>
       </c>
-      <c r="E1770" t="inlineStr"/>
       <c r="F1770" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1770" t="inlineStr"/>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
@@ -61281,13 +61196,11 @@
       <c r="D1771" t="n">
         <v>0</v>
       </c>
-      <c r="E1771" t="inlineStr"/>
       <c r="F1771" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1771" t="inlineStr"/>
     </row>
     <row r="1772">
       <c r="A1772" t="inlineStr">
@@ -61306,13 +61219,11 @@
       <c r="D1772" t="n">
         <v>0</v>
       </c>
-      <c r="E1772" t="inlineStr"/>
       <c r="F1772" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1772" t="inlineStr"/>
     </row>
     <row r="1773">
       <c r="A1773" t="inlineStr">
@@ -61331,13 +61242,11 @@
       <c r="D1773" t="n">
         <v>0</v>
       </c>
-      <c r="E1773" t="inlineStr"/>
       <c r="F1773" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1773" t="inlineStr"/>
     </row>
     <row r="1774">
       <c r="A1774" t="inlineStr">
@@ -61356,13 +61265,11 @@
       <c r="D1774" t="n">
         <v>0</v>
       </c>
-      <c r="E1774" t="inlineStr"/>
       <c r="F1774" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1774" t="inlineStr"/>
     </row>
     <row r="1775">
       <c r="A1775" t="inlineStr">
@@ -61381,13 +61288,11 @@
       <c r="D1775" t="n">
         <v>0</v>
       </c>
-      <c r="E1775" t="inlineStr"/>
       <c r="F1775" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1775" t="inlineStr"/>
     </row>
     <row r="1776">
       <c r="A1776" t="inlineStr">
@@ -61406,13 +61311,11 @@
       <c r="D1776" t="n">
         <v>0</v>
       </c>
-      <c r="E1776" t="inlineStr"/>
       <c r="F1776" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1776" t="inlineStr"/>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
@@ -61431,13 +61334,11 @@
       <c r="D1777" t="n">
         <v>0</v>
       </c>
-      <c r="E1777" t="inlineStr"/>
       <c r="F1777" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1777" t="inlineStr"/>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
@@ -61456,13 +61357,11 @@
       <c r="D1778" t="n">
         <v>0</v>
       </c>
-      <c r="E1778" t="inlineStr"/>
       <c r="F1778" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1778" t="inlineStr"/>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
@@ -61481,13 +61380,11 @@
       <c r="D1779" t="n">
         <v>0</v>
       </c>
-      <c r="E1779" t="inlineStr"/>
       <c r="F1779" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1779" t="inlineStr"/>
     </row>
     <row r="1780">
       <c r="A1780" t="inlineStr">
@@ -61506,13 +61403,11 @@
       <c r="D1780" t="n">
         <v>0</v>
       </c>
-      <c r="E1780" t="inlineStr"/>
       <c r="F1780" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1780" t="inlineStr"/>
     </row>
     <row r="1781">
       <c r="A1781" t="inlineStr">
@@ -61531,13 +61426,11 @@
       <c r="D1781" t="n">
         <v>0</v>
       </c>
-      <c r="E1781" t="inlineStr"/>
       <c r="F1781" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1781" t="inlineStr"/>
     </row>
     <row r="1782">
       <c r="A1782" t="inlineStr">
@@ -61556,13 +61449,11 @@
       <c r="D1782" t="n">
         <v>0</v>
       </c>
-      <c r="E1782" t="inlineStr"/>
       <c r="F1782" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1782" t="inlineStr"/>
     </row>
     <row r="1783">
       <c r="A1783" t="inlineStr">
@@ -61581,13 +61472,11 @@
       <c r="D1783" t="n">
         <v>0</v>
       </c>
-      <c r="E1783" t="inlineStr"/>
       <c r="F1783" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1783" t="inlineStr"/>
     </row>
     <row r="1784">
       <c r="A1784" t="inlineStr">
@@ -61606,13 +61495,11 @@
       <c r="D1784" t="n">
         <v>0</v>
       </c>
-      <c r="E1784" t="inlineStr"/>
       <c r="F1784" t="inlineStr">
         <is>
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1784" t="inlineStr"/>
     </row>
     <row r="1785">
       <c r="A1785" t="inlineStr">
@@ -61631,13 +61518,11 @@
       <c r="D1785" t="n">
         <v>0</v>
       </c>
-      <c r="E1785" t="inlineStr"/>
       <c r="F1785" t="inlineStr">
         <is>
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1785" t="inlineStr"/>
     </row>
     <row r="1786">
       <c r="A1786" t="inlineStr">
@@ -61656,13 +61541,11 @@
       <c r="D1786" t="n">
         <v>0</v>
       </c>
-      <c r="E1786" t="inlineStr"/>
       <c r="F1786" t="inlineStr">
         <is>
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1786" t="inlineStr"/>
     </row>
     <row r="1787">
       <c r="A1787" t="inlineStr">
@@ -61681,13 +61564,11 @@
       <c r="D1787" t="n">
         <v>0</v>
       </c>
-      <c r="E1787" t="inlineStr"/>
       <c r="F1787" t="inlineStr">
         <is>
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
-      <c r="G1787" t="inlineStr"/>
     </row>
     <row r="1788">
       <c r="A1788" t="inlineStr">
@@ -61706,13 +61587,11 @@
       <c r="D1788" t="n">
         <v>-1</v>
       </c>
-      <c r="E1788" t="inlineStr"/>
       <c r="F1788" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1788" t="inlineStr"/>
     </row>
     <row r="1789">
       <c r="A1789" t="inlineStr">
@@ -61731,13 +61610,11 @@
       <c r="D1789" t="n">
         <v>-1</v>
       </c>
-      <c r="E1789" t="inlineStr"/>
       <c r="F1789" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1789" t="inlineStr"/>
     </row>
     <row r="1790">
       <c r="A1790" t="inlineStr">
@@ -61756,13 +61633,11 @@
       <c r="D1790" t="n">
         <v>-1</v>
       </c>
-      <c r="E1790" t="inlineStr"/>
       <c r="F1790" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1790" t="inlineStr"/>
     </row>
     <row r="1791">
       <c r="A1791" t="inlineStr">
@@ -61781,13 +61656,11 @@
       <c r="D1791" t="n">
         <v>-1</v>
       </c>
-      <c r="E1791" t="inlineStr"/>
       <c r="F1791" t="inlineStr">
         <is>
           <t>github:nherx/free-llm-api-resources</t>
         </is>
       </c>
-      <c r="G1791" t="inlineStr"/>
     </row>
     <row r="1792">
       <c r="A1792" t="inlineStr">
@@ -61806,13 +61679,11 @@
       <c r="D1792" t="n">
         <v>-2</v>
       </c>
-      <c r="E1792" t="inlineStr"/>
       <c r="F1792" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1792" t="inlineStr"/>
     </row>
     <row r="1793">
       <c r="A1793" t="inlineStr">
@@ -61831,13 +61702,11 @@
       <c r="D1793" t="n">
         <v>-2</v>
       </c>
-      <c r="E1793" t="inlineStr"/>
       <c r="F1793" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1793" t="inlineStr"/>
     </row>
     <row r="1794">
       <c r="A1794" t="inlineStr">
@@ -61856,13 +61725,11 @@
       <c r="D1794" t="n">
         <v>-2</v>
       </c>
-      <c r="E1794" t="inlineStr"/>
       <c r="F1794" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1794" t="inlineStr"/>
     </row>
     <row r="1795">
       <c r="A1795" t="inlineStr">
@@ -61881,13 +61748,11 @@
       <c r="D1795" t="n">
         <v>-2</v>
       </c>
-      <c r="E1795" t="inlineStr"/>
       <c r="F1795" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1795" t="inlineStr"/>
     </row>
     <row r="1796">
       <c r="A1796" t="inlineStr">
@@ -61906,13 +61771,11 @@
       <c r="D1796" t="n">
         <v>-2</v>
       </c>
-      <c r="E1796" t="inlineStr"/>
       <c r="F1796" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1796" t="inlineStr"/>
     </row>
     <row r="1797">
       <c r="A1797" t="inlineStr">
@@ -61931,13 +61794,11 @@
       <c r="D1797" t="n">
         <v>-2</v>
       </c>
-      <c r="E1797" t="inlineStr"/>
       <c r="F1797" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1797" t="inlineStr"/>
     </row>
     <row r="1798">
       <c r="A1798" t="inlineStr">
@@ -61956,13 +61817,11 @@
       <c r="D1798" t="n">
         <v>-2</v>
       </c>
-      <c r="E1798" t="inlineStr"/>
       <c r="F1798" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1798" t="inlineStr"/>
     </row>
     <row r="1799">
       <c r="A1799" t="inlineStr">
@@ -61981,13 +61840,11 @@
       <c r="D1799" t="n">
         <v>-2</v>
       </c>
-      <c r="E1799" t="inlineStr"/>
       <c r="F1799" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1799" t="inlineStr"/>
     </row>
     <row r="1800">
       <c r="A1800" t="inlineStr">
@@ -62006,13 +61863,11 @@
       <c r="D1800" t="n">
         <v>-2</v>
       </c>
-      <c r="E1800" t="inlineStr"/>
       <c r="F1800" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1800" t="inlineStr"/>
     </row>
     <row r="1801">
       <c r="A1801" t="inlineStr">
@@ -62031,13 +61886,11 @@
       <c r="D1801" t="n">
         <v>-2</v>
       </c>
-      <c r="E1801" t="inlineStr"/>
       <c r="F1801" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1801" t="inlineStr"/>
     </row>
     <row r="1802">
       <c r="A1802" t="inlineStr">
@@ -62056,13 +61909,11 @@
       <c r="D1802" t="n">
         <v>-2</v>
       </c>
-      <c r="E1802" t="inlineStr"/>
       <c r="F1802" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1802" t="inlineStr"/>
     </row>
     <row r="1803">
       <c r="A1803" t="inlineStr">
@@ -62081,13 +61932,11 @@
       <c r="D1803" t="n">
         <v>-2</v>
       </c>
-      <c r="E1803" t="inlineStr"/>
       <c r="F1803" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1803" t="inlineStr"/>
     </row>
     <row r="1804">
       <c r="A1804" t="inlineStr">
@@ -62106,13 +61955,11 @@
       <c r="D1804" t="n">
         <v>-2</v>
       </c>
-      <c r="E1804" t="inlineStr"/>
       <c r="F1804" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1804" t="inlineStr"/>
     </row>
     <row r="1805">
       <c r="A1805" t="inlineStr">
@@ -62131,13 +61978,11 @@
       <c r="D1805" t="n">
         <v>-2</v>
       </c>
-      <c r="E1805" t="inlineStr"/>
       <c r="F1805" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1805" t="inlineStr"/>
     </row>
     <row r="1806">
       <c r="A1806" t="inlineStr">
@@ -62156,13 +62001,11 @@
       <c r="D1806" t="n">
         <v>-2</v>
       </c>
-      <c r="E1806" t="inlineStr"/>
       <c r="F1806" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
-      <c r="G1806" t="inlineStr"/>
     </row>
     <row r="1807">
       <c r="A1807" t="inlineStr">
@@ -62181,13 +62024,11 @@
       <c r="D1807" t="n">
         <v>-2</v>
       </c>
-      <c r="E1807" t="inlineStr"/>
       <c r="F1807" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1807" t="inlineStr"/>
     </row>
     <row r="1808">
       <c r="A1808" t="inlineStr">
@@ -62206,13 +62047,11 @@
       <c r="D1808" t="n">
         <v>-2</v>
       </c>
-      <c r="E1808" t="inlineStr"/>
       <c r="F1808" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1808" t="inlineStr"/>
     </row>
     <row r="1809">
       <c r="A1809" t="inlineStr">
@@ -62231,13 +62070,11 @@
       <c r="D1809" t="n">
         <v>-2</v>
       </c>
-      <c r="E1809" t="inlineStr"/>
       <c r="F1809" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1809" t="inlineStr"/>
     </row>
     <row r="1810">
       <c r="A1810" t="inlineStr">
@@ -62256,13 +62093,11 @@
       <c r="D1810" t="n">
         <v>-2</v>
       </c>
-      <c r="E1810" t="inlineStr"/>
       <c r="F1810" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1810" t="inlineStr"/>
     </row>
     <row r="1811">
       <c r="A1811" t="inlineStr">
@@ -62281,13 +62116,11 @@
       <c r="D1811" t="n">
         <v>-2</v>
       </c>
-      <c r="E1811" t="inlineStr"/>
       <c r="F1811" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1811" t="inlineStr"/>
     </row>
     <row r="1812">
       <c r="A1812" t="inlineStr">
@@ -62306,13 +62139,11 @@
       <c r="D1812" t="n">
         <v>-2</v>
       </c>
-      <c r="E1812" t="inlineStr"/>
       <c r="F1812" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1812" t="inlineStr"/>
     </row>
     <row r="1813">
       <c r="A1813" t="inlineStr">
@@ -62331,13 +62162,11 @@
       <c r="D1813" t="n">
         <v>-2</v>
       </c>
-      <c r="E1813" t="inlineStr"/>
       <c r="F1813" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1813" t="inlineStr"/>
     </row>
     <row r="1814">
       <c r="A1814" t="inlineStr">
@@ -62356,13 +62185,11 @@
       <c r="D1814" t="n">
         <v>-2</v>
       </c>
-      <c r="E1814" t="inlineStr"/>
       <c r="F1814" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1814" t="inlineStr"/>
     </row>
     <row r="1815">
       <c r="A1815" t="inlineStr">
@@ -62381,13 +62208,11 @@
       <c r="D1815" t="n">
         <v>-2</v>
       </c>
-      <c r="E1815" t="inlineStr"/>
       <c r="F1815" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1815" t="inlineStr"/>
     </row>
     <row r="1816">
       <c r="A1816" t="inlineStr">
@@ -62406,13 +62231,11 @@
       <c r="D1816" t="n">
         <v>-2</v>
       </c>
-      <c r="E1816" t="inlineStr"/>
       <c r="F1816" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1816" t="inlineStr"/>
     </row>
     <row r="1817">
       <c r="A1817" t="inlineStr">
@@ -62431,13 +62254,11 @@
       <c r="D1817" t="n">
         <v>-2</v>
       </c>
-      <c r="E1817" t="inlineStr"/>
       <c r="F1817" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1817" t="inlineStr"/>
     </row>
     <row r="1818">
       <c r="A1818" t="inlineStr">
@@ -62456,13 +62277,11 @@
       <c r="D1818" t="n">
         <v>-2</v>
       </c>
-      <c r="E1818" t="inlineStr"/>
       <c r="F1818" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1818" t="inlineStr"/>
     </row>
     <row r="1819">
       <c r="A1819" t="inlineStr">
@@ -62481,13 +62300,11 @@
       <c r="D1819" t="n">
         <v>-2</v>
       </c>
-      <c r="E1819" t="inlineStr"/>
       <c r="F1819" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1819" t="inlineStr"/>
     </row>
     <row r="1820">
       <c r="A1820" t="inlineStr">
@@ -62506,13 +62323,11 @@
       <c r="D1820" t="n">
         <v>-2</v>
       </c>
-      <c r="E1820" t="inlineStr"/>
       <c r="F1820" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1820" t="inlineStr"/>
     </row>
     <row r="1821">
       <c r="A1821" t="inlineStr">
@@ -62531,13 +62346,11 @@
       <c r="D1821" t="n">
         <v>-2</v>
       </c>
-      <c r="E1821" t="inlineStr"/>
       <c r="F1821" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1821" t="inlineStr"/>
     </row>
     <row r="1822">
       <c r="A1822" t="inlineStr">
@@ -62556,13 +62369,11 @@
       <c r="D1822" t="n">
         <v>-2</v>
       </c>
-      <c r="E1822" t="inlineStr"/>
       <c r="F1822" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1822" t="inlineStr"/>
     </row>
     <row r="1823">
       <c r="A1823" t="inlineStr">
@@ -62581,13 +62392,11 @@
       <c r="D1823" t="n">
         <v>-2</v>
       </c>
-      <c r="E1823" t="inlineStr"/>
       <c r="F1823" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1823" t="inlineStr"/>
     </row>
     <row r="1824">
       <c r="A1824" t="inlineStr">
@@ -62606,13 +62415,11 @@
       <c r="D1824" t="n">
         <v>-2</v>
       </c>
-      <c r="E1824" t="inlineStr"/>
       <c r="F1824" t="inlineStr">
         <is>
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
-      <c r="G1824" t="inlineStr"/>
     </row>
     <row r="1825">
       <c r="A1825" t="inlineStr">
@@ -62631,13 +62438,11 @@
       <c r="D1825" t="n">
         <v>-2</v>
       </c>
-      <c r="E1825" t="inlineStr"/>
       <c r="F1825" t="inlineStr">
         <is>
           <t>github:KhaiTrang1995/agentic-awesome-kit</t>
         </is>
       </c>
-      <c r="G1825" t="inlineStr"/>
     </row>
     <row r="1826">
       <c r="A1826" t="inlineStr">
@@ -62656,13 +62461,11 @@
       <c r="D1826" t="n">
         <v>-2</v>
       </c>
-      <c r="E1826" t="inlineStr"/>
       <c r="F1826" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1826" t="inlineStr"/>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
@@ -62681,13 +62484,11 @@
       <c r="D1827" t="n">
         <v>-2</v>
       </c>
-      <c r="E1827" t="inlineStr"/>
       <c r="F1827" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1827" t="inlineStr"/>
     </row>
     <row r="1828">
       <c r="A1828" t="inlineStr">
@@ -62706,13 +62507,11 @@
       <c r="D1828" t="n">
         <v>-2</v>
       </c>
-      <c r="E1828" t="inlineStr"/>
       <c r="F1828" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1828" t="inlineStr"/>
     </row>
     <row r="1829">
       <c r="A1829" t="inlineStr">
@@ -62731,13 +62530,11 @@
       <c r="D1829" t="n">
         <v>-2</v>
       </c>
-      <c r="E1829" t="inlineStr"/>
       <c r="F1829" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1829" t="inlineStr"/>
     </row>
     <row r="1830">
       <c r="A1830" t="inlineStr">
@@ -62756,13 +62553,11 @@
       <c r="D1830" t="n">
         <v>-2</v>
       </c>
-      <c r="E1830" t="inlineStr"/>
       <c r="F1830" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1830" t="inlineStr"/>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
@@ -62781,13 +62576,11 @@
       <c r="D1831" t="n">
         <v>-2</v>
       </c>
-      <c r="E1831" t="inlineStr"/>
       <c r="F1831" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1831" t="inlineStr"/>
     </row>
     <row r="1832">
       <c r="A1832" t="inlineStr">
@@ -62806,13 +62599,11 @@
       <c r="D1832" t="n">
         <v>-2</v>
       </c>
-      <c r="E1832" t="inlineStr"/>
       <c r="F1832" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1832" t="inlineStr"/>
     </row>
     <row r="1833">
       <c r="A1833" t="inlineStr">
@@ -62831,13 +62622,11 @@
       <c r="D1833" t="n">
         <v>-2</v>
       </c>
-      <c r="E1833" t="inlineStr"/>
       <c r="F1833" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1833" t="inlineStr"/>
     </row>
     <row r="1834">
       <c r="A1834" t="inlineStr">
@@ -62856,13 +62645,11 @@
       <c r="D1834" t="n">
         <v>-2</v>
       </c>
-      <c r="E1834" t="inlineStr"/>
       <c r="F1834" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1834" t="inlineStr"/>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
@@ -62881,13 +62668,11 @@
       <c r="D1835" t="n">
         <v>-2</v>
       </c>
-      <c r="E1835" t="inlineStr"/>
       <c r="F1835" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1835" t="inlineStr"/>
     </row>
     <row r="1836">
       <c r="A1836" t="inlineStr">
@@ -62906,13 +62691,11 @@
       <c r="D1836" t="n">
         <v>-2</v>
       </c>
-      <c r="E1836" t="inlineStr"/>
       <c r="F1836" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1836" t="inlineStr"/>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">
@@ -62931,13 +62714,11 @@
       <c r="D1837" t="n">
         <v>-2</v>
       </c>
-      <c r="E1837" t="inlineStr"/>
       <c r="F1837" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1837" t="inlineStr"/>
     </row>
     <row r="1838">
       <c r="A1838" t="inlineStr">
@@ -62956,13 +62737,11 @@
       <c r="D1838" t="n">
         <v>-2</v>
       </c>
-      <c r="E1838" t="inlineStr"/>
       <c r="F1838" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1838" t="inlineStr"/>
     </row>
     <row r="1839">
       <c r="A1839" t="inlineStr">
@@ -62981,13 +62760,11 @@
       <c r="D1839" t="n">
         <v>-2</v>
       </c>
-      <c r="E1839" t="inlineStr"/>
       <c r="F1839" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1839" t="inlineStr"/>
     </row>
     <row r="1840">
       <c r="A1840" t="inlineStr">
@@ -63006,13 +62783,11 @@
       <c r="D1840" t="n">
         <v>-2</v>
       </c>
-      <c r="E1840" t="inlineStr"/>
       <c r="F1840" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1840" t="inlineStr"/>
     </row>
     <row r="1841">
       <c r="A1841" t="inlineStr">
@@ -63031,13 +62806,11 @@
       <c r="D1841" t="n">
         <v>-2</v>
       </c>
-      <c r="E1841" t="inlineStr"/>
       <c r="F1841" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1841" t="inlineStr"/>
     </row>
     <row r="1842">
       <c r="A1842" t="inlineStr">
@@ -63056,13 +62829,11 @@
       <c r="D1842" t="n">
         <v>-2</v>
       </c>
-      <c r="E1842" t="inlineStr"/>
       <c r="F1842" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1842" t="inlineStr"/>
     </row>
     <row r="1843">
       <c r="A1843" t="inlineStr">
@@ -63081,13 +62852,11 @@
       <c r="D1843" t="n">
         <v>-2</v>
       </c>
-      <c r="E1843" t="inlineStr"/>
       <c r="F1843" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
-      <c r="G1843" t="inlineStr"/>
     </row>
     <row r="1844">
       <c r="A1844" t="inlineStr">
@@ -63106,13 +62875,11 @@
       <c r="D1844" t="n">
         <v>-2</v>
       </c>
-      <c r="E1844" t="inlineStr"/>
       <c r="F1844" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1844" t="inlineStr"/>
     </row>
     <row r="1845">
       <c r="A1845" t="inlineStr">
@@ -63131,13 +62898,11 @@
       <c r="D1845" t="n">
         <v>-2</v>
       </c>
-      <c r="E1845" t="inlineStr"/>
       <c r="F1845" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1845" t="inlineStr"/>
     </row>
     <row r="1846">
       <c r="A1846" t="inlineStr">
@@ -63156,13 +62921,11 @@
       <c r="D1846" t="n">
         <v>-2</v>
       </c>
-      <c r="E1846" t="inlineStr"/>
       <c r="F1846" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1846" t="inlineStr"/>
     </row>
     <row r="1847">
       <c r="A1847" t="inlineStr">
@@ -63181,13 +62944,11 @@
       <c r="D1847" t="n">
         <v>-2</v>
       </c>
-      <c r="E1847" t="inlineStr"/>
       <c r="F1847" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1847" t="inlineStr"/>
     </row>
     <row r="1848">
       <c r="A1848" t="inlineStr">
@@ -63206,13 +62967,11 @@
       <c r="D1848" t="n">
         <v>-2</v>
       </c>
-      <c r="E1848" t="inlineStr"/>
       <c r="F1848" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1848" t="inlineStr"/>
     </row>
     <row r="1849">
       <c r="A1849" t="inlineStr">
@@ -63231,13 +62990,11 @@
       <c r="D1849" t="n">
         <v>-2</v>
       </c>
-      <c r="E1849" t="inlineStr"/>
       <c r="F1849" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1849" t="inlineStr"/>
     </row>
     <row r="1850">
       <c r="A1850" t="inlineStr">
@@ -63256,13 +63013,11 @@
       <c r="D1850" t="n">
         <v>-2</v>
       </c>
-      <c r="E1850" t="inlineStr"/>
       <c r="F1850" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1850" t="inlineStr"/>
     </row>
     <row r="1851">
       <c r="A1851" t="inlineStr">
@@ -63281,13 +63036,11 @@
       <c r="D1851" t="n">
         <v>-2</v>
       </c>
-      <c r="E1851" t="inlineStr"/>
       <c r="F1851" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1851" t="inlineStr"/>
     </row>
     <row r="1852">
       <c r="A1852" t="inlineStr">
@@ -63306,13 +63059,11 @@
       <c r="D1852" t="n">
         <v>-2</v>
       </c>
-      <c r="E1852" t="inlineStr"/>
       <c r="F1852" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1852" t="inlineStr"/>
     </row>
     <row r="1853">
       <c r="A1853" t="inlineStr">
@@ -63331,13 +63082,11 @@
       <c r="D1853" t="n">
         <v>-2</v>
       </c>
-      <c r="E1853" t="inlineStr"/>
       <c r="F1853" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1853" t="inlineStr"/>
     </row>
     <row r="1854">
       <c r="A1854" t="inlineStr">
@@ -63356,13 +63105,11 @@
       <c r="D1854" t="n">
         <v>-2</v>
       </c>
-      <c r="E1854" t="inlineStr"/>
       <c r="F1854" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1854" t="inlineStr"/>
     </row>
     <row r="1855">
       <c r="A1855" t="inlineStr">
@@ -63381,13 +63128,11 @@
       <c r="D1855" t="n">
         <v>-2</v>
       </c>
-      <c r="E1855" t="inlineStr"/>
       <c r="F1855" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1855" t="inlineStr"/>
     </row>
     <row r="1856">
       <c r="A1856" t="inlineStr">
@@ -63406,13 +63151,11 @@
       <c r="D1856" t="n">
         <v>-2</v>
       </c>
-      <c r="E1856" t="inlineStr"/>
       <c r="F1856" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1856" t="inlineStr"/>
     </row>
     <row r="1857">
       <c r="A1857" t="inlineStr">
@@ -63431,13 +63174,11 @@
       <c r="D1857" t="n">
         <v>-2</v>
       </c>
-      <c r="E1857" t="inlineStr"/>
       <c r="F1857" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1857" t="inlineStr"/>
     </row>
     <row r="1858">
       <c r="A1858" t="inlineStr">
@@ -63456,13 +63197,11 @@
       <c r="D1858" t="n">
         <v>-2</v>
       </c>
-      <c r="E1858" t="inlineStr"/>
       <c r="F1858" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1858" t="inlineStr"/>
     </row>
     <row r="1859">
       <c r="A1859" t="inlineStr">
@@ -63481,13 +63220,11 @@
       <c r="D1859" t="n">
         <v>-2</v>
       </c>
-      <c r="E1859" t="inlineStr"/>
       <c r="F1859" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1859" t="inlineStr"/>
     </row>
     <row r="1860">
       <c r="A1860" t="inlineStr">
@@ -63506,13 +63243,11 @@
       <c r="D1860" t="n">
         <v>-2</v>
       </c>
-      <c r="E1860" t="inlineStr"/>
       <c r="F1860" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1860" t="inlineStr"/>
     </row>
     <row r="1861">
       <c r="A1861" t="inlineStr">
@@ -63531,13 +63266,11 @@
       <c r="D1861" t="n">
         <v>-2</v>
       </c>
-      <c r="E1861" t="inlineStr"/>
       <c r="F1861" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1861" t="inlineStr"/>
     </row>
     <row r="1862">
       <c r="A1862" t="inlineStr">
@@ -63556,13 +63289,11 @@
       <c r="D1862" t="n">
         <v>-2</v>
       </c>
-      <c r="E1862" t="inlineStr"/>
       <c r="F1862" t="inlineStr">
         <is>
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
-      <c r="G1862" t="inlineStr"/>
     </row>
     <row r="1863">
       <c r="A1863" t="inlineStr">
@@ -63581,13 +63312,11 @@
       <c r="D1863" t="n">
         <v>-2</v>
       </c>
-      <c r="E1863" t="inlineStr"/>
       <c r="F1863" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1863" t="inlineStr"/>
     </row>
     <row r="1864">
       <c r="A1864" t="inlineStr">
@@ -63606,13 +63335,11 @@
       <c r="D1864" t="n">
         <v>-2</v>
       </c>
-      <c r="E1864" t="inlineStr"/>
       <c r="F1864" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1864" t="inlineStr"/>
     </row>
     <row r="1865">
       <c r="A1865" t="inlineStr">
@@ -63631,13 +63358,11 @@
       <c r="D1865" t="n">
         <v>-2</v>
       </c>
-      <c r="E1865" t="inlineStr"/>
       <c r="F1865" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1865" t="inlineStr"/>
     </row>
     <row r="1866">
       <c r="A1866" t="inlineStr">
@@ -63656,13 +63381,11 @@
       <c r="D1866" t="n">
         <v>-2</v>
       </c>
-      <c r="E1866" t="inlineStr"/>
       <c r="F1866" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1866" t="inlineStr"/>
     </row>
     <row r="1867">
       <c r="A1867" t="inlineStr">
@@ -63681,13 +63404,11 @@
       <c r="D1867" t="n">
         <v>-2</v>
       </c>
-      <c r="E1867" t="inlineStr"/>
       <c r="F1867" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1867" t="inlineStr"/>
     </row>
     <row r="1868">
       <c r="A1868" t="inlineStr">
@@ -63706,13 +63427,11 @@
       <c r="D1868" t="n">
         <v>-2</v>
       </c>
-      <c r="E1868" t="inlineStr"/>
       <c r="F1868" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1868" t="inlineStr"/>
     </row>
     <row r="1869">
       <c r="A1869" t="inlineStr">
@@ -63731,13 +63450,11 @@
       <c r="D1869" t="n">
         <v>-2</v>
       </c>
-      <c r="E1869" t="inlineStr"/>
       <c r="F1869" t="inlineStr">
         <is>
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
-      <c r="G1869" t="inlineStr"/>
     </row>
     <row r="1870">
       <c r="A1870" t="inlineStr">
@@ -63756,13 +63473,11 @@
       <c r="D1870" t="n">
         <v>-2</v>
       </c>
-      <c r="E1870" t="inlineStr"/>
       <c r="F1870" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1870" t="inlineStr"/>
     </row>
     <row r="1871">
       <c r="A1871" t="inlineStr">
@@ -63781,13 +63496,11 @@
       <c r="D1871" t="n">
         <v>-2</v>
       </c>
-      <c r="E1871" t="inlineStr"/>
       <c r="F1871" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1871" t="inlineStr"/>
     </row>
     <row r="1872">
       <c r="A1872" t="inlineStr">
@@ -63806,13 +63519,11 @@
       <c r="D1872" t="n">
         <v>-2</v>
       </c>
-      <c r="E1872" t="inlineStr"/>
       <c r="F1872" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1872" t="inlineStr"/>
     </row>
     <row r="1873">
       <c r="A1873" t="inlineStr">
@@ -63831,13 +63542,11 @@
       <c r="D1873" t="n">
         <v>-2</v>
       </c>
-      <c r="E1873" t="inlineStr"/>
       <c r="F1873" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1873" t="inlineStr"/>
     </row>
     <row r="1874">
       <c r="A1874" t="inlineStr">
@@ -63856,13 +63565,11 @@
       <c r="D1874" t="n">
         <v>-2</v>
       </c>
-      <c r="E1874" t="inlineStr"/>
       <c r="F1874" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1874" t="inlineStr"/>
     </row>
     <row r="1875">
       <c r="A1875" t="inlineStr">
@@ -63881,13 +63588,11 @@
       <c r="D1875" t="n">
         <v>-2</v>
       </c>
-      <c r="E1875" t="inlineStr"/>
       <c r="F1875" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1875" t="inlineStr"/>
     </row>
     <row r="1876">
       <c r="A1876" t="inlineStr">
@@ -63906,13 +63611,11 @@
       <c r="D1876" t="n">
         <v>-2</v>
       </c>
-      <c r="E1876" t="inlineStr"/>
       <c r="F1876" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1876" t="inlineStr"/>
     </row>
     <row r="1877">
       <c r="A1877" t="inlineStr">
@@ -63931,13 +63634,11 @@
       <c r="D1877" t="n">
         <v>-2</v>
       </c>
-      <c r="E1877" t="inlineStr"/>
       <c r="F1877" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1877" t="inlineStr"/>
     </row>
     <row r="1878">
       <c r="A1878" t="inlineStr">
@@ -63956,13 +63657,11 @@
       <c r="D1878" t="n">
         <v>-2</v>
       </c>
-      <c r="E1878" t="inlineStr"/>
       <c r="F1878" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1878" t="inlineStr"/>
     </row>
     <row r="1879">
       <c r="A1879" t="inlineStr">
@@ -63981,13 +63680,11 @@
       <c r="D1879" t="n">
         <v>-2</v>
       </c>
-      <c r="E1879" t="inlineStr"/>
       <c r="F1879" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1879" t="inlineStr"/>
     </row>
     <row r="1880">
       <c r="A1880" t="inlineStr">
@@ -64006,13 +63703,11 @@
       <c r="D1880" t="n">
         <v>-2</v>
       </c>
-      <c r="E1880" t="inlineStr"/>
       <c r="F1880" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1880" t="inlineStr"/>
     </row>
     <row r="1881">
       <c r="A1881" t="inlineStr">
@@ -64031,13 +63726,11 @@
       <c r="D1881" t="n">
         <v>-2</v>
       </c>
-      <c r="E1881" t="inlineStr"/>
       <c r="F1881" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1881" t="inlineStr"/>
     </row>
     <row r="1882">
       <c r="A1882" t="inlineStr">
@@ -64056,13 +63749,11 @@
       <c r="D1882" t="n">
         <v>-2</v>
       </c>
-      <c r="E1882" t="inlineStr"/>
       <c r="F1882" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1882" t="inlineStr"/>
     </row>
     <row r="1883">
       <c r="A1883" t="inlineStr">
@@ -64081,13 +63772,11 @@
       <c r="D1883" t="n">
         <v>-2</v>
       </c>
-      <c r="E1883" t="inlineStr"/>
       <c r="F1883" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1883" t="inlineStr"/>
     </row>
     <row r="1884">
       <c r="A1884" t="inlineStr">
@@ -64106,13 +63795,11 @@
       <c r="D1884" t="n">
         <v>-2</v>
       </c>
-      <c r="E1884" t="inlineStr"/>
       <c r="F1884" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1884" t="inlineStr"/>
     </row>
     <row r="1885">
       <c r="A1885" t="inlineStr">
@@ -64131,13 +63818,11 @@
       <c r="D1885" t="n">
         <v>-2</v>
       </c>
-      <c r="E1885" t="inlineStr"/>
       <c r="F1885" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1885" t="inlineStr"/>
     </row>
     <row r="1886">
       <c r="A1886" t="inlineStr">
@@ -64156,13 +63841,11 @@
       <c r="D1886" t="n">
         <v>-2</v>
       </c>
-      <c r="E1886" t="inlineStr"/>
       <c r="F1886" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1886" t="inlineStr"/>
     </row>
     <row r="1887">
       <c r="A1887" t="inlineStr">
@@ -64181,13 +63864,11 @@
       <c r="D1887" t="n">
         <v>-2</v>
       </c>
-      <c r="E1887" t="inlineStr"/>
       <c r="F1887" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1887" t="inlineStr"/>
     </row>
     <row r="1888">
       <c r="A1888" t="inlineStr">
@@ -64206,13 +63887,11 @@
       <c r="D1888" t="n">
         <v>-2</v>
       </c>
-      <c r="E1888" t="inlineStr"/>
       <c r="F1888" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1888" t="inlineStr"/>
     </row>
     <row r="1889">
       <c r="A1889" t="inlineStr">
@@ -64231,13 +63910,11 @@
       <c r="D1889" t="n">
         <v>-2</v>
       </c>
-      <c r="E1889" t="inlineStr"/>
       <c r="F1889" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1889" t="inlineStr"/>
     </row>
     <row r="1890">
       <c r="A1890" t="inlineStr">
@@ -64256,13 +63933,11 @@
       <c r="D1890" t="n">
         <v>-2</v>
       </c>
-      <c r="E1890" t="inlineStr"/>
       <c r="F1890" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1890" t="inlineStr"/>
     </row>
     <row r="1891">
       <c r="A1891" t="inlineStr">
@@ -64281,13 +63956,11 @@
       <c r="D1891" t="n">
         <v>-2</v>
       </c>
-      <c r="E1891" t="inlineStr"/>
       <c r="F1891" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1891" t="inlineStr"/>
     </row>
     <row r="1892">
       <c r="A1892" t="inlineStr">
@@ -64306,13 +63979,11 @@
       <c r="D1892" t="n">
         <v>-2</v>
       </c>
-      <c r="E1892" t="inlineStr"/>
       <c r="F1892" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1892" t="inlineStr"/>
     </row>
     <row r="1893">
       <c r="A1893" t="inlineStr">
@@ -64331,13 +64002,11 @@
       <c r="D1893" t="n">
         <v>-2</v>
       </c>
-      <c r="E1893" t="inlineStr"/>
       <c r="F1893" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1893" t="inlineStr"/>
     </row>
     <row r="1894">
       <c r="A1894" t="inlineStr">
@@ -64356,13 +64025,11 @@
       <c r="D1894" t="n">
         <v>-2</v>
       </c>
-      <c r="E1894" t="inlineStr"/>
       <c r="F1894" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1894" t="inlineStr"/>
     </row>
     <row r="1895">
       <c r="A1895" t="inlineStr">
@@ -64381,13 +64048,11 @@
       <c r="D1895" t="n">
         <v>-2</v>
       </c>
-      <c r="E1895" t="inlineStr"/>
       <c r="F1895" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1895" t="inlineStr"/>
     </row>
     <row r="1896">
       <c r="A1896" t="inlineStr">
@@ -64406,13 +64071,11 @@
       <c r="D1896" t="n">
         <v>-2</v>
       </c>
-      <c r="E1896" t="inlineStr"/>
       <c r="F1896" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1896" t="inlineStr"/>
     </row>
     <row r="1897">
       <c r="A1897" t="inlineStr">
@@ -64431,13 +64094,11 @@
       <c r="D1897" t="n">
         <v>-2</v>
       </c>
-      <c r="E1897" t="inlineStr"/>
       <c r="F1897" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1897" t="inlineStr"/>
     </row>
     <row r="1898">
       <c r="A1898" t="inlineStr">
@@ -64456,13 +64117,11 @@
       <c r="D1898" t="n">
         <v>-2</v>
       </c>
-      <c r="E1898" t="inlineStr"/>
       <c r="F1898" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1898" t="inlineStr"/>
     </row>
     <row r="1899">
       <c r="A1899" t="inlineStr">
@@ -64481,13 +64140,11 @@
       <c r="D1899" t="n">
         <v>-2</v>
       </c>
-      <c r="E1899" t="inlineStr"/>
       <c r="F1899" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1899" t="inlineStr"/>
     </row>
     <row r="1900">
       <c r="A1900" t="inlineStr">
@@ -64506,13 +64163,11 @@
       <c r="D1900" t="n">
         <v>-2</v>
       </c>
-      <c r="E1900" t="inlineStr"/>
       <c r="F1900" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1900" t="inlineStr"/>
     </row>
     <row r="1901">
       <c r="A1901" t="inlineStr">
@@ -64531,13 +64186,11 @@
       <c r="D1901" t="n">
         <v>-2</v>
       </c>
-      <c r="E1901" t="inlineStr"/>
       <c r="F1901" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1901" t="inlineStr"/>
     </row>
     <row r="1902">
       <c r="A1902" t="inlineStr">
@@ -64556,13 +64209,11 @@
       <c r="D1902" t="n">
         <v>-2</v>
       </c>
-      <c r="E1902" t="inlineStr"/>
       <c r="F1902" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1902" t="inlineStr"/>
     </row>
     <row r="1903">
       <c r="A1903" t="inlineStr">
@@ -64581,13 +64232,11 @@
       <c r="D1903" t="n">
         <v>-2</v>
       </c>
-      <c r="E1903" t="inlineStr"/>
       <c r="F1903" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1903" t="inlineStr"/>
     </row>
     <row r="1904">
       <c r="A1904" t="inlineStr">
@@ -64606,13 +64255,11 @@
       <c r="D1904" t="n">
         <v>-2</v>
       </c>
-      <c r="E1904" t="inlineStr"/>
       <c r="F1904" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1904" t="inlineStr"/>
     </row>
     <row r="1905">
       <c r="A1905" t="inlineStr">
@@ -64631,13 +64278,11 @@
       <c r="D1905" t="n">
         <v>-2</v>
       </c>
-      <c r="E1905" t="inlineStr"/>
       <c r="F1905" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1905" t="inlineStr"/>
     </row>
     <row r="1906">
       <c r="A1906" t="inlineStr">
@@ -64656,13 +64301,11 @@
       <c r="D1906" t="n">
         <v>-2</v>
       </c>
-      <c r="E1906" t="inlineStr"/>
       <c r="F1906" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1906" t="inlineStr"/>
     </row>
     <row r="1907">
       <c r="A1907" t="inlineStr">
@@ -64681,13 +64324,11 @@
       <c r="D1907" t="n">
         <v>-2</v>
       </c>
-      <c r="E1907" t="inlineStr"/>
       <c r="F1907" t="inlineStr">
         <is>
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
-      <c r="G1907" t="inlineStr"/>
     </row>
     <row r="1908">
       <c r="A1908" t="inlineStr">
@@ -64706,13 +64347,11 @@
       <c r="D1908" t="n">
         <v>-2</v>
       </c>
-      <c r="E1908" t="inlineStr"/>
       <c r="F1908" t="inlineStr">
         <is>
           <t>github:nherx/free-llm-api-resources</t>
         </is>
       </c>
-      <c r="G1908" t="inlineStr"/>
     </row>
     <row r="1909">
       <c r="A1909" t="inlineStr">
@@ -64731,13 +64370,11 @@
       <c r="D1909" t="n">
         <v>-2</v>
       </c>
-      <c r="E1909" t="inlineStr"/>
       <c r="F1909" t="inlineStr">
         <is>
           <t>github:nherx/free-llm-api-resources</t>
         </is>
       </c>
-      <c r="G1909" t="inlineStr"/>
     </row>
     <row r="1910">
       <c r="A1910" t="inlineStr">
@@ -64756,13 +64393,11 @@
       <c r="D1910" t="n">
         <v>-2</v>
       </c>
-      <c r="E1910" t="inlineStr"/>
       <c r="F1910" t="inlineStr">
         <is>
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
-      <c r="G1910" t="inlineStr"/>
     </row>
     <row r="1911">
       <c r="A1911" t="inlineStr">
@@ -64781,13 +64416,11 @@
       <c r="D1911" t="n">
         <v>-2</v>
       </c>
-      <c r="E1911" t="inlineStr"/>
       <c r="F1911" t="inlineStr">
         <is>
           <t>https://developer.cloud.tencent.com/arti</t>
         </is>
       </c>
-      <c r="G1911" t="inlineStr"/>
     </row>
     <row r="1912">
       <c r="A1912" t="inlineStr">
@@ -64806,13 +64439,11 @@
       <c r="D1912" t="n">
         <v>-2</v>
       </c>
-      <c r="E1912" t="inlineStr"/>
       <c r="F1912" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1912" t="inlineStr"/>
     </row>
     <row r="1913">
       <c r="A1913" t="inlineStr">
@@ -64831,13 +64462,11 @@
       <c r="D1913" t="n">
         <v>-2</v>
       </c>
-      <c r="E1913" t="inlineStr"/>
       <c r="F1913" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1913" t="inlineStr"/>
     </row>
     <row r="1914">
       <c r="A1914" t="inlineStr">
@@ -64856,13 +64485,11 @@
       <c r="D1914" t="n">
         <v>-2</v>
       </c>
-      <c r="E1914" t="inlineStr"/>
       <c r="F1914" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1914" t="inlineStr"/>
     </row>
     <row r="1915">
       <c r="A1915" t="inlineStr">
@@ -64881,13 +64508,11 @@
       <c r="D1915" t="n">
         <v>-2</v>
       </c>
-      <c r="E1915" t="inlineStr"/>
       <c r="F1915" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1915" t="inlineStr"/>
     </row>
     <row r="1916">
       <c r="A1916" t="inlineStr">
@@ -64906,13 +64531,11 @@
       <c r="D1916" t="n">
         <v>-2</v>
       </c>
-      <c r="E1916" t="inlineStr"/>
       <c r="F1916" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1916" t="inlineStr"/>
     </row>
     <row r="1917">
       <c r="A1917" t="inlineStr">
@@ -64931,13 +64554,11 @@
       <c r="D1917" t="n">
         <v>-2</v>
       </c>
-      <c r="E1917" t="inlineStr"/>
       <c r="F1917" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1917" t="inlineStr"/>
     </row>
     <row r="1918">
       <c r="A1918" t="inlineStr">
@@ -64956,13 +64577,11 @@
       <c r="D1918" t="n">
         <v>-2</v>
       </c>
-      <c r="E1918" t="inlineStr"/>
       <c r="F1918" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1918" t="inlineStr"/>
     </row>
     <row r="1919">
       <c r="A1919" t="inlineStr">
@@ -64981,13 +64600,11 @@
       <c r="D1919" t="n">
         <v>-2</v>
       </c>
-      <c r="E1919" t="inlineStr"/>
       <c r="F1919" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1919" t="inlineStr"/>
     </row>
     <row r="1920">
       <c r="A1920" t="inlineStr">
@@ -65006,13 +64623,11 @@
       <c r="D1920" t="n">
         <v>-2</v>
       </c>
-      <c r="E1920" t="inlineStr"/>
       <c r="F1920" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1920" t="inlineStr"/>
     </row>
     <row r="1921">
       <c r="A1921" t="inlineStr">
@@ -65031,13 +64646,11 @@
       <c r="D1921" t="n">
         <v>-2</v>
       </c>
-      <c r="E1921" t="inlineStr"/>
       <c r="F1921" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1921" t="inlineStr"/>
     </row>
     <row r="1922">
       <c r="A1922" t="inlineStr">
@@ -65056,13 +64669,11 @@
       <c r="D1922" t="n">
         <v>-2</v>
       </c>
-      <c r="E1922" t="inlineStr"/>
       <c r="F1922" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1922" t="inlineStr"/>
     </row>
     <row r="1923">
       <c r="A1923" t="inlineStr">
@@ -65081,13 +64692,11 @@
       <c r="D1923" t="n">
         <v>-2</v>
       </c>
-      <c r="E1923" t="inlineStr"/>
       <c r="F1923" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1923" t="inlineStr"/>
     </row>
     <row r="1924">
       <c r="A1924" t="inlineStr">
@@ -65106,13 +64715,11 @@
       <c r="D1924" t="n">
         <v>-2</v>
       </c>
-      <c r="E1924" t="inlineStr"/>
       <c r="F1924" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1924" t="inlineStr"/>
     </row>
     <row r="1925">
       <c r="A1925" t="inlineStr">
@@ -65131,13 +64738,11 @@
       <c r="D1925" t="n">
         <v>-2</v>
       </c>
-      <c r="E1925" t="inlineStr"/>
       <c r="F1925" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1925" t="inlineStr"/>
     </row>
     <row r="1926">
       <c r="A1926" t="inlineStr">
@@ -65156,13 +64761,11 @@
       <c r="D1926" t="n">
         <v>-2</v>
       </c>
-      <c r="E1926" t="inlineStr"/>
       <c r="F1926" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1926" t="inlineStr"/>
     </row>
     <row r="1927">
       <c r="A1927" t="inlineStr">
@@ -65181,13 +64784,11 @@
       <c r="D1927" t="n">
         <v>-2</v>
       </c>
-      <c r="E1927" t="inlineStr"/>
       <c r="F1927" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1927" t="inlineStr"/>
     </row>
     <row r="1928">
       <c r="A1928" t="inlineStr">
@@ -65206,13 +64807,11 @@
       <c r="D1928" t="n">
         <v>-2</v>
       </c>
-      <c r="E1928" t="inlineStr"/>
       <c r="F1928" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1928" t="inlineStr"/>
     </row>
     <row r="1929">
       <c r="A1929" t="inlineStr">
@@ -65231,13 +64830,11 @@
       <c r="D1929" t="n">
         <v>-2</v>
       </c>
-      <c r="E1929" t="inlineStr"/>
       <c r="F1929" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1929" t="inlineStr"/>
     </row>
     <row r="1930">
       <c r="A1930" t="inlineStr">
@@ -65256,13 +64853,11 @@
       <c r="D1930" t="n">
         <v>-2</v>
       </c>
-      <c r="E1930" t="inlineStr"/>
       <c r="F1930" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1930" t="inlineStr"/>
     </row>
     <row r="1931">
       <c r="A1931" t="inlineStr">
@@ -65281,13 +64876,11 @@
       <c r="D1931" t="n">
         <v>-2</v>
       </c>
-      <c r="E1931" t="inlineStr"/>
       <c r="F1931" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
-      <c r="G1931" t="inlineStr"/>
     </row>
     <row r="1932">
       <c r="A1932" t="inlineStr">
@@ -65306,13 +64899,11 @@
       <c r="D1932" t="n">
         <v>-2</v>
       </c>
-      <c r="E1932" t="inlineStr"/>
       <c r="F1932" t="inlineStr">
         <is>
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
-      <c r="G1932" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -13,6 +13,7 @@
     <sheet name="发现日志" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="候选源池" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="长期源清单" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="海外聚合专项" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67732,4 +67733,375 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>盯防重点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>lane</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>收录时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ov-kilo-pricing</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kilo Code</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://kilo.ai/pricing</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ov-taotoken</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TaoToken 聚合网关</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://taotoken.net</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ov-llm7-docs</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>llm7 免费聚合</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://docs.llm7.io</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ov-agnes-ai</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agnes AI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://platform.agnes-ai.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ov-regolo-pricing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Regolo.ai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://regolo.ai/pricing/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ov-tokenharbor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TokenHarbor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://tokenharbor.ai/pricing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ov-iteracompute</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IteraCompute</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://platform.iteracompute.com/api-keys</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ov-upstage</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Upstage</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://console.upstage.ai</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ov-replicate-pricing</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Replicate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://replicate.com/pricing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ov-hf-inference</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HuggingFace 推理</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/docs/inference-providers/index</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>免费层/credits/限额变动</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ov-aggregator</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -51106,6 +51106,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
@@ -51134,6 +51139,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
@@ -51162,6 +51172,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
@@ -51190,6 +51205,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
@@ -51218,6 +51238,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
@@ -51274,6 +51299,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
@@ -51302,6 +51332,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
@@ -51330,6 +51365,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
@@ -51358,6 +51398,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
@@ -51386,6 +51431,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
@@ -51414,6 +51464,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
@@ -51442,6 +51497,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
@@ -51470,6 +51530,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
@@ -51498,6 +51563,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
@@ -51526,6 +51596,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
@@ -51554,6 +51629,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
@@ -51582,6 +51662,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
@@ -51610,6 +51695,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
@@ -51638,6 +51728,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
@@ -51666,6 +51761,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
@@ -51694,6 +51794,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
@@ -51722,6 +51827,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
@@ -51750,6 +51860,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
@@ -51778,6 +51893,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
@@ -51806,6 +51926,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
@@ -51834,6 +51959,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
@@ -51862,6 +51992,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
@@ -51890,6 +52025,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
@@ -51918,6 +52058,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
@@ -51946,6 +52091,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
@@ -51974,6 +52124,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
@@ -52002,6 +52157,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
@@ -52030,6 +52190,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
@@ -52058,6 +52223,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
@@ -52086,6 +52256,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
@@ -52114,6 +52289,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
@@ -52142,6 +52322,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
@@ -52170,6 +52355,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
@@ -52198,6 +52388,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
@@ -52226,6 +52421,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
@@ -52254,6 +52454,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
@@ -52282,6 +52487,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
@@ -52310,6 +52520,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
@@ -52338,6 +52553,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
@@ -52366,6 +52586,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
@@ -52394,6 +52619,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
@@ -52422,6 +52652,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
@@ -52450,6 +52685,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
@@ -52478,6 +52718,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
@@ -52504,6 +52749,11 @@
       <c r="F1454" t="inlineStr">
         <is>
           <t>github:aimarket/awesome-autonomous-drone</t>
+        </is>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>offtopic</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -7940,7 +7940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8848,6 +8848,28 @@
       <c r="D41" t="inlineStr">
         <is>
           <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>海外扩容会师：10 个 ov- 前缀新源建基线（llm7/TokenHarbor/Replicate/Upstage/Agnes/IteraCompute/Regolo/HF推理/Kilo/TaoToken）——主会话海外推入，采集器自动接管盯防</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>采集器</t>
         </is>
       </c>
     </row>
@@ -37944,6 +37966,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -37967,6 +37994,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -37990,6 +38022,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -38013,6 +38050,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -38036,6 +38078,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -38059,6 +38106,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -38082,6 +38134,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -38105,6 +38162,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -38128,6 +38190,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -38197,6 +38264,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -38243,6 +38315,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -38358,6 +38435,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -38496,6 +38578,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -39092,6 +39179,11 @@
       <c r="F950" t="inlineStr">
         <is>
           <t>github:AIPMAndy/FreeToken</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4930,6 +4930,110 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>线索-套餐(高优)⭐</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>阿里云 Coding Plan 骨折价 7.9 元/月</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>(公众号「财闻」多源)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>套餐订阅</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>多源(公众号标题雷达)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>号称爽玩 Claude Code；vs 智谱官宣需求火爆上调优惠——价格战开打</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plans.json/⌨️Coding面板必须跟进</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>线索-变更(高优)⭐</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>智谱 GLM Coding Plan 即日起调整首购优惠并涨价</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>(公众号标题雷达多帖)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>套餐订阅</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>多帖佐证</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>官方口径：需求火爆+成本上涨</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plans.json 智谱条目需复核</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7595,7 +7699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7929,6 +8033,33 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>财闻 🆕(雷达发现)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>阿里云/智谱 Coding Plan 价格战首发</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>微信内搜索</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>👁 人工关注</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>雷达第2个产出号，套餐类情报敏锐</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7940,7 +8071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8870,6 +9001,28 @@
       <c r="D42" t="inlineStr">
         <is>
           <t>采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>⭐雷达首捕重磅：阿里云 Coding Plan 7.9元 vs 智谱涨价——价格战开打(高优→主管)；新号「财闻」；查询词噪音待清</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>公众号专属管线</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>总表+公众号sheet</t>
         </is>
       </c>
     </row>
@@ -38343,6 +38496,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -38486,6 +38644,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -38509,6 +38672,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -38652,6 +38820,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -38675,6 +38848,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -38698,6 +38876,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -38744,6 +38927,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -38859,6 +39047,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -38905,6 +39098,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -39020,6 +39218,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -39043,6 +39246,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -39066,6 +39274,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -39135,6 +39348,11 @@
           <t>github:AIPMAndy/FreeToken</t>
         </is>
       </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -39209,6 +39427,11 @@
           <t>github:AIPMAndy/FreeToken</t>
         </is>
       </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -39232,6 +39455,11 @@
           <t>github:ruodou233/free-token-eggs</t>
         </is>
       </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -60808,6 +61036,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
@@ -60923,6 +61156,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
@@ -60946,6 +61184,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
@@ -60969,6 +61212,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
@@ -61015,6 +61263,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
@@ -61038,6 +61291,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
@@ -61107,6 +61365,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
@@ -61153,6 +61416,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
@@ -61174,6 +61442,11 @@
       <c r="F1755" t="inlineStr">
         <is>
           <t>github:OuterSpacee/free-ai-apis</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -14,6 +14,7 @@
     <sheet name="候选源池" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="长期源清单" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="海外聚合专项" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="归档-已结案" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F6F4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00666666"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -95,6 +101,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,2247 +467,2480 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>官方-API</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>OpenRouter Models API</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>https://openrouter.ai/api/v1/models</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>结构化 JSON</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>🤖 sync.py 自动</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>17+:free 模型+比价</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>免鉴权</t>
         </is>
       </c>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>时效</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>官方-API</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>ModelScope API-Inference</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://api-inference.modelscope.cn/v1/models</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>结构化 JSON</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>🤖 sync.py 自动</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>37 模型清单</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>免鉴权</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>DeepSeek 定价（中英双语）</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>https://api-docs.deepseek.com/zh-cn/quick_start/pricing</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>换代/错峰半价/缓存价</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>哈希监控</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>智谱 BigModel 定价</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://docs.bigmodel.cn/cn/guide/start/pricing.md</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>🤖 sync.py 监控</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>免费模型清单/积分公式</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>markdown 直出</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>智谱 活动页</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>https://docs.bigmodel.cn/cn/update/promotion</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>活动页</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>邀请活动</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>滞后需交叉</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ZCode Changelog</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>https://zcode.z.ai/changelog</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>changelog</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>大礼包时间线</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>客户端活动真源</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>阿里云百炼免费额度</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://help.aliyun.com/zh/model-studio/new-free-quota</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>帮助文档</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>🤖 sync.py 监控</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>70+模型 7000 万</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>火山方舟协作奖励</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>https://docs.volcengine.com/docs/ark/collaboration-reward-program</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>🤖 sync.py 监控</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>每日 500 万口径</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>讯飞 Coding Plan</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://www.xfyun.cn/doc/spark/CodingPlan.html</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>🤖 sync.py 监控</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>波谷 0.8 系数</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Kimi 会员定价</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://www.kimi.com/help/membership/membership-pricing</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>定价页</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>🤖 harvest 新源</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>会员四档</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>GitHub Copilot Plans</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://docs.github.com/en/copilot/get-started/plans</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>🤖 sync.py 监控</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>AI Credits 定案</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>硅基流动定价中心</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://siliconflow.cn/pricing</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>定价页(JS)</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>免费池收缩口径</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>UI 学习对象</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Groq Rate Limits</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://console.groq.com/docs/rate-limits</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>收缩轨迹</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Gemini API Pricing/Ratelimits</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/pricing</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>免费层数字已撤</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Azure for Students</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/en-us/free/students</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>产品页</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>$100/年</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>OpenCode Zen Models</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://opencode.ai/docs/zen</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>⏳ R8 深挖中</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>免费模型限额不透明</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>国外线第一站</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>smzdm 全网 AI 免费权益清单</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://post.smzdm.com（搜 AI 免费权益）</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>聚合帖(系列)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>月度聚合器</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>一篇抵六家公众号</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>GitHub: yacuo/ai-coding-plan</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://github.com/yacuo/ai-coding-plan</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>跟踪仓库</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>👁 每周 diff</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>各家 Coding Plan 价格</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>linux.do 福利板块</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://linux.do</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>论坛</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>🤖 RSS→草稿区</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>线索多需甄别</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>403 风控,海外 IP 可试</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>神秘喵星人 ⭐新收录</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>示例: mp.weixin.qq.com/s/7mSCNv7ZumV8urTr37eKrg</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>👁 人工关注</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>ClinePass 60亿/额度大战</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>编程羊毛第一线,往期全是干货</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>智谱系公众号</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>微信内搜索认证号</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>👁 老板人工</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>周末 3 亿/1024 5 亿</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>讯飞星火公众号</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>微信内搜索认证号</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>👁 老板人工</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>10 亿活动首发</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>火山引擎公众号</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>微信内搜索认证号</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>👁 老板人工</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>普惠季/协作奖励</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>硅基流动公众号</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>微信内搜索认证号</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>公众号</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>👁 老板人工</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>充值返券 1000 档</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>工具-自研</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>sync.py 流水线</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>tools/sync.py（40 源注册表）</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>脚本</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>🤖 Actions 每日 2 跑</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>全站续期引擎</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>工具-自研</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>harvest.py+diff</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>tools/harvest.py（19 源）</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>脚本</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>🤖 Actions 每日</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>关键词快照+告警</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>工具-自研</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>爬虫主管 agent</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>会话内 SendMessage 续单</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>AI 产线</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>🔥 按需派单</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>R1-R8 共 80+ 条</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>官方原文直核</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>硅基流动计费规则</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>https://docs.siliconflow.com/cn/faqs/billing-rules</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>14元/2000万口径</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>OpenRouter 限流文档</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://openrouter.ai/docs/api_reference/limits</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>5 命中</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>50→1000次/天规则</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Kimi 开放平台 API 定价</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://platform.kimi.com/docs/pricing/chat</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>1 命中</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>文件解析限免/缓存价</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>助理源；与会员定价页互补</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>阿里云百炼模型清单</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>https://help.aliyun.com/zh/model-studio/models</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>帮助文档(JS)</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>0 命中(CSR)</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>静态不可抓，sync.py 的 new-free-quota 页为主</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>MiniMax 定价总览</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://platform.minimax.cn/docs/pricing/overview.md</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>markdown直出</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>30 命中</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>M3 五折</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>SambaNova 限流</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>https://docs.sambanova.ai/docs/en/models/rate-limits</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>19 命中</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>免费层 20RPM/日20次</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Together AI 定价</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>https://www.together.ai/pricing</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>定价页</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>30 命中</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Bonsai 全免费</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Cerebras 定价</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>https://www.cerebras.ai/pricing</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>定价页</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>7 命中</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>$5 试用金(需绑卡)</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Mistral 用量限额</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>https://docs.mistral.ai/admin/billing-usage/usage-limits</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>30 命中</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>免费档限额</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Cohere 限流</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>https://docs.cohere.com/docs/rate-limits</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>30 命中</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Trial 1000次/月·禁商用</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>智谱杭州 Coding Plan 规则</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>https://docs.bigmodel.cn/cn/coding-plan/hangzhou-rules</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>活动规则页</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>30 命中</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>44%/51% 减免</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>12-09 活动结束后撤源</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>活动规则-CDN</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>豆包天天领额度活动规则</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>https://lf3-cdn-tos.draftstatic.com/obj/ies-hotsoon-draft/incentive-campaign-rules/f7f2c423-c770-44e7-9be4-bd67a28f074e.html</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>规则页(静态)</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>30 命中</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>签到+任务领额度/30天有效</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>老板指派；数额待客户端实锤</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>官方-页面(CSR壳)</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>豆包智能体广场</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>https://www.doubao.com/pc/agent-explore</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>活动页(CSR)</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>🤖 harvest 观察位</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>SSR恢复检测</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>0 命中属预期</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>天天领额度活动入口</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>老板指派；真源在豆包客户端</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>官方-页面</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Gemini API 限流</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>https://ai.google.dev/gemini-api/docs/rate-limits</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>文档页</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>🤖 harvest 盯防</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>11 命中</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>免费层约20RPD(缩水)</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>助理源</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>知乎·薅光天下免费token(27家)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>https://zhuanlan.zhihu.com/p/2014053076936438015</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>攻略帖</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>27家供应商免费额度清单</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2026.3 更新</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>GitHub·FreeLLM-API-KeyHub</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>https://github.com/guihuashaoxiang/FreeLLM-API-KeyHub</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>跟踪仓库</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>👁 每周 diff</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>国内免费LLM API 汇总</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>与 yacuo 仓互补</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>博客园·免费Token薅羊毛攻略(2026.7)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>攻略帖</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>企业邮箱加赠/签到技巧</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>腾讯云社区·免费Token渠道</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>https://developer.cloud.tencent.com/article/2712136</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>攻略帖</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>讯飞星辰Qwen不限量/NIM 70+</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>CSDN·每日刷新免费额度汇总</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>https://blog.csdn.net/2402_84764726/article/details/158284048</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>攻略帖</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>实名认证每日领额度</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>个人博客·2026白嫖API推荐</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>https://blog.liurb.org/posts/2026/01/06/free_api</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>攻略帖</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Google Antigravity/OpenCode Zen/小米MiMo</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>知乎·10个真永久免费无限Token</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>(知乎内搜标题)</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>攻略帖</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>长期白嫖 API 筛选</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>社区-聚合</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>SegmentFault·免费Token/优惠整理</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>(segmentfault.com 内搜)</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>攻略帖</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>👁 每周人工</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>待核</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>智谱实名送2亿Token线索</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>线索-平台</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>小米 MiMo</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>(待查官方入口)</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>⏳ 主管核实</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>新线索</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>曾推100万亿Token免费计划</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>智东西报道</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>线索-平台</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>讯飞星辰 Qwen 不限量</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>(待查官方入口)</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>⏳ 主管核实</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>新线索</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Qwen 系列 Token 不限量至 2026 年</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>腾讯云社区佐证</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>线索-平台</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>MonkeyCode / TRAE</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>(待查官方入口)</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>⏳ 主管核实</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>新线索</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>博客园攻略提及</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2753,6 +2993,11 @@
           <t>r/LLM 172 赞</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2800,6 +3045,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2847,6 +3097,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2899,6 +3154,11 @@
           <t>下轮评估入采集器</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2946,6 +3206,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2998,6 +3263,11 @@
           <t>⌨️Coding面板变更线索</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3050,6 +3320,11 @@
           <t>外网体验档</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3102,6 +3377,11 @@
           <t>超过火山500万/日6倍</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3154,6 +3434,11 @@
           <t>字节海外 IDE</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3206,31 +3491,36 @@
           <t>官网 monkeycode.cn · GitHub chaitin/MonkeyCode</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>线索-平台(外网)</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HuggingFace 推理积分</t>
+          <t>smzdm·AI产品免费权益清单(2026.09)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://huggingface.co/docs/inference-providers</t>
+          <t>https://post.smzdm.com/p/arz6v8rg</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(低优)</t>
+          <t>👁 每周人工</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3240,12 +3530,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>已查实</t>
+          <t>新发现</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>免费档仅$0.10/月≈10条消息；PRO$9/月含$2——负情报</t>
+          <t>9月版免费权益清单</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3255,24 +3545,29 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Startup 项目另有赠码渠道</t>
+          <t>主会话 smzdm 系列新增一贴</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>线索-平台</t>
+          <t>线索-平台(外网)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>小米 MiMo（已查实：免费计划已领完→转永久降价99%）</t>
+          <t>NVIDIA NIM 免费API大升级⭐</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://100t.xiaomimimo.com</t>
+          <t>https://news.cnblogs.com/n/841857</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3282,7 +3577,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(低价条目)</t>
+          <t>⏳ 主管核实(高优)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3292,12 +3587,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>已查实</t>
+          <t>双源(smzdm+cnblogs)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>100T计划5月领完；MiMo-2.5 API 约Claude 1/5价·百万上下文</t>
+          <t>80-100+模型一年免费·不限总量·40RPM·国内手机号可注册——远超主数据1000 credits口径</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3307,7 +3602,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>多源交叉：鉅亨/网易/知乎/腾讯</t>
+          <t>变更线索：nvidia-nim 条目或需改写</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3619,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>smzdm·AI产品免费权益清单(2026.09)</t>
+          <t>CSDN·每月16亿token开源API实践(姊妹两篇)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://post.smzdm.com/p/arz6v8rg</t>
+          <t>https://blog.csdn.net/weixin_32597009/article/details/163422709</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3349,7 +3649,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>9月版免费权益清单</t>
+          <t>15个免费大模型API获取指南</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3359,34 +3659,39 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>主会话 smzdm 系列新增一贴</t>
+          <t>含姊妹篇 163422710</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>线索-降级</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>讯飞星辰 Qwen 不限量=6月限时月度活动</t>
+          <t>CSDN·2026大模型API免费额度汇总</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(CSDN 博客口径，非官方)</t>
+          <t>https://blog.csdn.net/weixin_55062269/article/details/158925835</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>✅ 已查实(降级)</t>
+          <t>👁 每周人工</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3396,12 +3701,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>已过期(10月)</t>
+          <t>新发现</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>「不限量至2026年」说法不实——限时活动</t>
+          <t>百炼/千帆等额度清单</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3409,36 +3714,36 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>与讯飞避雷前科相互印证</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>线索-平台(外网)</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NVIDIA NIM 免费API大升级⭐</t>
+          <t>CSDN·2026免费LLM API完全指南</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://news.cnblogs.com/n/841857</t>
+          <t>https://blog.csdn.net/weixin_48321392/article/details/159241594</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(高优)</t>
+          <t>👁 每周人工</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3448,12 +3753,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>双源(smzdm+cnblogs)</t>
+          <t>新发现</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>80-100+模型一年免费·不限总量·40RPM·国内手机号可注册——远超主数据1000 credits口径</t>
+          <t>主流平台限额实测对比</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3461,36 +3766,36 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>变更线索：nvidia-nim 条目或需改写</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>线索-活动</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CSDN·每月16亿token开源API实践(姊妹两篇)</t>
+          <t>智谱「每日一亿 token 免费领取」</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://blog.csdn.net/weixin_32597009/article/details/163422709</t>
+          <t>https://bigmodel.cn/activity/trial-card/*（页族）</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>活动</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>⏳ 主管核实(入口已定位)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3500,12 +3805,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>单源</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>15个免费大模型API获取指南</t>
+          <t>体验卡页族已定位（8+ 个 trial-card 页），数额需登录核</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3515,34 +3820,39 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>含姊妹篇 163422710</t>
+          <t>每日登录类摸底唯一产出</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>变更线索(外网)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CSDN·2026大模型API免费额度汇总</t>
+          <t>Windsurf 并入 Cognition/Devin⭐</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://blog.csdn.net/weixin_55062269/article/details/158925835</t>
+          <t>https://devin.ai/pricing</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>⏳ 主管核实(已补全细节)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3552,44 +3862,54 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>windsurf.com 308 实测</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>百炼/千帆等额度清单</t>
+          <t>改名 Devin Desktop；积分制3月废→每日/每周用量刷新；免费档=轻量+有限Cascade；Pro$20/500+credits；薅法=devin.ai 注册14天Pro试用再登录 Windsurf</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>采集器已改指新地址</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>线索-修正</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CSDN·2026免费LLM API完全指南</t>
+          <t>小米 MiMo 额度重置+50倍配额+0.01元续费</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://blog.csdn.net/weixin_48321392/article/details/159241594</t>
+          <t>(v2ex TG 频道 2026-05 多帖)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>⏳ 主管核实</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3599,44 +3919,54 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>多帖佐证</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>主流平台限额实测对比</t>
+          <t>修正昨日「已领完」结论——现为重置+50倍态</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>另有免费送380亿额度帖</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>线索-降级</t>
+          <t>线索-平台</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>智谱「实名送2亿」未证实</t>
+          <t>快手/美团 免费 API(14天)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(SegmentFault 线索)</t>
+          <t>(v2ex 帖 cn.v2ex.com/t/1180034)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>✅ 已查实(降级)</t>
+          <t>⏳ 主管核实</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3646,12 +3976,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>官方页无此活动</t>
+          <t>单帖</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>实为:邀请2000万/注册200万/周末3亿等，2亿系夸大</t>
+          <t>国产大厂免费 API 14 天</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3659,36 +3989,36 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>防止假羊毛</t>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>线索-活动</t>
+          <t>线索-变更(外网)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>智谱「每日一亿 token 免费领取」</t>
+          <t>GitHub Copilot 学生免费权益变动⭐</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://bigmodel.cn/activity/trial-card/*（页族）</t>
+          <t>https://education.github.com/pack</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>活动</t>
+          <t>权益</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(入口已定位)</t>
+          <t>⏳ 主管核实(高优)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3698,12 +4028,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>单源</t>
+          <t>多源</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>体验卡页族已定位（8+ 个 trial-card 页），数额需登录核</t>
+          <t>Copilot Pro 学生版 3-12 终止→Copilot Student 4月暂停→现状不明；主数据 github-student-pack 条目表述需复核</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3713,34 +4043,39 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>每日登录类摸底唯一产出</t>
+          <t>Copilot Free 2000补全/50聊天 仍有效</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>变更线索(外网)</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Windsurf 并入 Cognition/Devin⭐</t>
+          <t>CSDN·2026免费额度汇总(10-14新版)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://devin.ai/pricing</t>
+          <t>https://blog.csdn.net/2601_95945860/article/details/167894223</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(已补全细节)</t>
+          <t>👁 每周人工</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3750,12 +4085,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>windsurf.com 308 实测</t>
+          <t>新发现</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>改名 Devin Desktop；积分制3月废→每日/每周用量刷新；免费档=轻量+有限Cascade；Pro$20/500+credits；薅法=devin.ai 注册14天Pro试用再登录 Windsurf</t>
+          <t>DeepSeek/Qwen 等主流盘点</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3763,36 +4098,36 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>采集器已改指新地址</t>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>竞品/同类站</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>token.pencilai.top（token羊毛党）</t>
+          <t>CSDN·AI编程免费活动盘点+避坑(10-17)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://token.pencilai.top</t>
+          <t>https://blog.csdn.net/weixin_30694389/article/details/168316137</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>汇总站</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>🤖 harvest 竞品雷达</t>
+          <t>👁 每周人工</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3802,12 +4137,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>✅ 已收编监测</t>
+          <t>新发现</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>汇集免费模型/编程套餐/领取步骤——同类站，监测其收录差异</t>
+          <t>「羊毛密度比前两月高」——市场趋势利好</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3815,36 +4150,36 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>侦察完成：编辑线=本地agent免费模型/编程套餐，网页聊天不收录（与我们差异互补）；静态78KB可抓，已入采集器</t>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>线索-修正</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>小米 MiMo 额度重置+50倍配额+0.01元续费</t>
+          <t>TaoToken 统一Key·十家免费层盘点</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(v2ex TG 频道 2026-05 多帖)</t>
+          <t>https://blog.csdn.net/weixin_35756624/article/details/167365693</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>👁 每周人工</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3854,12 +4189,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>多帖佐证</t>
+          <t>新发现</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>修正昨日「已领完」结论——现为重置+50倍态</t>
+          <t>统一网关接十家免费层——同类工具</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3867,36 +4202,36 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>另有免费送380亿额度帖</t>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>线索-平台</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>快手/美团 免费 API(14天)</t>
+          <t>lololowe·免费LLM API收集(持续更新)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(v2ex 帖 cn.v2ex.com/t/1180034)</t>
+          <t>https://blog.lololowe.com/posts/fe0d</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3906,44 +4241,49 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>单帖</t>
+          <t>✅ 评估通过已入列</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>国产大厂免费 API 14 天</t>
+          <t>智谱/硅基/千帆等 Key 获取合集</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>线索-变更(外网)</t>
+          <t>社区-聚合</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GitHub Copilot 学生免费权益变动⭐</t>
+          <t>explinks·9家免费靠谱API盘点</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://education.github.com/pack</t>
+          <t>https://www.explinks.com/blog/roundup-of-9-free-and-reliable-ai-large-model-apis-unified-encapsulation-easy-invocation</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>权益</t>
+          <t>攻略帖</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(高优)</t>
+          <t>👁 每周人工</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3953,12 +4293,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>多源</t>
+          <t>新发现</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Copilot Pro 学生版 3-12 终止→Copilot Student 4月暂停→现状不明；主数据 github-student-pack 条目表述需复核</t>
+          <t>星火/千帆/混元等</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3966,36 +4306,36 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Copilot Free 2000补全/50聊天 仍有效</t>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>线索-佐证</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CSDN·2026免费额度汇总(10-14新版)</t>
+          <t>NVIDIA AI Playground 永久免费(佐证NIM升级)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://blog.csdn.net/2601_95945860/article/details/167894223</t>
+          <t>https://build.nvidia.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>⏳ 主管核实(高优)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4005,91 +4345,106 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>多源</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DeepSeek/Qwen 等主流盘点</t>
+          <t>注册即领·GLM-4.7 Flash 128K 实测——与 NIM 升级线索互证</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>神级工具(外网)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CSDN·AI编程免费活动盘点+避坑(10-17)</t>
+          <t>OmniRoute 本地AI网关⭐</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://blog.csdn.net/weixin_30694389/article/details/168316137</t>
+          <t>https://github.com/diegosouzapw/OmniRoute</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>开源工具</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>待首轮</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>「羊毛密度比前两月高」——市场趋势利好</t>
+          <t>200-300+提供商聚一个端点·免费额度仪表盘15-16亿/月·Combo永不停机路由</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>「34家白嫖神」定位成功；CSDN 双文佐证</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>线索-平台</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TaoToken 统一Key·十家免费层盘点</t>
+          <t>TaoToken 统一Key聚合网关</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://blog.csdn.net/weixin_35756624/article/details/167365693</t>
+          <t>https://taotoken.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>⏳ 主管核实</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4099,44 +4454,54 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>CSDN 5篇推广</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>统一网关接十家免费层——同类工具</t>
+          <t>OpenAI+Anthropic双协议·国内直连·注册送免费额度——数额口径待核</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>聚合平台类（中间商层在收录范围内）</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>线索-套餐(海外)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>lololowe·免费LLM API收集(持续更新)</t>
+          <t>z.ai GLM Coding Plan 海外版</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://blog.lololowe.com/posts/fe0d</t>
+          <t>https://z.ai</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>套餐订阅</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>🤖 harvest 盯防</t>
+          <t>⏳ 主管核实</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4146,44 +4511,54 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>✅ 评估通过已入列</t>
+          <t>Reddit+第三方</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>智谱/硅基/千帆等 Key 获取合集</t>
+          <t>Lite$18/Pro$80/Max$168；配额≈Claude同级3倍；海外ZCode $16.2/月</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>⌨️Coding面板海外版候选；无常驻免费额度</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>社区-聚合</t>
+          <t>线索-工具(外网)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>explinks·9家免费靠谱API盘点</t>
+          <t>AgentReady 省 token 代理</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.explinks.com/blog/roundup-of-9-free-and-reliable-ai-large-model-apis-unified-encapsulation-easy-invocation</t>
+          <t>https://agentready.cloud</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>攻略帖</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>👁 每周人工</t>
+          <t>⏳ 主管核实(低优)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4193,34 +4568,44 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>新发现</t>
+          <t>HN 2026-02 front</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>星火/千帆/混元等</t>
+          <t>Drop-in 代理砍 LLM 成本 40-60%——生产力侧工具，非免费token源</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>HN 摸底产出</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>线索-佐证</t>
+          <t>线索-平台</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NVIDIA AI Playground 永久免费(佐证NIM升级)</t>
+          <t>美团 LongCat 开放平台⭐</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://build.nvidia.com</t>
+          <t>https://longcat.ai</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4230,7 +4615,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(高优)</t>
+          <t>⏳ 主管核实</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4245,12 +4630,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>注册即领·GLM-4.7 Flash 128K 实测——与 NIM 升级线索互证</t>
+          <t>LongCat-Flash-Chat 已开源(560B MoE)；官方平台+文档已入采集器；免费数额待控制台核</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>快手/美团线索的美团侧落点</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
@@ -4262,37 +4657,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OmniRoute 本地AI网关⭐</t>
+          <t>Kilo Code 免费路由扩展</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://github.com/diegosouzapw/OmniRoute</t>
+          <t>https://blog.kilo.ai</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>开源工具</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>🤖 harvest 盯防</t>
+          <t>⏳ 主管核实</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>待首轮</t>
+          <t>多源</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>200-300+提供商聚一个端点·免费额度仪表盘15-16亿/月·Combo永不停机路由</t>
+          <t>Kilo Auto Free：免信用卡自动路由 8+ 免费模型（开源 VS Code 扩展）</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4302,49 +4697,54 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>「34家白嫖神」定位成功；CSDN 双文佐证</t>
+          <t>其官方文档源已在采集器</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>线索-平台</t>
+          <t>竞品/同类站(老板指派)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TaoToken 统一Key聚合网关</t>
+          <t>AI羊毛情报站 aiyangmao.xyz⭐</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://taotoken.net</t>
+          <t>https://aiyangmao.xyz</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>汇总站</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>🤖 harvest 竞品雷达</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CSDN 5篇推广</t>
+          <t>待首轮</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>OpenAI+Anthropic双协议·国内直连·注册送免费额度——数额口径待核</t>
+          <t>免费×139/额度×86/token×99——内容密度高，纯前端皮肤系统(light/dark/neon)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4354,49 +4754,54 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>聚合平台类（中间商层在收录范围内）</t>
+          <t>排版学习对象：三主题一键切换+卡片圆角+CSS变量</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>线索-套餐(海外)</t>
+          <t>官方-页面(海外)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>z.ai GLM Coding Plan 海外版</t>
+          <t>DeepInfra 定价</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://z.ai</t>
+          <t>https://deepinfra.com/prices</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>套餐订阅</t>
+          <t>定价页</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Reddit+第三方</t>
+          <t>待首轮</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Lite$18/Pro$80/Max$168；配额≈Claude同级3倍；海外ZCode $16.2/月</t>
+          <t>免费起·按量</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4406,49 +4811,54 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>⌨️Coding面板海外版候选；无常驻免费额度</t>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>线索-工具(外网)</t>
+          <t>官方-页面(海外)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AgentReady 省 token 代理</t>
+          <t>Fireworks 定价</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://agentready.cloud</t>
+          <t>https://fireworks.ai/pricing</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>定价页</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(低优)</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HN 2026-02 front</t>
+          <t>待首轮</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Drop-in 代理砍 LLM 成本 40-60%——生产力侧工具，非免费token源</t>
+          <t>$1 起步积分</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4458,49 +4868,54 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>HN 摸底产出</t>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>线索-平台</t>
+          <t>官方-页面(海外)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>美团 LongCat 开放平台⭐</t>
+          <t>Modal 定价</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://longcat.ai</t>
+          <t>https://modal.com/pricing</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>定价页</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>多源</t>
+          <t>待首轮</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>LongCat-Flash-Chat 已开源(560B MoE)；官方平台+文档已入采集器；免费数额待控制台核</t>
+          <t>$30/月免费积分(历史口径)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4510,49 +4925,54 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>快手/美团线索的美团侧落点</t>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>神级工具(外网)</t>
+          <t>官方-页面(海外)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kilo Code 免费路由扩展</t>
+          <t>Novita 定价</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://blog.kilo.ai</t>
+          <t>https://novita.ai/pricing</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>定价页</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>⏳ 主管核实</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>多源</t>
+          <t>待首轮</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kilo Auto Free：免信用卡自动路由 8+ 免费模型（开源 VS Code 扩展）</t>
+          <t>free-to-start·130模型</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4562,133 +4982,148 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>其官方文档源已在采集器</t>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>竞品/同类站(老板指派)</t>
+          <t>线索-套餐(高优)⭐</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AI羊毛情报站 aiyangmao.xyz⭐</t>
+          <t>阿里云 Coding Plan 骨折价 7.9 元/月</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://aiyangmao.xyz</t>
+          <t>https://www.aliyun.com/benefit/scene/tokenplan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>汇总站</t>
+          <t>套餐订阅</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>🤖 harvest 竞品雷达</t>
+          <t>⏳ 主管核实(重要修正)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>待首轮</t>
+          <t>多源(公众号标题雷达)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>免费×139/额度×86/token×99——内容密度高，纯前端皮肤系统(light/dark/neon)</t>
+          <t>⚠️ 修正：7.9元为2026-02-22上市首月价(1.8万次请求/9万次39.9元)；低价Lite版3-20已下架——现价需控制台核；市场真相=集体涨价</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>排版学习对象：三主题一键切换+卡片圆角+CSS变量</t>
+          <t>plans.json/⌨️Coding面板必须跟进</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>官方-页面(海外)</t>
+          <t>线索-变更(高优)⭐</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DeepInfra 定价</t>
+          <t>智谱 GLM Coding Plan 即日起调整首购优惠并涨价</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://deepinfra.com/prices</t>
+          <t>(公众号标题雷达多帖)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>定价页</t>
+          <t>套餐订阅</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>🤖 harvest 盯防</t>
+          <t>⏳ 主管核实(高优)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>待首轮</t>
+          <t>多帖佐证</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>免费起·按量</t>
+          <t>官方口径：需求火爆+成本上涨</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>海外扩容战役</t>
+          <t>plans.json 智谱条目需复核</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>官方-页面(海外)</t>
+          <t>官方-页面</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fireworks 定价</t>
+          <t>阿里云 Coding Plan 官方文档</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://fireworks.ai/pricing</t>
+          <t>https://help.aliyun.com/zh/model-studio/coding-plan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>定价页</t>
+          <t>文档页</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4708,200 +5143,215 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>$1 起步积分</t>
+          <t>价格战核心页</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>海外扩容战役</t>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>官方-页面(海外)</t>
+          <t>线索-套餐(紧急)⭐</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Modal 定价</t>
+          <t>MiniMax Code 首月五折 10-31 截止</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://modal.com/pricing</t>
+          <t>(多源)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>定价页</t>
+          <t>套餐订阅</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>🤖 harvest 盯防</t>
+          <t>⏳ 主管核实(紧急·仅剩2天)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>待首轮</t>
+          <t>多源</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>$30/月免费积分(历史口径)</t>
+          <t>首月 24.5/59.5/234.5 元(次月 49/119/469)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>海外扩容战役</t>
+          <t>10-31 截止——用户马上能薅</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>官方-页面(海外)</t>
+          <t>线索-变更(高优)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Novita 定价</t>
+          <t>智谱 Coding Plan 涨价历程补全</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://novita.ai/pricing</t>
+          <t>(凤凰/明报等多源)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>定价页</t>
+          <t>套餐订阅</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>🤖 harvest 盯防</t>
+          <t>⏳ 主管核实</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>待首轮</t>
+          <t>多源</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>free-to-start·130模型</t>
+          <t>2-12 结构性+30%；7-30 积分制改版 Lite 49→118/Pro 149→538/Max 破千；老用户赠2个月新套餐</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>海外扩容战役</t>
+          <t>plans.json 智谱行需大改</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>官方-页面(海外)</t>
+          <t>情报-趋势</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>xAI 定价</t>
+          <t>低价 Coding Plan 时代正在结束</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://console.x.ai</t>
+          <t>(业内普遍观点)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>定价页</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>🤖 harvest 盯防</t>
+          <t>👁 持续观察</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>待首轮</t>
+          <t>多源</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>负情报盯防(免费档已退场)</t>
+          <t>性价比之争转向按量计费或年付锁价；Kimi K3 输出贵4倍</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>海外扩容战役</t>
+          <t>现存低价套餐价值凸显→站点应标注紧迫性</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>线索-降级(海外)</t>
+          <t>线索-传闻(突发)⭐</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>xAI 免费档退场</t>
+          <t>Claude Code 开源传闻（待官方实锤）</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>(console.x.ai)</t>
+          <t>(公众号「碗里飞Vannifaye」)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>生态事件</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>✅ 已查实(负情报)</t>
+          <t>⏳ 主管核实(高优·需官方实锤)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4911,126 +5361,79 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>多源</t>
+          <t>单源公众号</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>$150/月数据共享计划2026春退场；仅剩注册$25(或有不)——Grok4.7 $2/$6每M</t>
+          <t>「就在刚刚,Claude Code开源啦!全网狂欢」——标题级传闻，勿当事实传播；核 Anthropic/GitHub 官方口径</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>不立项，盯防再变</t>
+          <t>若属实影响全生态条目</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>近一月</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>线索-套餐(高优)⭐</t>
+          <t>官方-页面(海外)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>阿里云 Coding Plan 骨折价 7.9 元/月</t>
+          <t>xAI 定价（负情报盯防）</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>(公众号「财闻」多源)</t>
+          <t>https://console.x.ai</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>套餐订阅</t>
+          <t>定价页</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(高优)</t>
+          <t>🤖 harvest 盯防</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>多源(公众号标题雷达)</t>
+          <t>监测中</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>号称爽玩 Claude Code；vs 智谱官宣需求火爆上调优惠——价格战开打</t>
+          <t>免费档已退场——盯防是否回归或出新活动</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>plans.json/⌨️Coding面板必须跟进</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>线索-变更(高优)⭐</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>智谱 GLM Coding Plan 即日起调整首购优惠并涨价</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>(公众号标题雷达多帖)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>套餐订阅</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>⏳ 主管核实(高优)</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>多帖佐证</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>官方口径：需求火爆+成本上涨</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plans.json 智谱条目需复核</t>
+          <t>归档误伤回收：活监控源</t>
         </is>
       </c>
     </row>
@@ -7699,7 +8102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8060,6 +8463,33 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>碗里飞Vannifaye 🆕(雷达发现)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Claude Code 开源传闻首发等 AI 编程资讯</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>微信内搜索</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>👁 人工关注</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>雷达第3个产出号，突发事件敏锐</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8071,7 +8501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9021,6 +9451,72 @@
         </is>
       </c>
       <c r="D43" t="inlineStr">
+        <is>
+          <t>总表+公众号sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>阿里云 Coding Plan 官方口径全核：7.9元首月+7000万tokens+9万次请求（三官方页定位）；文档页入采集器</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>⭐价格战深挖修正：阿里云7.9元=2月旧闻+低价版已下架；市场集体涨价；紧急羊毛=MiniMax五折10-31截止；智谱涨价历程补全</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>⭐雷达捕突发：Claude Code 开源传闻(单源公众号,待官方实锤)；新号「碗里飞Vannifaye」；验证推进1410条(1002相关)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>公众号专属管线</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>总表+公众号sheet</t>
         </is>
@@ -39195,6 +39691,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -39529,6 +40030,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -39552,6 +40058,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -39575,6 +40086,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -39598,6 +40114,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -39621,6 +40142,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -39644,6 +40170,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -39690,6 +40221,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -39713,6 +40249,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -39736,6 +40277,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -39759,6 +40305,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -39782,6 +40333,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -39828,6 +40384,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
@@ -39851,6 +40412,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -39897,6 +40463,11 @@
           <t>github:amardeeplakshkar/awesome-free-llm</t>
         </is>
       </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -39920,6 +40491,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -39943,6 +40519,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -39966,6 +40547,11 @@
           <t>github:ClawLabsAI/free-ai-models</t>
         </is>
       </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -39989,6 +40575,11 @@
           <t>github:jtig37/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -40012,6 +40603,11 @@
           <t>github:ruodou233/free-token-eggs</t>
         </is>
       </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
@@ -40035,6 +40631,11 @@
           <t>github:ruodou233/free-token-eggs</t>
         </is>
       </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -40058,6 +40659,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -40150,6 +40756,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -40196,6 +40807,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -40426,6 +41042,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -40587,6 +41208,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
@@ -61472,6 +62098,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
@@ -61518,6 +62149,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
@@ -61541,6 +62177,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
@@ -61610,6 +62251,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1763">
       <c r="A1763" t="inlineStr">
@@ -61633,6 +62279,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1764">
       <c r="A1764" t="inlineStr">
@@ -61656,6 +62307,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1765">
       <c r="A1765" t="inlineStr">
@@ -61679,6 +62335,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1766">
       <c r="A1766" t="inlineStr">
@@ -61771,6 +62432,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1770">
       <c r="A1770" t="inlineStr">
@@ -61794,6 +62460,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1771">
       <c r="A1771" t="inlineStr">
@@ -61932,6 +62603,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1776" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1777">
       <c r="A1777" t="inlineStr">
@@ -61978,6 +62654,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1778" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
@@ -62001,6 +62682,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1780">
       <c r="A1780" t="inlineStr">
@@ -62093,6 +62779,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1784">
       <c r="A1784" t="inlineStr">
@@ -62116,6 +62807,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1785">
       <c r="A1785" t="inlineStr">
@@ -62139,6 +62835,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1786">
       <c r="A1786" t="inlineStr">
@@ -62208,6 +62909,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1789">
       <c r="A1789" t="inlineStr">
@@ -62231,6 +62937,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1790">
       <c r="A1790" t="inlineStr">
@@ -62254,6 +62965,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1791">
       <c r="A1791" t="inlineStr">
@@ -62275,6 +62991,11 @@
       <c r="F1791" t="inlineStr">
         <is>
           <t>github:nherx/free-llm-api-resources</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>
@@ -68719,4 +69440,462 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>官方-API</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>OpenRouter Models API</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>https://openrouter.ai/api/v1/models</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>结构化 JSON</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>🤖 sync.py 自动</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>17+:free 模型+比价</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>免鉴权</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
+      <c r="J1" s="6" t="n"/>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>时效</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>线索-平台(外网)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HuggingFace 推理积分</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/docs/inference-providers</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(低优)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已查实</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>免费档仅$0.10/月≈10条消息；PRO$9/月含$2——负情报</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Startup 项目另有赠码渠道</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>已归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>线索-平台</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小米 MiMo（已查实：免费计划已领完→转永久降价99%）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://100t.xiaomimimo.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(低价条目)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已查实</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>100T计划5月领完；MiMo-2.5 API 约Claude 1/5价·百万上下文</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>多源交叉：鉅亨/网易/知乎/腾讯</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>已归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>线索-降级</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>智谱「实名送2亿」未证实</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(SegmentFault 线索)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>活动</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>✅ 已查实(降级)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>官方页无此活动</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>实为:邀请2000万/注册200万/周末3亿等，2亿系夸大</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>防止假羊毛</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>已归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>竞品/同类站</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>token.pencilai.top（token羊毛党）</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://token.pencilai.top</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>汇总站</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🤖 harvest 竞品雷达</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>✅ 已收编监测</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>汇集免费模型/编程套餐/领取步骤——同类站，监测其收录差异</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>侦察完成：编辑线=本地agent免费模型/编程套餐，网页聊天不收录（与我们差异互补）；静态78KB可抓，已入采集器</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>已归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>线索-降级</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>讯飞星辰 Qwen 不限量=6月限时月度活动</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(CSDN 博客口径，非官方)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>活动</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✅ 已查实(降级)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>已过期(10月)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>「不限量至2026年」说法不实——限时活动</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>与讯飞避雷前科相互印证</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>官方-页面(海外)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xAI 定价</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://console.x.ai</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>定价页</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>负情报盯防(免费档已退场)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>海外扩容战役</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>线索-降级(海外)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xAI 免费档退场</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(console.x.ai)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>✅ 已查实(负情报)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>$150/月数据共享计划2026春退场；仅剩注册$25(或有不)——Grok4.7 $2/$6每M</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>不立项，盯防再变</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>近一月</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5434,6 +5434,2063 @@
       <c r="J97" t="inlineStr">
         <is>
           <t>归档误伤回收：活监控源</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>线索-套餐(1111前瞻)⭐</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>火山引擎双十一：AI程序员首月9.9元</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://developer.volcengine.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>套餐订阅</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>官方开发者社区</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>双十一促销+新模型 Doubao-Seed-Code(Agentic编程优化)——Coding Plan 价格战第三家</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1111 节点前瞻首条</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>线索-趋势</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1111 节点前瞻：智谱活动未官宣</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>(预计临近发布)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>👁 雷达持续盯</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>上周末3亿/1024节5亿先例——1111 大礼包概率高</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>changelog+promotion页已盯防</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>线索-平台(雷达)⭐</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FreeMilk 每天白送 GLM/DeepSeek/GPT 额度</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>(公众号标题线索,官方入口待定位)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>单源标题</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>手机端免费 AI 编程 Agent，每日赠送额度</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>雷达轮13</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>线索-工具(雷达)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Magpie 多平台额度聚合+自动签到</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>(公众号保姆级教程)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>单源教程</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>一个 Agent 用遍多平台免费额度——合规注意：单账号自动签到可讨论，多号坚决不收</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>雷达轮13</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>社区-聚合(公众号)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>免费 Agent/服务器/模型额度清单(筛过版)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>(公众号长文)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>聚合帖</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>👁 人工关注</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>同类筛选清单——与 token.pencilai.top 同类</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>雷达轮13</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>smzdm·2026 AI编程工具盘点(免费额度对比)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://post.smzdm.com/p/arzp7klw</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>GLM Lite 49元/月等编程工具对比</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>搜索时发现</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>smzdm·全网AI产品免费权益清单(2026.08版)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://post.smzdm.com/p/ae6dewlq</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>免费额度多为限时需及时领</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>搜索时发现</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>线索-套餐(海外)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OpenAI Codex（随 ChatGPT 各档附带）</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>(官方社区+第三方评测)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>套餐订阅</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Free 账号有计量制 Codex；$8-20→$100→$200(9月砍半)→新$500档；积分转API计价</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>⌨️Coding面板海外版候选</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>线索-算力(海外)⭐</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Kaggle 每周30小时免费GPU</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>算力</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2×T4 16GB+4CPU+29GB内存——全免费最慷慨的笔记本算力</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>海外算力层首条</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>线索-算力(海外)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lightning AI 每月22小时免费GPU</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://lightning.ai</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>算力</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>待核时效</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>历史口径22h/月，付费$0.41/hr起；2025-08上线多云GPU市场</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>线索-算力(海外)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Google Colab 免费档</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>算力</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>👁 人工关注</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>已知</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>动态T4不限时数但重度会被限；单会话上限12h</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>线索-算力(海外)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Oracle Cloud 永久免费层</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/cloud/free/</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>算力</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>多源提及</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>always free 层——云厂商中少见</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>线索-趋势</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Coding Plan 价格战烧到企业级：OpenAI 折扣挖 Anthropic 企业客户</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>(公众号标题雷达)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>单源标题</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>与阿里云7.9/智谱涨价同谱系——价格战从个人蔓延到企业</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>雷达轮17</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>线索-工具</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CC Switch 一键切换 API / Tokscale 编程成本观测</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>(公众号工具文)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>单源标题</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>AI 编程生产力侧工具两枚</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>雷达轮17</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>社区-聚合(外网)⭐</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Reddit·49家AI API审计(28家真免费)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/AgentZero/comments/1w557h5/</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>审计帖</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026最新审计——可与咱验证池互证</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>r/AgentZero</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>线索-赛道(海外)⭐</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>初创企业积分（Startup Credits）</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.getaiperks.com/en/blogs/1-maximize-free-ai-credits</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>子赛道</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>OpenAI $500/Anthropic $1000/Google $300/Azure $200/AWS $500——新子赛道，可开「初创区」</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>getaiperks+creditforstartups</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>社区-聚合(外网)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>creditforstartups·免费初创工具</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://creditforstartups.com/resources/free-startup-tools</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>聚合站</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>云积分/AI API/SaaS</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>线索-初创区⭐</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>AWS Activate 最高 $200,000 积分（开放申请✅）</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/startups</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>初创积分</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>官方</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>startups.aws.com 申请；覆盖基础设施+AI/ML 费用</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>初创区首条可行动项</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>线索-初创区</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Anthropic Startup Program $5,000(直申)/$100,000(经VC)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/startup-program-official-terms</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>初创积分</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>⚠️ 当前批次满员</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-10 月暂停收新——盯防重开</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>SecurityBoulevard 2026-08 指南</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>线索-初创区⭐</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Google for Startups 最高 $350,000（AI初创）</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/startup</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>初创积分</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>官方+dev.to指南</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>标准$200K/2年；AI档$350K含Gemini/Vertex+DeepMind导师；⚠️批准额随融资阶段浮动(有$2K先例)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>cloud.google.com/startup 申请</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>线索-科研区⭐</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Google Cloud for Researchers 最高 $5K 云积分</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>(Google 工程师渠道)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>科研积分</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>工程师贴</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>可申请制；另有 TPU Research Awards 2026 征集+Academic Research Awards（限高校教职/博士/博后）</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>科研子赛道首条</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>线索-降级</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Meta 学术 grant 2026 无在研项目</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>(搜索确认)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>科研积分</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>✅ 已查实(负情报)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>搜索确认</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>无活跃 2026 学术免费计算项目</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>不立项</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>线索-运营商云⭐</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>天翼云 免费领 2500万 Tokens</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.ctyun.cn/newsboard/1000245559</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>运营商云</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(领取路径全核·四源互证)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>官方活动页</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>路径：ctyun.cn→息壤模型推理服务控制台→模型广场→领取；已从新春限时升级为新用户长期体验额度；编程Token Plan已上GLM5.1/DeepSeek V4 Flash；四源互证(CSDN/51CTO/网易/InfoQ)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>运营商层首条·最慷慨</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>线索-运营商云</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>联通云 注册送最高 600万 Tokens</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.cucloud.cn/information/535/7137.html</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>运营商云</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>官方</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>经联通云微信公众号注册，Token Plan Lite 券，限量1万份</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>线索-运营商云</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>移动云 Coding Plan 40元/月起</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>(通信世界网报道)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>运营商云</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>媒体报道</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>三朵云首家C端套餐；未见大额免费活动</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>线索-结构建议</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>站点建议新增「运营商云」分区</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>结构建议</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>⏳ 主管拍板</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>本轮发现</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>三朵云均为官方渠道、数额大（2500万/600万）且无人收录——差异化机会</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>五层分类外新层级</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>官方-页面(运营商云)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>天翼云大模型AI专项</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.ctyun.cn/act/AI/zhuanxiang</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>活动页</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>✅ 已测可抓(941KB富内容)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2500万Tokens/息壤/GLM5/OpenClaw</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>运营商层首源</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>官方-页面(运营商云)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>联通云 Token Plan 活动</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.cucloud.cn/information/535/7137.html</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>活动页</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>✅ 已测可抓(540KB)</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>600万Tokens/公众号注册渠道/限量1万份</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>运营商层第二源</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>线索-AI浏览器⭐</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Comet(Perplexity) 全面免费+邀请送$10</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>(多源：techNice/数位时代/cnblogs)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AI浏览器</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>原$200/月→2025-10起全面免费；邀请双方各约$10额度</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>AI浏览器层首条</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>线索-AI浏览器</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Dia 免费档限额制(被Atlassian收购)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>(Atlassian社区/Reddit)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AI浏览器</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>免费档token限额未公开；Pro $20/月；早期免费不限量已终结</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>线索-AI浏览器</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>夸克 AI 功能基本免费</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>(smzdm评测)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AI浏览器</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>单源评测</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>通义/千问底座，核心AI功能免费无明确限额</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>线索-结构建议</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>站点可考虑「AI 浏览器」分区</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>结构建议</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>⏳ 主管拍板</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>本轮发现</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Comet免费+夸克免费——浏览器层羊毛密度尚可</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>线索-AI浏览器</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>360 纳米AI 免费额度无公开口径</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>(搜索确认)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AI浏览器</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>✅ 已查实(信息不足)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>搜索确认</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>大会员付费制¥216/年；2024 安全大模型免费为搜索侧</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>浏览器层补全</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>情报-趋势佐证</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026 AI 订阅涨价潮（smzdm）</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>(smzdm)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>单源</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>豆包推会员保免费版/Kimi暂停新订/DeepSeek免费版仍可用——与Coding Plan涨价互证</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>lzw.me·注册送百万级Token网站合集</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://lzw.me/a/ai-coding-llm-freeapi.html</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>唯一AI邀请送15元等渠道</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CSDN·免费LLM API平台汇总(2026最新)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://gitcode.csdn.net/6a06ced310ee7a33f272c93d.html</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>GLM-4-Flash/4.7-Flash 完全免费(128K/200K)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CSDN·白嫖党福音全网免费API指南</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://gitcode.csdn.net/6a02ec7454b52172bc737b57.html</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>攻略帖</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>国内到国际全覆盖</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>社区-聚合</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>cloudinsight·8款免费LLM API评测</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://cloudinsight.cc/zh/blog/free-ai-api</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>评测帖</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>👁 每周人工</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>新发现</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Gemini/Groq/Mistral 免费额度评测</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>情报-口径提醒</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>智谱新客赠送存在双版本口径</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>(多源对比)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>口径</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>👁 注意</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2000万永久 vs 2500万礼包 两说</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>以控制台实测为准（主数据 verify_by:auto 权威）</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>线索-平台(雷达)⭐</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>WorkBuddy 每天白拿 100 积分</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>(公众号标题线索,官方入口待定位)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(厂商已定位)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>单源标题</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>✅ 本地侦察：腾讯官方产品(com.tencent.workbuddy.mac v5.9.3)——每日100积分=大厂官方羊毛，领取入口在App内签到</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>雷达轮29</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>线索-子赛道</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AI 绘画/视频生成免费额度（即梦/可灵）</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>(cooyue 2026-10-24 评测)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>子赛道</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>单源评测(5天前)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>即梦免费积分+会员档位；可灵每日签到灵感值</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>新子类候选</t>
         </is>
       </c>
     </row>
@@ -8102,7 +10159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8490,6 +10547,33 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>孔某人的低维认知 🆕(雷达发现)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Claude Code 源码拆解等 AI 编程技术文</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>微信内搜索</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>雷达第4个产出号（技术向，羊毛相关性待观察）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8501,7 +10585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9519,6 +11603,512 @@
       <c r="D46" t="inlineStr">
         <is>
           <t>总表+公众号sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1111前瞻：火山双十一 AI程序员 9.9元+Doubao-Seed-Code 发布（价格战第三家）；智谱未官宣持续盯</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>雷达轮13大丰收：FreeMilk 每日白送额度⭐+Magpie 多平台签到工具+聚合清单长文（3线索→主管）</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>公众号专属管线</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FreeMilk 未定位(维持线索)；意外发现：tokenmost.com 已进搜索结果前列(部署可见信号)+2 篇 smzdm 新帖入表</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>OpenAI Codex 查实（随ChatGPT各档附带，Free可用）→海外Coding面板候选</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>海外算力层开拓：Kaggle 30h/周⭐+Lightning 22h/月+Colab+Oracle always free（4条→主管）</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>雷达轮17：价格战烧到企业级(OpenAI挖角)+2工具线索；验证推进1860条(1212相关)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>公众号专属管线</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>dev.to方向：49家审计帖⭐+初创积分新赛道⭐+creditforstartups 入表</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>初创区首条可行动：AWS Activate $200K开放申请✅；Anthropic $5K/$100K 满员待重开</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>初创区三巨头凑齐：Google $200K/$350K(AI)开放申请✅——AWS$200K✅+Google✅+Anthropic⏸满员</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>科研子赛道：Google Researchers $5K 可申请+TPU Awards 征集；Meta 无在研(降级)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>⭐全新层级：运营商三朵云（天翼2500万/联通600万/移动Coding Plan）+建议站点新增「运营商云」分区→主管</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>天翼云AI专项页测试通过入采集器（运营商层首源）；95源盯防全绿</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>联通云活动页测试通过入采集器（运营商层第二源）；95源盯防1项抖动</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>天翼云2500万领取路径全核+长期额度升级确认（四源互证）</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>总表线索升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1111 未官宣确认；10月下旬活动细节补全互证（10-23弹窗20万份5亿/1024节5亿至10-26）</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>雷达轮25：新号「孔某人的低维认知」（技术向）；验证推进2220条(1401相关)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>公众号专属管线</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>公众号sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>⭐新子层：AI浏览器（Comet全面免费+邀请$10⭐/Dia限额/夸克免费）+分区建议→主管</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>360纳米AI无公开口径(信息不足)；AI订阅涨价潮佐证入账</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4 个聚合源入表+智谱新客赠送双口径提醒（以控制台实测为准）</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>雷达轮29：WorkBuddy 每日100积分线索⭐(老板机器可验证)；AI绘画/视频免费额度子赛道候选</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>公众号专属管线</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>WorkBuddy 厂商定位：腾讯官方产品（本地 Info.plist 侦察）——每日100积分可信度拉满</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>总表线索升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1111仍无官宣；长青新客政策确认无变化；千帆模型清单已更新至文心5.1/DeepSeek-V4/GLM-5时代(小数据点)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>扣子口径演进确认：旧版500资源点/天说法已过时，主数据10-26实测（免费档0积分）权威——无需变更</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>日志</t>
         </is>
       </c>
     </row>
@@ -34824,7 +37414,7 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>relevant</t>
         </is>
       </c>
     </row>
@@ -41093,6 +43683,11 @@
           <t>github:mnfst/awesome-free-llm-apis</t>
         </is>
       </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
@@ -41236,6 +43831,11 @@
           <t>github:guihuashaoxiang/FreeLLM-API-KeyHu</t>
         </is>
       </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -41305,6 +43905,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -41351,6 +43956,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -41420,6 +44030,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
@@ -41443,6 +44058,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -41489,6 +44109,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -41558,6 +44183,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
@@ -41627,6 +44257,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
@@ -41673,6 +44308,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
@@ -41719,6 +44359,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
@@ -41788,6 +44433,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -41811,6 +44461,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
@@ -41857,6 +44512,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -41880,6 +44540,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
@@ -41972,6 +44637,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
@@ -42018,6 +44688,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -42064,6 +44739,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
@@ -42110,6 +44790,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -42156,6 +44841,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -42179,6 +44869,11 @@
           <t>github:open-free-llm-api/awesome-freellm</t>
         </is>
       </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -42202,6 +44897,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
@@ -42271,6 +44971,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
@@ -42294,6 +44999,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -42340,6 +45050,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -42432,6 +45147,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -42524,6 +45244,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
@@ -42616,6 +45341,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -42754,6 +45484,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
@@ -42800,6 +45535,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
@@ -42869,6 +45609,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
@@ -42938,6 +45683,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -42961,6 +45711,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
@@ -43030,6 +45785,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
@@ -43076,6 +45836,11 @@
           <t>github:ShaikhWarsi/free-ai-tools</t>
         </is>
       </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
@@ -44157,6 +46922,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -44387,6 +47157,11 @@
           <t>github:peter123023/awesome-free-llm-api</t>
         </is>
       </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
@@ -44824,6 +47599,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
@@ -44847,6 +47627,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
@@ -44939,6 +47724,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
@@ -44985,6 +47775,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
@@ -45031,6 +47826,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
@@ -45054,6 +47854,11 @@
           <t>github:mvalentsev/awesome-free-ai-coding</t>
         </is>
       </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -45146,6 +47951,11 @@
           <t>github:AIPMAndy/FreeToken</t>
         </is>
       </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
@@ -45215,6 +48025,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
@@ -45261,6 +48076,11 @@
           <t>https://www.cnblogs.com/nkds/p/21203036</t>
         </is>
       </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
@@ -45422,6 +48242,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
@@ -46342,6 +49167,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
@@ -46664,6 +49494,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
@@ -46756,6 +49591,11 @@
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
         </is>
       </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
@@ -53730,6 +56570,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
@@ -53758,6 +56603,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
@@ -53786,6 +56636,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
@@ -53814,6 +56669,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
@@ -53842,6 +56702,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
@@ -53870,6 +56735,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
@@ -53898,6 +56768,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
@@ -53926,6 +56801,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
@@ -53954,6 +56834,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
@@ -53982,6 +56867,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
@@ -54010,6 +56900,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
@@ -54038,6 +56933,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
@@ -54066,6 +56966,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
@@ -54094,6 +56999,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
@@ -54122,6 +57032,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
@@ -54150,6 +57065,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
@@ -54178,6 +57098,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
@@ -54206,6 +57131,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
@@ -54234,6 +57164,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
@@ -54262,6 +57197,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
@@ -54290,6 +57230,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
@@ -54318,6 +57263,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
@@ -54346,6 +57296,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
@@ -54374,6 +57329,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
@@ -54402,6 +57362,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
@@ -54430,6 +57395,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
@@ -54486,6 +57456,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
@@ -54514,6 +57489,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
@@ -54542,6 +57522,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
@@ -54570,6 +57555,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
@@ -54598,6 +57588,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
@@ -54626,6 +57621,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
@@ -54654,6 +57654,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
@@ -54682,6 +57687,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
@@ -54710,6 +57720,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
@@ -54738,6 +57753,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
@@ -54766,6 +57786,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
@@ -54794,6 +57819,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
@@ -54822,6 +57852,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
@@ -54850,6 +57885,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
@@ -54878,6 +57918,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
@@ -54906,6 +57951,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
@@ -54962,6 +58012,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
@@ -54990,6 +58045,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
@@ -55046,6 +58106,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
@@ -55102,6 +58167,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
@@ -55130,6 +58200,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
@@ -55158,6 +58233,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
@@ -55214,6 +58294,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
@@ -55242,6 +58327,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
@@ -55270,6 +58360,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
@@ -55298,6 +58393,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
@@ -55326,6 +58426,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
@@ -55354,6 +58459,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
@@ -55382,6 +58492,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
@@ -55410,6 +58525,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
@@ -55438,6 +58558,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
@@ -55466,6 +58591,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
@@ -55494,6 +58624,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
@@ -55522,6 +58657,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
@@ -55550,6 +58690,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
@@ -55578,6 +58723,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
@@ -55606,6 +58756,11 @@
           <t>github:KhaiTrang1995/agentic-awesome-kit</t>
         </is>
       </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
@@ -55634,6 +58789,11 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
@@ -55662,6 +58822,11 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
@@ -55690,6 +58855,11 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
@@ -55718,6 +58888,11 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
@@ -55746,6 +58921,11 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
@@ -55774,6 +58954,11 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
@@ -55802,6 +58987,11 @@
           <t>github:precis1onz/tokenation</t>
         </is>
       </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
@@ -55830,6 +59020,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
@@ -55858,6 +59053,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
@@ -55886,6 +59086,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
@@ -55914,6 +59119,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
@@ -55942,6 +59152,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
@@ -55970,6 +59185,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
@@ -55998,6 +59218,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
@@ -56026,6 +59251,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
@@ -56054,6 +59284,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
@@ -56082,6 +59317,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
@@ -56110,6 +59350,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
@@ -56138,6 +59383,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
@@ -56166,6 +59416,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
@@ -56194,6 +59449,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
@@ -56222,6 +59482,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
@@ -56250,6 +59515,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
@@ -56278,6 +59548,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
@@ -56306,6 +59581,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
@@ -56334,6 +59614,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
@@ -56362,6 +59647,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
@@ -56390,6 +59680,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
@@ -56418,6 +59713,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
@@ -56446,6 +59746,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
@@ -56474,6 +59779,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
@@ -56502,6 +59812,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
@@ -56530,6 +59845,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
@@ -56558,6 +59878,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
@@ -56586,6 +59911,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
@@ -56614,6 +59944,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
@@ -56642,6 +59977,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
@@ -56670,6 +60010,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
@@ -56698,6 +60043,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
@@ -56726,6 +60076,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
@@ -56754,6 +60109,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
@@ -56782,6 +60142,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
@@ -56810,6 +60175,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
@@ -56838,6 +60208,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
@@ -56866,6 +60241,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
@@ -56894,6 +60274,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
@@ -56922,6 +60307,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
@@ -56950,6 +60340,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
@@ -56978,6 +60373,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
@@ -57006,6 +60406,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
@@ -57034,6 +60439,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
@@ -57062,6 +60472,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
@@ -57090,6 +60505,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
@@ -57118,6 +60538,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
@@ -57146,6 +60571,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
@@ -57174,6 +60604,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
@@ -57202,6 +60637,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
@@ -57230,6 +60670,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
@@ -57258,6 +60703,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
@@ -57286,6 +60736,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
@@ -57314,6 +60769,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
@@ -57342,6 +60802,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
@@ -57370,6 +60835,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
@@ -57398,6 +60868,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
@@ -57426,6 +60901,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
@@ -57454,6 +60934,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
@@ -57482,6 +60967,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
@@ -57510,6 +61000,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
@@ -57538,6 +61033,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
@@ -57566,6 +61066,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
@@ -57594,6 +61099,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
@@ -57622,6 +61132,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
@@ -57650,6 +61165,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
@@ -57678,6 +61198,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
@@ -57706,6 +61231,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
@@ -57734,6 +61264,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
@@ -57762,6 +61297,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
@@ -57790,6 +61330,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
@@ -57818,6 +61363,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
@@ -57846,6 +61396,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
@@ -57874,6 +61429,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
@@ -57902,6 +61462,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
@@ -57930,6 +61495,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
@@ -57958,6 +61528,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
@@ -57986,6 +61561,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
@@ -58014,6 +61594,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
@@ -58042,6 +61627,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
@@ -58070,6 +61660,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
@@ -58098,6 +61693,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
@@ -58126,6 +61726,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
@@ -58154,6 +61759,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
@@ -58210,6 +61820,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
@@ -58238,6 +61853,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
@@ -58266,6 +61886,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
@@ -58322,6 +61947,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
@@ -58350,6 +61980,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
@@ -58378,6 +62013,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
@@ -58406,6 +62046,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
@@ -58434,6 +62079,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
@@ -58462,6 +62112,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
@@ -58490,6 +62145,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
@@ -58518,6 +62178,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
@@ -58546,6 +62211,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
@@ -58574,6 +62244,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
@@ -58602,6 +62277,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
@@ -58630,6 +62310,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
@@ -58658,6 +62343,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
@@ -58686,6 +62376,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
@@ -58714,6 +62409,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
@@ -58742,6 +62442,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
@@ -58770,6 +62475,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
@@ -58798,6 +62508,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
@@ -58826,6 +62541,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
@@ -58854,6 +62574,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
@@ -58882,6 +62607,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
@@ -58910,6 +62640,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
@@ -58938,6 +62673,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
@@ -58966,6 +62706,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
@@ -58994,6 +62739,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
@@ -59022,6 +62772,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
@@ -59050,6 +62805,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
@@ -59078,6 +62838,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
@@ -59106,6 +62871,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
@@ -59134,6 +62904,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
@@ -59162,6 +62937,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
@@ -59190,6 +62970,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
@@ -59218,6 +63003,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
@@ -59246,6 +63036,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
@@ -59274,6 +63069,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
@@ -59302,6 +63102,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
@@ -59330,6 +63135,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
@@ -59358,6 +63168,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
@@ -59386,6 +63201,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
@@ -59414,6 +63234,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
@@ -59442,6 +63267,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
@@ -59470,6 +63300,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
@@ -59498,6 +63333,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
@@ -59526,6 +63366,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
@@ -59554,6 +63399,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
@@ -59582,6 +63432,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
@@ -59638,6 +63493,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
@@ -59666,6 +63526,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
@@ -59694,6 +63559,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
@@ -59722,6 +63592,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
@@ -59750,6 +63625,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
@@ -59806,6 +63686,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
@@ -59834,6 +63719,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
@@ -59862,6 +63752,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
@@ -59890,6 +63785,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
@@ -59918,6 +63818,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
@@ -59946,6 +63851,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
@@ -59974,6 +63884,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
@@ -60002,6 +63917,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
@@ -60030,6 +63950,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
@@ -60058,6 +63983,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
@@ -60086,6 +64016,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
@@ -60114,6 +64049,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
@@ -60142,6 +64082,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
@@ -60170,6 +64115,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
@@ -60198,6 +64148,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
@@ -60226,6 +64181,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
@@ -60254,6 +64214,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
@@ -60282,6 +64247,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
@@ -60310,6 +64280,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
@@ -60338,6 +64313,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
@@ -60366,6 +64346,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
@@ -60394,6 +64379,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
@@ -60422,6 +64412,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
@@ -60450,6 +64445,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
@@ -60478,6 +64478,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
@@ -60506,6 +64511,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
@@ -60562,6 +64572,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
@@ -60590,6 +64605,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
@@ -60618,6 +64638,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
@@ -60646,6 +64671,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
@@ -60674,6 +64704,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
@@ -60702,6 +64737,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
@@ -60758,6 +64798,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
@@ -60786,6 +64831,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
@@ -60814,6 +64864,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
@@ -60842,6 +64897,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
@@ -60898,6 +64958,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
@@ -60926,6 +64991,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
@@ -60954,6 +65024,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
@@ -60982,6 +65057,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
@@ -61010,6 +65090,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
@@ -61038,6 +65123,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
@@ -61066,6 +65156,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
@@ -61094,6 +65189,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
@@ -61122,6 +65222,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
@@ -61150,6 +65255,11 @@
           <t>github:Krushnaapatil/free-llm-api-resour</t>
         </is>
       </c>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
@@ -61371,6 +65481,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
@@ -61417,6 +65532,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
@@ -61440,6 +65560,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
@@ -61463,6 +65588,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
@@ -61486,6 +65616,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
@@ -61509,6 +65644,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
@@ -61532,6 +65672,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
@@ -61555,6 +65700,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
@@ -63044,6 +67194,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1794">
       <c r="A1794" t="inlineStr">
@@ -63113,6 +67268,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1797">
       <c r="A1797" t="inlineStr">
@@ -63182,6 +67342,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1800">
       <c r="A1800" t="inlineStr">
@@ -63228,6 +67393,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1802">
       <c r="A1802" t="inlineStr">
@@ -63274,6 +67444,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1803" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1804">
       <c r="A1804" t="inlineStr">
@@ -63343,6 +67518,11 @@
           <t>github:aimarket/awesome-autonomous-drone</t>
         </is>
       </c>
+      <c r="G1806" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1807">
       <c r="A1807" t="inlineStr">
@@ -63458,6 +67638,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1811" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1812">
       <c r="A1812" t="inlineStr">
@@ -63550,6 +67735,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1815" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1816">
       <c r="A1816" t="inlineStr">
@@ -63596,6 +67786,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1817" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1818">
       <c r="A1818" t="inlineStr">
@@ -63642,6 +67837,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1819" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1820">
       <c r="A1820" t="inlineStr">
@@ -63711,6 +67911,11 @@
           <t>github:ayoubncbae/awesome-medical-world-</t>
         </is>
       </c>
+      <c r="G1822" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1823">
       <c r="A1823" t="inlineStr">
@@ -63803,6 +68008,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1826" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
@@ -63826,6 +68036,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1827" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1828">
       <c r="A1828" t="inlineStr">
@@ -63964,6 +68179,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1833" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1834">
       <c r="A1834" t="inlineStr">
@@ -63987,6 +68207,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1834" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1835">
       <c r="A1835" t="inlineStr">
@@ -64033,6 +68258,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1836" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1837">
       <c r="A1837" t="inlineStr">
@@ -64079,6 +68309,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1838" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1839">
       <c r="A1839" t="inlineStr">
@@ -64194,6 +68429,11 @@
           <t>github:OuterSpacee/free-ai-apis</t>
         </is>
       </c>
+      <c r="G1843" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1844">
       <c r="A1844" t="inlineStr">
@@ -64263,6 +68503,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1846" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1847">
       <c r="A1847" t="inlineStr">
@@ -64286,6 +68531,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1847" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1848">
       <c r="A1848" t="inlineStr">
@@ -64309,6 +68559,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1848" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1849">
       <c r="A1849" t="inlineStr">
@@ -64332,6 +68587,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1849" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1850">
       <c r="A1850" t="inlineStr">
@@ -64447,6 +68707,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1854" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1855">
       <c r="A1855" t="inlineStr">
@@ -64539,6 +68804,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1858" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1859">
       <c r="A1859" t="inlineStr">
@@ -64562,6 +68832,11 @@
           <t>github:YoannDev90/awesome-free-ai-api</t>
         </is>
       </c>
+      <c r="G1859" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1860">
       <c r="A1860" t="inlineStr">
@@ -64677,6 +68952,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1864" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1865">
       <c r="A1865" t="inlineStr">
@@ -64700,6 +68980,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1865" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1866">
       <c r="A1866" t="inlineStr">
@@ -64746,6 +69031,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1867" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1868">
       <c r="A1868" t="inlineStr">
@@ -64769,6 +69059,11 @@
           <t>github:oniondas/Awesome-Hidden-AI-Credit</t>
         </is>
       </c>
+      <c r="G1868" t="inlineStr">
+        <is>
+          <t>relevant</t>
+        </is>
+      </c>
     </row>
     <row r="1869">
       <c r="A1869" t="inlineStr">
@@ -64815,6 +69110,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1870" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
     </row>
     <row r="1871">
       <c r="A1871" t="inlineStr">
@@ -65574,6 +69874,11 @@
           <t>github:velo4705/awesome-free-byok-models</t>
         </is>
       </c>
+      <c r="G1903" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1904">
       <c r="A1904" t="inlineStr">
@@ -65689,6 +69994,11 @@
           <t>github:nherx/free-llm-api-resources</t>
         </is>
       </c>
+      <c r="G1908" t="inlineStr">
+        <is>
+          <t>offtopic</t>
+        </is>
+      </c>
     </row>
     <row r="1909">
       <c r="A1909" t="inlineStr">
@@ -65781,6 +70091,11 @@
           <t>https://blog.csdn.net/2402_84764726/arti</t>
         </is>
       </c>
+      <c r="G1912" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
     </row>
     <row r="1913">
       <c r="A1913" t="inlineStr">
@@ -66239,6 +70554,11 @@
       <c r="F1932" t="inlineStr">
         <is>
           <t>https://blog.liurb.org/posts/2026/01/06/</t>
+        </is>
+      </c>
+      <c r="G1932" t="inlineStr">
+        <is>
+          <t>relevant</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7493,6 +7493,158 @@
           <t>新子类候选</t>
         </is>
       </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>线索-活动(雷达)⭐</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>「白捡价值900块的大模型额度」长文+领取指南内容潮</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>(公众号多帖)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>活动聚合</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>多帖内容潮</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>小米MiMo入口/双11券+AI额度15条/现在能领清单——1111预热实锤；长文可解析直达全文提取清单</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>雷达轮34</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>情报-生态(TG雷达)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GitHub 发布 Copilot Fusion 多模型自动编排</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>(TG AI_News_CN·Universe2026)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>生态</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>官方大会</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>自动路由 OpenAI/Anthropic/Google——⌨️Coding面板相关新品</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>TG监视器首捕</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>情报-成本(TG雷达)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Particle-1(DeepSeek V4.1 Flash后训练)编码token用量-39%</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>(TG AI_News_CN)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>成本优化</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>实测基准</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>88个Go任务实测：token-39%/成本降低</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10585,7 +10737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12109,6 +12261,50 @@
       <c r="D69" t="inlineStr">
         <is>
           <t>日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>⭐雷达轮34：「白捡900块额度」长文+领取指南内容潮（1111预热实锤）；Trae国际站源(主会话)；垃圾账号清理+提取加固</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>公众号专属管线</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>⭐Telegram监视器收编4频道(linuxdoit/linuxdo_tg/AI_Copilot/AI_News_CN)首扫11命中：Copilot Fusion发布+Particle-1省token实测+Anthropic企业管控</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TG管线</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>总表</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K144"/>
+  <dimension ref="A1:K147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7793,6 +7793,162 @@
       <c r="I144" t="inlineStr">
         <is>
           <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>官方-页面</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>阶跃星辰 Step Plan</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://platform.stepfun.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>平台页</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>盲区补全：15天Mini Plan免费领</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>盲区补全</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>官方-页面</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>天工开放平台</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://model-platform.tiangong.cn/</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>平台页</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>🤖 harvest 盯防</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>待首轮</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>盲区补全：昆仑万维官方平台</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>盲区补全</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>情报-口径(已知)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>阶跃 STEPX Neo 购机送月百亿Token(12个月)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>(搜索发现)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>硬件捆绑</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>单源</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>3999元手机捆绑连续12个月月百亿Token——硬件羊毛子类</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>盲区扫描发现</t>
         </is>
       </c>
     </row>
@@ -10914,7 +11070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12548,6 +12704,28 @@
       <c r="D74" t="inlineStr">
         <is>
           <t>日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>全网覆盖战役开打：盲区图谱生成（Agent平台全盲/国产5家盲/绘画视频浅）；+2 官方源；STEPX硬件捆绑Token线索</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>盲区补全</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>总表+采集器</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7949,6 +7949,58 @@
       <c r="J147" t="inlineStr">
         <is>
           <t>盲区扫描发现</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>情报-Agent平台口径</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Agent平台盲区清扫（四平台免费口径核）</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>(多源对比)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>口径</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>👁 与主数据一致</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>清扫确认</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>扣子资源点/Dify Sandbox 200次/FastGPT积分制/n8n社区版全免费——主数据口径准确无需变更</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>全网覆盖战役</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12726,6 +12778,28 @@
       <c r="D75" t="inlineStr">
         <is>
           <t>总表+采集器</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>全网覆盖：Agent平台盲区清扫完成（口径与主数据一致）；prev.json git冲突故障修复；152源全量跑通</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5h巡检+盲区补全</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>总表+日志</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8003,6 +8003,462 @@
           <t>全网覆盖战役</t>
         </is>
       </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>线索-活动(雷达)⭐</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GLM-5.1 发布+白嫖 7 天 AI 编程</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>(公众号标题雷达)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>新模型+试用</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>标题雷达</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>GLM-5.1 新模型上线+7天编程试用——⌨️Coding面板/新品条目双相关</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>雷达轮40</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>线索-试用(雷达)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>小米 MiMo-V2-Pro 编程试用教程</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>(公众号标题雷达)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>试用</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>标题雷达</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>MiMo-V2-Pro 编程免费试用（与 MiMo 条目互补）</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>雷达轮40</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>线索-中转(雷达)⭐</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>AI世创云：Claude Code 5折接入 DeepSeek-V4.1-Flash</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>(公众号「AI世创云」)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>中转平台</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>单源标题</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>中转平台跟进价格战——需核平台资质与模型真实性（防套壳）</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>雷达轮41</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>线索-套餐(海外)⭐</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OpenAI Pro/Business 每月可领最高 $500 API 额度</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>(TG AI_News_CN 转官方更新)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>套餐订阅</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>官方连续更新(第24天)</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>连续28天更新第24天：符合条件的 Pro/Business 月领最高$500 API credits</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>TG监视器捕获</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>线索-活动(雷达)⭐⭐</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Anthropic 开源维护者免费 Claude Max（1万名额先到先得）</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>(公众号标题雷达)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>开发者福利</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实(高优·限时)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>多帖</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>6个月 20x 配额——开源维护者身份可申；名额限时</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>本轮最热羊毛</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>线索-变更(雷达)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Anthropic 向免费 Claude 用户开放多项高级功能</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>(公众号「大众软件」)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>功能变更</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>官方号转述</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>免费档功能扩容</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>大众软件=新号(第8号)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>线索-工具(雷达)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Command Code GOAT 计划 $100 用量额度永久化</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>(TG AI_News_CN)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>TG捕获</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>$10 GOAT 计划的 $100 用量永久化</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>线索-活动(雷达)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>OpenCode「Operation Christmas」免费额度活动</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>(TG linuxdo_tg)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>限时活动</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>TG捕获</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>OpenCode 推出 Operation Ch...(截断，详待核)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>风险提醒(雷达)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Grok Ultra 7天试用反薅提醒</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>(TG linuxdo_tg)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>风险提示</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>社区实测</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>苹果渠道试用 Grok Ultra 记得关订阅，否则反薅</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10669,7 +11125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11111,6 +11567,60 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI世创云 🆕(雷达发现)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Claude Code 5折接 DeepSeek 等中转优惠</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>微信内搜索</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>雷达第7个产出号（中转类，资质待核）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>大众软件 🆕(雷达发现)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Anthropic 免费用户高级功能开放等</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>微信内搜索</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>👁 人工关注</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>雷达第8个产出号</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11122,7 +11632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12800,6 +13310,94 @@
       <c r="D76" t="inlineStr">
         <is>
           <t>总表+日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>雷达轮40：GLM-5.1发布+7天白嫖⭐+MiMo-V2-Pro试用；28项变化=VPN波动潮恢复为主(天翼/联通/Cursor内容变化二次观测中)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>5h巡检</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>总表</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5h巡检：154源采集完成落盘（尾部管线后台收尾中）；VPN波动潮持续（4-6源瞬时失败自愈类）</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5h巡检</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>双雷达捕获：AI世创云 Claude Code 5折接DeepSeek(资质待核)+OpenAI Pro/Business 月领最高$500 API credits⭐</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>5h巡检+管线</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>总表+公众号sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>⭐雷达大丰收：Anthropic 开源维护者免费 Claude Max(1万名额)⭐+免费档功能扩容+Command Code $100永久化+OpenCode圣诞活动+Grok试用反薅提醒；43源失败=断网时段采集（现已恢复自愈）</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>5h巡检+双管线</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>总表+公众号sheet</t>
         </is>
       </c>
     </row>

--- a/data-research/信息源总表-全量版.xlsx
+++ b/data-research/信息源总表-全量版.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K157"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>(公众号标题雷达)</t>
+          <t>https://claude.com/contact-sales/claude-for-oss</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>⏳ 主管核实(高优·限时)</t>
+          <t>⏳ 主管核实(官方入口已核)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6个月 20x 配额——开源维护者身份可申；名额限时</t>
+          <t>官方申请入口已定位；条件=公开仓库主要维护者+5000 Star或NPM月下载100万（关键基础设施可特批说明）；6个月Max 20x价值$1200无需绑卡；名额1万（2万系误传修正）</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8362,7 +8362,6 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8410,7 +8409,6 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8458,7 +8456,58 @@
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>情报-风险(雷达)⭐</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>API 中转站「蒸馏」掺假风暴：187篇论文因盗版API翻车</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>(公众号标题雷达多帖)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>行业风险</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>⏳ 主管核实</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>多源</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>准确率83%→37%——**对我们站点是重要风险教育内容**：用户以为省钱实被蒸馏，中转站选型指南价值凸显</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>雷达轮43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11125,7 +11174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11621,6 +11670,33 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>赵逍遥Xavier 🆕(雷达发现)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AI 编程/中转站评测类</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>微信内搜索</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>👁 观察</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>雷达第9个产出号</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11632,7 +11708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13398,6 +13474,94 @@
       <c r="D80" t="inlineStr">
         <is>
           <t>总表+公众号sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Claude for OSS 官方入口定位+名额修正(1万)——高优羊毛可行动项</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>15分钟找源巡检</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>总表线索升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>雷达轮43：API中转站蒸馏掺假风暴⭐(187篇论文翻车——风险教育内容)+新号「赵逍遥Xavier」；47项变化含VPN波动恢复潮</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5h巡检</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>总表+公众号sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OpenCode「圣诞活动」未获官方确认——降级低优观察（opencode.ai 无公告；该公司促销谨慎）</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5h巡检</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5h轮44收尾：查询词噪音修正（「模型免费送」撞实体模型赠品→「大模型限免」）；TG捕获Gemini反代帖（灰产边缘观察）；7源失败=VPN波恢复</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5h巡检</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>日志</t>
         </is>
       </c>
     </row>
